--- a/Meta/Analytes3.xlsx
+++ b/Meta/Analytes3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/vitense_kelsey_epa_gov/Documents/GL_Data/Meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2B3F092-6A59-41EA-9D13-A71F4529A48B}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CD11F8-FC60-46E6-8AFE-FA02E2177325}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-3490" windowWidth="25820" windowHeight="15500" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="802" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="11" r:id="rId1"/>
@@ -1953,9 +1953,6 @@
     <t>Turbidity_USGS</t>
   </si>
   <si>
-    <t>par</t>
-  </si>
-  <si>
     <t>Remove because no surface PAR to compute CPAR</t>
   </si>
   <si>
@@ -2137,6 +2134,9 @@
   </si>
   <si>
     <t>Units of associated measurement.</t>
+  </si>
+  <si>
+    <t>PAR</t>
   </si>
 </sst>
 </file>
@@ -2614,11 +2614,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2626,10 +2650,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2643,30 +2667,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2971,284 +2971,284 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944E5B29-DA5B-4213-9FBD-6DB720F31476}">
   <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="65"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="65"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="65" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="65"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="65" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="65" t="s">
+      <c r="B8" t="s">
         <v>636</v>
       </c>
-      <c r="B8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="65" t="s">
         <v>76</v>
       </c>
       <c r="B9" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="65" t="s">
+        <v>639</v>
+      </c>
+      <c r="B10" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="65" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="65" t="s">
+        <v>641</v>
+      </c>
+      <c r="B11" t="s">
         <v>640</v>
       </c>
-      <c r="B10" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="65" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="65" t="s">
         <v>642</v>
       </c>
-      <c r="B11" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="65" t="s">
+      <c r="B12" t="s">
         <v>643</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="65" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="B13" t="s">
         <v>645</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="65" t="s">
+        <v>687</v>
+      </c>
+      <c r="B14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="65" t="s">
+        <v>688</v>
+      </c>
+      <c r="B15" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="65" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
-        <v>688</v>
-      </c>
-      <c r="B14" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="65" t="s">
-        <v>689</v>
-      </c>
-      <c r="B15" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="B16" t="s">
         <v>647</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="65" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
+      <c r="B17" t="s">
         <v>649</v>
       </c>
-      <c r="B17" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="65" t="s">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="65" t="s">
         <v>568</v>
       </c>
       <c r="B19" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="65" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="65" t="s">
+      <c r="B20" t="s">
         <v>653</v>
       </c>
-      <c r="B20" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="65" t="s">
         <v>570</v>
       </c>
       <c r="B21" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="65" t="s">
+        <v>654</v>
+      </c>
+      <c r="B22" t="s">
         <v>655</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="65" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="65" t="s">
+      <c r="B23" t="s">
         <v>657</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="65" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
+      <c r="B24" t="s">
         <v>659</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="65" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="B25" t="s">
         <v>661</v>
       </c>
-      <c r="B25" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="65" t="s">
         <v>569</v>
       </c>
       <c r="B26" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="65" t="s">
+        <v>662</v>
+      </c>
+      <c r="B27" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="65" t="s">
         <v>663</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="65" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="65" t="s">
         <v>664</v>
       </c>
-      <c r="B28" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="65" t="s">
+      <c r="B29" t="s">
         <v>665</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="65" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+      <c r="B30" t="s">
         <v>667</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="65" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="65" t="s">
+      <c r="B31" t="s">
         <v>669</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="65" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="65" t="s">
+      <c r="B32" t="s">
         <v>671</v>
       </c>
-      <c r="B32" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="65" t="s">
         <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="65" t="s">
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="65" t="s">
         <v>152</v>
       </c>
       <c r="B35" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="65" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="65" t="s">
+      <c r="B36" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="65" t="s">
         <v>676</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="65" t="s">
-        <v>677</v>
-      </c>
-      <c r="B37" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="63"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="64"/>
     </row>
   </sheetData>
@@ -3262,16 +3262,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>258</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>224</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>287</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>291</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>295</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>438</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>57</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>61</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>268</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>328</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>329</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>331</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>333</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>337</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>339</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>37</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>35</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>360</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>44</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>94</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>308</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>300</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>149</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>111</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>52</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>39</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>36</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>394</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>47</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>119</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>396</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>397</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>196</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>410</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>233</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>416</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>417</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>63</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>27</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>204</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>434</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>431</v>
       </c>
@@ -4030,23 +4030,23 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L127"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="75.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="64.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>76</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="165" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>75</v>
       </c>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>75</v>
       </c>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>75</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
     </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>75</v>
       </c>
@@ -4204,7 +4204,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
     </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>75</v>
       </c>
@@ -4232,7 +4232,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>75</v>
       </c>
@@ -4262,7 +4262,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>75</v>
       </c>
@@ -4292,7 +4292,7 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>75</v>
       </c>
@@ -4322,7 +4322,7 @@
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>75</v>
       </c>
@@ -4350,7 +4350,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>75</v>
       </c>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>75</v>
       </c>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>75</v>
       </c>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L13" s="13"/>
     </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="L14" s="13"/>
     </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>75</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>75</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
     </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>75</v>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
     </row>
-    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>75</v>
       </c>
@@ -4608,7 +4608,7 @@
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
     </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>75</v>
       </c>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="L20" s="13"/>
     </row>
-    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>75</v>
       </c>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="L21" s="13"/>
     </row>
-    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>75</v>
       </c>
@@ -4700,7 +4700,7 @@
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
     </row>
-    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>75</v>
       </c>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>75</v>
       </c>
@@ -4762,7 +4762,7 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
     </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>75</v>
       </c>
@@ -4790,7 +4790,7 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
     </row>
-    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>75</v>
       </c>
@@ -4818,7 +4818,7 @@
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
     </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>75</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
     </row>
-    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>75</v>
       </c>
@@ -4876,7 +4876,7 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
     </row>
-    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>75</v>
       </c>
@@ -4904,7 +4904,7 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>75</v>
       </c>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>75</v>
       </c>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="L31" s="13"/>
     </row>
-    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>500</v>
       </c>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="L32" s="13"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>500</v>
       </c>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="L33" s="13"/>
     </row>
-    <row r="34" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>500</v>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>500</v>
       </c>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="L35" s="13"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>500</v>
       </c>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L36" s="13"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>500</v>
       </c>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L37" s="13"/>
     </row>
-    <row r="38" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>500</v>
       </c>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="L38" s="13"/>
     </row>
-    <row r="39" spans="1:12" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>500</v>
       </c>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="L39" s="13"/>
     </row>
-    <row r="40" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>500</v>
       </c>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L40" s="13"/>
     </row>
-    <row r="41" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>500</v>
       </c>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L41" s="13"/>
     </row>
-    <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>500</v>
       </c>
@@ -5288,7 +5288,7 @@
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
     </row>
-    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>500</v>
       </c>
@@ -5314,7 +5314,7 @@
       <c r="K43" s="13"/>
       <c r="L43" s="13"/>
     </row>
-    <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>500</v>
       </c>
@@ -5342,7 +5342,7 @@
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
     </row>
-    <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>500</v>
       </c>
@@ -5370,7 +5370,7 @@
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
     </row>
-    <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>500</v>
       </c>
@@ -5398,7 +5398,7 @@
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
     </row>
-    <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>500</v>
       </c>
@@ -5426,7 +5426,7 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13"/>
     </row>
-    <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>500</v>
       </c>
@@ -5454,7 +5454,7 @@
       <c r="K48" s="13"/>
       <c r="L48" s="13"/>
     </row>
-    <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>500</v>
       </c>
@@ -5482,7 +5482,7 @@
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
     </row>
-    <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>500</v>
       </c>
@@ -5508,7 +5508,7 @@
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
     </row>
-    <row r="51" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>500</v>
       </c>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="L51" s="13"/>
     </row>
-    <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>500</v>
       </c>
@@ -5562,7 +5562,7 @@
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
     </row>
-    <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>500</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
     </row>
-    <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>500</v>
       </c>
@@ -5614,7 +5614,7 @@
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
     </row>
-    <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>500</v>
       </c>
@@ -5640,7 +5640,7 @@
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
     </row>
-    <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>500</v>
       </c>
@@ -5666,7 +5666,7 @@
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
     </row>
-    <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>500</v>
       </c>
@@ -5692,7 +5692,7 @@
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
     </row>
-    <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>500</v>
       </c>
@@ -5718,7 +5718,7 @@
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
     </row>
-    <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>500</v>
       </c>
@@ -5744,7 +5744,7 @@
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
     </row>
-    <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>500</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
     </row>
-    <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>500</v>
       </c>
@@ -5798,7 +5798,7 @@
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
     </row>
-    <row r="62" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>500</v>
       </c>
@@ -5826,7 +5826,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
     </row>
-    <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>500</v>
       </c>
@@ -5852,7 +5852,7 @@
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
     </row>
-    <row r="64" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>500</v>
       </c>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="L64" s="13"/>
     </row>
-    <row r="65" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>500</v>
       </c>
@@ -5908,7 +5908,7 @@
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
     </row>
-    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>500</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
     </row>
-    <row r="67" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>500</v>
       </c>
@@ -5960,7 +5960,7 @@
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
     </row>
-    <row r="68" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>500</v>
       </c>
@@ -5986,7 +5986,7 @@
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
     </row>
-    <row r="69" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>500</v>
       </c>
@@ -6012,7 +6012,7 @@
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
     </row>
-    <row r="70" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>500</v>
       </c>
@@ -6040,7 +6040,7 @@
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
     </row>
-    <row r="71" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>500</v>
       </c>
@@ -6068,7 +6068,7 @@
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
     </row>
-    <row r="72" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>500</v>
       </c>
@@ -6090,7 +6090,7 @@
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
     </row>
-    <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>500</v>
       </c>
@@ -6118,7 +6118,7 @@
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
     </row>
-    <row r="74" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
         <v>500</v>
       </c>
@@ -6140,7 +6140,7 @@
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
     </row>
-    <row r="75" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>500</v>
       </c>
@@ -6166,7 +6166,7 @@
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
     </row>
-    <row r="76" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>500</v>
       </c>
@@ -6192,7 +6192,7 @@
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
     </row>
-    <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>500</v>
       </c>
@@ -6220,7 +6220,7 @@
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
     </row>
-    <row r="78" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>542</v>
       </c>
@@ -6248,7 +6248,7 @@
       <c r="K78" s="26"/>
       <c r="L78" s="13"/>
     </row>
-    <row r="79" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>542</v>
       </c>
@@ -6276,7 +6276,7 @@
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
     </row>
-    <row r="80" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
         <v>542</v>
       </c>
@@ -6304,7 +6304,7 @@
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
     </row>
-    <row r="81" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>542</v>
       </c>
@@ -6332,7 +6332,7 @@
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
     </row>
-    <row r="82" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>542</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
     </row>
-    <row r="83" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>542</v>
       </c>
@@ -6388,7 +6388,7 @@
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
     </row>
-    <row r="84" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
         <v>542</v>
       </c>
@@ -6416,7 +6416,7 @@
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
     </row>
-    <row r="85" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>542</v>
       </c>
@@ -6444,7 +6444,7 @@
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
     </row>
-    <row r="86" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
         <v>542</v>
       </c>
@@ -6472,7 +6472,7 @@
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
     </row>
-    <row r="87" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>542</v>
       </c>
@@ -6500,7 +6500,7 @@
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
     </row>
-    <row r="88" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
         <v>542</v>
       </c>
@@ -6528,7 +6528,7 @@
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
     </row>
-    <row r="89" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>542</v>
       </c>
@@ -6556,7 +6556,7 @@
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
     </row>
-    <row r="90" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>542</v>
       </c>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="L90" s="13"/>
     </row>
-    <row r="91" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>542</v>
       </c>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="L91" s="13"/>
     </row>
-    <row r="92" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>542</v>
       </c>
@@ -6646,7 +6646,7 @@
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
     </row>
-    <row r="93" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>74</v>
       </c>
@@ -6674,7 +6674,7 @@
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
     </row>
-    <row r="94" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>74</v>
       </c>
@@ -6702,7 +6702,7 @@
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
     </row>
-    <row r="95" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>74</v>
       </c>
@@ -6730,7 +6730,7 @@
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
     </row>
-    <row r="96" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>74</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
     </row>
-    <row r="97" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
@@ -6786,7 +6786,7 @@
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
     </row>
-    <row r="98" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>74</v>
       </c>
@@ -6814,7 +6814,7 @@
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
     </row>
-    <row r="99" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>74</v>
       </c>
@@ -6842,7 +6842,7 @@
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
     </row>
-    <row r="100" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>74</v>
       </c>
@@ -6870,7 +6870,7 @@
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
     </row>
-    <row r="101" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>74</v>
       </c>
@@ -6898,7 +6898,7 @@
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
     </row>
-    <row r="102" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>74</v>
       </c>
@@ -6926,7 +6926,7 @@
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
     </row>
-    <row r="103" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>74</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
     </row>
-    <row r="104" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>74</v>
       </c>
@@ -6982,7 +6982,7 @@
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
     </row>
-    <row r="105" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>74</v>
       </c>
@@ -7010,7 +7010,7 @@
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
     </row>
-    <row r="106" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>74</v>
       </c>
@@ -7038,7 +7038,7 @@
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
     </row>
-    <row r="107" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>74</v>
       </c>
@@ -7066,7 +7066,7 @@
       <c r="K107" s="13"/>
       <c r="L107" s="13"/>
     </row>
-    <row r="108" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>74</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>74</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>74</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>74</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>74</v>
       </c>
@@ -7236,7 +7236,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>74</v>
       </c>
@@ -7270,7 +7270,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>74</v>
       </c>
@@ -7298,7 +7298,7 @@
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
     </row>
-    <row r="115" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>74</v>
       </c>
@@ -7326,7 +7326,7 @@
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
     </row>
-    <row r="116" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>74</v>
       </c>
@@ -7354,7 +7354,7 @@
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
     </row>
-    <row r="117" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>74</v>
       </c>
@@ -7382,7 +7382,7 @@
       <c r="K117" s="13"/>
       <c r="L117" s="13"/>
     </row>
-    <row r="118" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>74</v>
       </c>
@@ -7410,7 +7410,7 @@
       <c r="K118" s="13"/>
       <c r="L118" s="13"/>
     </row>
-    <row r="119" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>74</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="K119" s="13"/>
       <c r="L119" s="13"/>
     </row>
-    <row r="120" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
         <v>74</v>
       </c>
@@ -7468,7 +7468,7 @@
       <c r="K120" s="13"/>
       <c r="L120" s="13"/>
     </row>
-    <row r="121" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>74</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="K121" s="13"/>
       <c r="L121" s="13"/>
     </row>
-    <row r="122" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
         <v>74</v>
       </c>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L122" s="13"/>
     </row>
-    <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>74</v>
       </c>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L123" s="13"/>
     </row>
-    <row r="124" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>74</v>
       </c>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="L124" s="13"/>
     </row>
-    <row r="125" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>74</v>
       </c>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L125" s="13"/>
     </row>
-    <row r="126" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>74</v>
       </c>
@@ -7646,7 +7646,7 @@
       <c r="K126" s="13"/>
       <c r="L126" s="13"/>
     </row>
-    <row r="127" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>74</v>
       </c>
@@ -7685,20 +7685,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" style="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>76</v>
       </c>
@@ -7727,12 +7727,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>437</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>203</v>
@@ -7741,10 +7741,10 @@
         <v>148</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>437</v>
       </c>
@@ -7763,7 +7763,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>437</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>437</v>
       </c>
@@ -7801,12 +7801,12 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>437</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
@@ -7820,7 +7820,7 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>437</v>
       </c>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>437</v>
       </c>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>437</v>
       </c>
@@ -7883,12 +7883,12 @@
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>437</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
@@ -7902,7 +7902,7 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>441</v>
       </c>
@@ -7921,7 +7921,7 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>441</v>
       </c>
@@ -7940,7 +7940,7 @@
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>441</v>
       </c>
@@ -7959,7 +7959,7 @@
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>441</v>
       </c>
@@ -7976,18 +7976,18 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>441</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>631</v>
+        <v>692</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>148</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -8001,22 +8001,22 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="51.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="8.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="51.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="8.6640625" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>76</v>
       </c>
@@ -8060,7 +8060,7 @@
       <c r="O1" s="30"/>
       <c r="P1" s="30"/>
     </row>
-    <row r="2" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>73</v>
       </c>
@@ -8089,8 +8089,8 @@
       <c r="J2" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="K2" s="66"/>
-      <c r="L2" s="68"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="76"/>
       <c r="M2" s="25" t="s">
         <v>259</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>73</v>
       </c>
@@ -8127,8 +8127,8 @@
       <c r="J3" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K3" s="67"/>
-      <c r="L3" s="69"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="77"/>
       <c r="M3" s="9" t="s">
         <v>259</v>
       </c>
@@ -8136,7 +8136,7 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>73</v>
       </c>
@@ -8165,8 +8165,8 @@
       <c r="J4" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="69"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="77"/>
       <c r="M4" s="9" t="s">
         <v>259</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>73</v>
       </c>
@@ -8201,8 +8201,8 @@
       <c r="J5" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="69"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="77"/>
       <c r="M5" s="9" t="s">
         <v>259</v>
       </c>
@@ -8210,7 +8210,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>73</v>
       </c>
@@ -8239,10 +8239,10 @@
       <c r="J6" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K6" s="70" t="s">
+      <c r="K6" s="75" t="s">
         <v>269</v>
       </c>
-      <c r="L6" s="72"/>
+      <c r="L6" s="80"/>
       <c r="M6" s="9" t="s">
         <v>259</v>
       </c>
@@ -8250,7 +8250,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>73</v>
       </c>
@@ -8279,8 +8279,8 @@
       <c r="J7" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K7" s="67"/>
-      <c r="L7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="81"/>
       <c r="M7" s="9" t="s">
         <v>259</v>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>73</v>
       </c>
@@ -8315,8 +8315,8 @@
       <c r="J8" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K8" s="71"/>
-      <c r="L8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="82"/>
       <c r="M8" s="9" t="s">
         <v>259</v>
       </c>
@@ -8324,7 +8324,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>73</v>
       </c>
@@ -8353,10 +8353,10 @@
       <c r="J9" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K9" s="75" t="s">
+      <c r="K9" s="83" t="s">
         <v>277</v>
       </c>
-      <c r="L9" s="77" t="s">
+      <c r="L9" s="78" t="s">
         <v>278</v>
       </c>
       <c r="M9" s="25" t="s">
@@ -8366,7 +8366,7 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>73</v>
       </c>
@@ -8395,8 +8395,8 @@
       <c r="J10" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K10" s="76"/>
-      <c r="L10" s="69"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="77"/>
       <c r="M10" s="9" t="s">
         <v>259</v>
       </c>
@@ -8404,7 +8404,7 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>73</v>
       </c>
@@ -8433,8 +8433,8 @@
       <c r="J11" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K11" s="76"/>
-      <c r="L11" s="69"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="77"/>
       <c r="M11" s="9" t="s">
         <v>259</v>
       </c>
@@ -8442,7 +8442,7 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
         <v>73</v>
       </c>
@@ -8482,7 +8482,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
         <v>73</v>
       </c>
@@ -8520,7 +8520,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
         <v>73</v>
       </c>
@@ -8562,7 +8562,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
         <v>73</v>
       </c>
@@ -8600,7 +8600,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
         <v>73</v>
       </c>
@@ -8642,7 +8642,7 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>73</v>
       </c>
@@ -8684,7 +8684,7 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
         <v>73</v>
       </c>
@@ -8713,7 +8713,7 @@
       <c r="J18" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K18" s="70"/>
+      <c r="K18" s="75"/>
       <c r="L18" s="23"/>
       <c r="M18" s="9" t="s">
         <v>259</v>
@@ -8722,7 +8722,7 @@
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
     </row>
-    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
         <v>73</v>
       </c>
@@ -8751,7 +8751,7 @@
       <c r="J19" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K19" s="71"/>
+      <c r="K19" s="74"/>
       <c r="L19" s="45"/>
       <c r="M19" s="28" t="s">
         <v>259</v>
@@ -8760,7 +8760,7 @@
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
     </row>
-    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
         <v>73</v>
       </c>
@@ -8789,10 +8789,10 @@
       <c r="J20" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K20" s="70" t="s">
+      <c r="K20" s="75" t="s">
         <v>312</v>
       </c>
-      <c r="L20" s="77" t="s">
+      <c r="L20" s="78" t="s">
         <v>313</v>
       </c>
       <c r="M20" s="9" t="s">
@@ -8802,7 +8802,7 @@
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
     </row>
-    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +8831,8 @@
       <c r="J21" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K21" s="67"/>
-      <c r="L21" s="69"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="77"/>
       <c r="M21" s="9" t="s">
         <v>259</v>
       </c>
@@ -8840,7 +8840,7 @@
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
     </row>
-    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
         <v>73</v>
       </c>
@@ -8867,8 +8867,8 @@
       <c r="J22" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K22" s="67"/>
-      <c r="L22" s="69"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="77"/>
       <c r="M22" s="9" t="s">
         <v>259</v>
       </c>
@@ -8876,7 +8876,7 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
-    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
         <v>73</v>
       </c>
@@ -8905,8 +8905,8 @@
       <c r="J23" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K23" s="67"/>
-      <c r="L23" s="69"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="77"/>
       <c r="M23" s="9" t="s">
         <v>259</v>
       </c>
@@ -8914,7 +8914,7 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
-    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
         <v>73</v>
       </c>
@@ -8943,8 +8943,8 @@
       <c r="J24" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K24" s="67"/>
-      <c r="L24" s="69"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="77"/>
       <c r="M24" s="9" t="s">
         <v>259</v>
       </c>
@@ -8952,7 +8952,7 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
     </row>
-    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>73</v>
       </c>
@@ -8981,10 +8981,10 @@
       <c r="J25" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="K25" s="66" t="s">
+      <c r="K25" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="L25" s="68" t="s">
+      <c r="L25" s="76" t="s">
         <v>320</v>
       </c>
       <c r="M25" s="25" t="s">
@@ -8994,7 +8994,7 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
     </row>
-    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
         <v>73</v>
       </c>
@@ -9023,8 +9023,8 @@
       <c r="J26" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K26" s="67"/>
-      <c r="L26" s="69"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="77"/>
       <c r="M26" s="9" t="s">
         <v>259</v>
       </c>
@@ -9032,7 +9032,7 @@
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
     </row>
-    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
         <v>73</v>
       </c>
@@ -9061,8 +9061,8 @@
       <c r="J27" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K27" s="67"/>
-      <c r="L27" s="69"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="77"/>
       <c r="M27" s="9" t="s">
         <v>259</v>
       </c>
@@ -9070,7 +9070,7 @@
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
     </row>
-    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
         <v>73</v>
       </c>
@@ -9097,8 +9097,8 @@
       <c r="J28" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K28" s="71"/>
-      <c r="L28" s="78"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="79"/>
       <c r="M28" s="28" t="s">
         <v>259</v>
       </c>
@@ -9106,7 +9106,7 @@
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
     </row>
-    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
         <v>73</v>
       </c>
@@ -9135,7 +9135,7 @@
       <c r="J29" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K29" s="70" t="s">
+      <c r="K29" s="75" t="s">
         <v>325</v>
       </c>
       <c r="L29" s="23"/>
@@ -9146,7 +9146,7 @@
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
     </row>
-    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
         <v>73</v>
       </c>
@@ -9175,7 +9175,7 @@
       <c r="J30" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K30" s="67"/>
+      <c r="K30" s="73"/>
       <c r="L30" s="23"/>
       <c r="M30" s="9" t="s">
         <v>259</v>
@@ -9184,7 +9184,7 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
         <v>73</v>
       </c>
@@ -9213,7 +9213,7 @@
       <c r="J31" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K31" s="67"/>
+      <c r="K31" s="73"/>
       <c r="L31" s="23"/>
       <c r="M31" s="9" t="s">
         <v>259</v>
@@ -9222,7 +9222,7 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="s">
         <v>73</v>
       </c>
@@ -9249,7 +9249,7 @@
       <c r="J32" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K32" s="67"/>
+      <c r="K32" s="73"/>
       <c r="L32" s="23"/>
       <c r="M32" s="9" t="s">
         <v>259</v>
@@ -9258,7 +9258,7 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
-    <row r="33" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="s">
         <v>73</v>
       </c>
@@ -9287,7 +9287,7 @@
       <c r="J33" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="K33" s="66" t="s">
+      <c r="K33" s="72" t="s">
         <v>292</v>
       </c>
       <c r="L33" s="44" t="s">
@@ -9300,7 +9300,7 @@
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
     </row>
-    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="24" t="s">
         <v>73</v>
       </c>
@@ -9329,7 +9329,7 @@
       <c r="J34" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K34" s="71"/>
+      <c r="K34" s="74"/>
       <c r="L34" s="45"/>
       <c r="M34" s="28" t="s">
         <v>259</v>
@@ -9338,7 +9338,7 @@
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
     </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="s">
         <v>73</v>
       </c>
@@ -9367,7 +9367,7 @@
       <c r="J35" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K35" s="70" t="s">
+      <c r="K35" s="75" t="s">
         <v>292</v>
       </c>
       <c r="L35" s="23" t="s">
@@ -9380,7 +9380,7 @@
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
     </row>
-    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="s">
         <v>73</v>
       </c>
@@ -9409,7 +9409,7 @@
       <c r="J36" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K36" s="67"/>
+      <c r="K36" s="73"/>
       <c r="L36" s="23"/>
       <c r="M36" s="9" t="s">
         <v>259</v>
@@ -9418,7 +9418,7 @@
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
-    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
         <v>73</v>
       </c>
@@ -9456,7 +9456,7 @@
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
     </row>
-    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
         <v>73</v>
       </c>
@@ -9494,7 +9494,7 @@
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
-    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
         <v>73</v>
       </c>
@@ -9526,7 +9526,7 @@
       <c r="K39" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="L39" s="68"/>
+      <c r="L39" s="76"/>
       <c r="M39" s="25" t="s">
         <v>259</v>
       </c>
@@ -9534,7 +9534,7 @@
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
     </row>
-    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
         <v>73</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>259</v>
       </c>
       <c r="K40" s="36"/>
-      <c r="L40" s="69"/>
+      <c r="L40" s="77"/>
       <c r="M40" s="9" t="s">
         <v>259</v>
       </c>
@@ -9572,7 +9572,7 @@
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
     </row>
-    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
         <v>73</v>
       </c>
@@ -9614,7 +9614,7 @@
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
     </row>
-    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
         <v>73</v>
       </c>
@@ -9643,10 +9643,10 @@
       <c r="J42" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K42" s="70" t="s">
+      <c r="K42" s="75" t="s">
         <v>349</v>
       </c>
-      <c r="L42" s="77" t="s">
+      <c r="L42" s="78" t="s">
         <v>350</v>
       </c>
       <c r="M42" s="25" t="s">
@@ -9656,7 +9656,7 @@
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
     </row>
-    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
         <v>73</v>
       </c>
@@ -9685,8 +9685,8 @@
       <c r="J43" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K43" s="67"/>
-      <c r="L43" s="69"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="77"/>
       <c r="M43" s="9" t="s">
         <v>259</v>
       </c>
@@ -9694,7 +9694,7 @@
       <c r="O43" s="7"/>
       <c r="P43" s="7"/>
     </row>
-    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
         <v>73</v>
       </c>
@@ -9723,8 +9723,8 @@
       <c r="J44" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K44" s="67"/>
-      <c r="L44" s="69"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="77"/>
       <c r="M44" s="9" t="s">
         <v>259</v>
       </c>
@@ -9732,7 +9732,7 @@
       <c r="O44" s="7"/>
       <c r="P44" s="7"/>
     </row>
-    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
         <v>73</v>
       </c>
@@ -9759,8 +9759,8 @@
       <c r="J45" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K45" s="67"/>
-      <c r="L45" s="69"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="77"/>
       <c r="M45" s="9" t="s">
         <v>259</v>
       </c>
@@ -9768,7 +9768,7 @@
       <c r="O45" s="7"/>
       <c r="P45" s="7"/>
     </row>
-    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="s">
         <v>73</v>
       </c>
@@ -9797,8 +9797,8 @@
       <c r="J46" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K46" s="67"/>
-      <c r="L46" s="69"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="77"/>
       <c r="M46" s="9" t="s">
         <v>259</v>
       </c>
@@ -9806,7 +9806,7 @@
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
     </row>
-    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="s">
         <v>73</v>
       </c>
@@ -9835,8 +9835,8 @@
       <c r="J47" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K47" s="67"/>
-      <c r="L47" s="69"/>
+      <c r="K47" s="73"/>
+      <c r="L47" s="77"/>
       <c r="M47" s="9" t="s">
         <v>259</v>
       </c>
@@ -9844,7 +9844,7 @@
       <c r="O47" s="7"/>
       <c r="P47" s="7"/>
     </row>
-    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="s">
         <v>73</v>
       </c>
@@ -9886,7 +9886,7 @@
       <c r="O48" s="7"/>
       <c r="P48" s="7"/>
     </row>
-    <row r="49" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="s">
         <v>73</v>
       </c>
@@ -9924,7 +9924,7 @@
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
     </row>
-    <row r="50" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="s">
         <v>73</v>
       </c>
@@ -9953,7 +9953,7 @@
       <c r="J50" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="K50" s="79" t="s">
+      <c r="K50" s="66" t="s">
         <v>363</v>
       </c>
       <c r="L50" s="44"/>
@@ -9964,7 +9964,7 @@
       <c r="O50" s="7"/>
       <c r="P50" s="7"/>
     </row>
-    <row r="51" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="s">
         <v>73</v>
       </c>
@@ -9993,7 +9993,7 @@
       <c r="J51" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K51" s="76"/>
+      <c r="K51" s="67"/>
       <c r="L51" s="23"/>
       <c r="M51" s="25" t="s">
         <v>259</v>
@@ -10002,7 +10002,7 @@
       <c r="O51" s="7"/>
       <c r="P51" s="7"/>
     </row>
-    <row r="52" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="s">
         <v>73</v>
       </c>
@@ -10031,7 +10031,7 @@
       <c r="J52" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K52" s="76"/>
+      <c r="K52" s="67"/>
       <c r="L52" s="23"/>
       <c r="M52" s="25" t="s">
         <v>259</v>
@@ -10040,7 +10040,7 @@
       <c r="O52" s="7"/>
       <c r="P52" s="7"/>
     </row>
-    <row r="53" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
         <v>73</v>
       </c>
@@ -10069,7 +10069,7 @@
       <c r="J53" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K53" s="76"/>
+      <c r="K53" s="67"/>
       <c r="L53" s="23"/>
       <c r="M53" s="25" t="s">
         <v>259</v>
@@ -10078,7 +10078,7 @@
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
-    <row r="54" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
         <v>73</v>
       </c>
@@ -10105,7 +10105,7 @@
       <c r="J54" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K54" s="80"/>
+      <c r="K54" s="68"/>
       <c r="L54" s="45"/>
       <c r="M54" s="25" t="s">
         <v>259</v>
@@ -10114,7 +10114,7 @@
       <c r="O54" s="7"/>
       <c r="P54" s="7"/>
     </row>
-    <row r="55" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="s">
         <v>73</v>
       </c>
@@ -10156,7 +10156,7 @@
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
     </row>
-    <row r="56" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="s">
         <v>73</v>
       </c>
@@ -10196,7 +10196,7 @@
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
     </row>
-    <row r="57" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="s">
         <v>73</v>
       </c>
@@ -10225,7 +10225,7 @@
       <c r="J57" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K57" s="70" t="s">
+      <c r="K57" s="75" t="s">
         <v>380</v>
       </c>
       <c r="L57" s="23"/>
@@ -10236,7 +10236,7 @@
       <c r="O57" s="7"/>
       <c r="P57" s="7"/>
     </row>
-    <row r="58" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
         <v>73</v>
       </c>
@@ -10265,7 +10265,7 @@
       <c r="J58" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K58" s="67"/>
+      <c r="K58" s="73"/>
       <c r="L58" s="23"/>
       <c r="M58" s="9" t="s">
         <v>259</v>
@@ -10274,7 +10274,7 @@
       <c r="O58" s="7"/>
       <c r="P58" s="7"/>
     </row>
-    <row r="59" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
         <v>73</v>
       </c>
@@ -10301,7 +10301,7 @@
       <c r="J59" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K59" s="67"/>
+      <c r="K59" s="73"/>
       <c r="L59" s="23"/>
       <c r="M59" s="9" t="s">
         <v>259</v>
@@ -10310,7 +10310,7 @@
       <c r="O59" s="7"/>
       <c r="P59" s="7"/>
     </row>
-    <row r="60" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
         <v>73</v>
       </c>
@@ -10339,7 +10339,7 @@
       <c r="J60" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="K60" s="68" t="s">
+      <c r="K60" s="76" t="s">
         <v>385</v>
       </c>
       <c r="L60" s="44"/>
@@ -10350,7 +10350,7 @@
       <c r="O60" s="7"/>
       <c r="P60" s="7"/>
     </row>
-    <row r="61" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
         <v>73</v>
       </c>
@@ -10379,7 +10379,7 @@
       <c r="J61" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="K61" s="69"/>
+      <c r="K61" s="77"/>
       <c r="L61" s="23" t="s">
         <v>387</v>
       </c>
@@ -10390,7 +10390,7 @@
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
     </row>
-    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
         <v>73</v>
       </c>
@@ -10419,7 +10419,7 @@
       <c r="J62" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K62" s="69"/>
+      <c r="K62" s="77"/>
       <c r="L62" s="23" t="s">
         <v>389</v>
       </c>
@@ -10430,7 +10430,7 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
     </row>
-    <row r="63" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
         <v>73</v>
       </c>
@@ -10459,7 +10459,7 @@
       <c r="J63" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="K63" s="70"/>
+      <c r="K63" s="75"/>
       <c r="L63" s="23"/>
       <c r="M63" s="9" t="s">
         <v>259</v>
@@ -10468,7 +10468,7 @@
       <c r="O63" s="7"/>
       <c r="P63" s="7"/>
     </row>
-    <row r="64" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
         <v>73</v>
       </c>
@@ -10497,7 +10497,7 @@
       <c r="J64" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="K64" s="67"/>
+      <c r="K64" s="73"/>
       <c r="L64" s="23"/>
       <c r="M64" s="9" t="s">
         <v>259</v>
@@ -10506,7 +10506,7 @@
       <c r="O64" s="7"/>
       <c r="P64" s="7"/>
     </row>
-    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
         <v>73</v>
       </c>
@@ -10535,7 +10535,7 @@
       <c r="J65" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="K65" s="67"/>
+      <c r="K65" s="73"/>
       <c r="L65" s="23" t="s">
         <v>389</v>
       </c>
@@ -10546,7 +10546,7 @@
       <c r="O65" s="7"/>
       <c r="P65" s="7"/>
     </row>
-    <row r="66" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="s">
         <v>73</v>
       </c>
@@ -10573,7 +10573,7 @@
       <c r="J66" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="K66" s="67"/>
+      <c r="K66" s="73"/>
       <c r="L66" s="13"/>
       <c r="M66" s="35" t="s">
         <v>259</v>
@@ -10582,7 +10582,7 @@
       <c r="O66" s="7"/>
       <c r="P66" s="7"/>
     </row>
-    <row r="67" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
         <v>73</v>
       </c>
@@ -10620,7 +10620,7 @@
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
     </row>
-    <row r="68" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="s">
         <v>73</v>
       </c>
@@ -10658,7 +10658,7 @@
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
     </row>
-    <row r="69" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="s">
         <v>73</v>
       </c>
@@ -10687,7 +10687,7 @@
       <c r="J69" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K69" s="70" t="s">
+      <c r="K69" s="75" t="s">
         <v>292</v>
       </c>
       <c r="L69" s="23" t="s">
@@ -10700,7 +10700,7 @@
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
     </row>
-    <row r="70" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
         <v>73</v>
       </c>
@@ -10729,7 +10729,7 @@
       <c r="J70" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K70" s="67"/>
+      <c r="K70" s="73"/>
       <c r="L70" s="23"/>
       <c r="M70" s="9" t="s">
         <v>259</v>
@@ -10738,7 +10738,7 @@
       <c r="O70" s="7"/>
       <c r="P70" s="7"/>
     </row>
-    <row r="71" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="s">
         <v>73</v>
       </c>
@@ -10778,7 +10778,7 @@
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
     </row>
-    <row r="72" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="s">
         <v>73</v>
       </c>
@@ -10807,7 +10807,7 @@
       <c r="J72" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K72" s="70"/>
+      <c r="K72" s="75"/>
       <c r="L72" s="23"/>
       <c r="M72" s="9" t="s">
         <v>259</v>
@@ -10816,7 +10816,7 @@
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
     </row>
-    <row r="73" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="s">
         <v>73</v>
       </c>
@@ -10843,7 +10843,7 @@
       <c r="J73" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K73" s="67"/>
+      <c r="K73" s="73"/>
       <c r="L73" s="23"/>
       <c r="M73" s="9" t="s">
         <v>259</v>
@@ -10852,7 +10852,7 @@
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
     </row>
-    <row r="74" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
         <v>73</v>
       </c>
@@ -10879,7 +10879,7 @@
       <c r="J74" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K74" s="67"/>
+      <c r="K74" s="73"/>
       <c r="L74" s="23"/>
       <c r="M74" s="9" t="s">
         <v>259</v>
@@ -10888,7 +10888,7 @@
       <c r="O74" s="7"/>
       <c r="P74" s="7"/>
     </row>
-    <row r="75" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="24" t="s">
         <v>73</v>
       </c>
@@ -10913,7 +10913,7 @@
       <c r="J75" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K75" s="71"/>
+      <c r="K75" s="74"/>
       <c r="L75" s="45"/>
       <c r="M75" s="9" t="s">
         <v>259</v>
@@ -10922,7 +10922,7 @@
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
     </row>
-    <row r="76" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
         <v>73</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
     </row>
-    <row r="77" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>73</v>
       </c>
@@ -10991,10 +10991,10 @@
       <c r="J77" s="34" t="s">
         <v>259</v>
       </c>
-      <c r="K77" s="79" t="s">
+      <c r="K77" s="66" t="s">
         <v>412</v>
       </c>
-      <c r="L77" s="66" t="s">
+      <c r="L77" s="72" t="s">
         <v>413</v>
       </c>
       <c r="M77" s="25" t="s">
@@ -11004,7 +11004,7 @@
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
     </row>
-    <row r="78" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
         <v>73</v>
       </c>
@@ -11035,8 +11035,8 @@
       <c r="J78" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K78" s="80"/>
-      <c r="L78" s="82"/>
+      <c r="K78" s="68"/>
+      <c r="L78" s="70"/>
       <c r="M78" s="35" t="s">
         <v>259</v>
       </c>
@@ -11044,7 +11044,7 @@
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
     </row>
-    <row r="79" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
         <v>73</v>
       </c>
@@ -11076,7 +11076,7 @@
       <c r="K79" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="L79" s="82"/>
+      <c r="L79" s="70"/>
       <c r="M79" s="35" t="s">
         <v>259</v>
       </c>
@@ -11084,7 +11084,7 @@
       <c r="O79" s="7"/>
       <c r="P79" s="7"/>
     </row>
-    <row r="80" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="s">
         <v>73</v>
       </c>
@@ -11116,7 +11116,7 @@
       <c r="K80" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="L80" s="71"/>
+      <c r="L80" s="74"/>
       <c r="M80" s="9" t="s">
         <v>259</v>
       </c>
@@ -11124,7 +11124,7 @@
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
     </row>
-    <row r="81" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="s">
         <v>73</v>
       </c>
@@ -11153,7 +11153,7 @@
       <c r="J81" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K81" s="70" t="s">
+      <c r="K81" s="75" t="s">
         <v>292</v>
       </c>
       <c r="L81" s="23" t="s">
@@ -11166,7 +11166,7 @@
       <c r="O81" s="7"/>
       <c r="P81" s="7"/>
     </row>
-    <row r="82" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="s">
         <v>73</v>
       </c>
@@ -11195,7 +11195,7 @@
       <c r="J82" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K82" s="67"/>
+      <c r="K82" s="73"/>
       <c r="L82" s="23"/>
       <c r="M82" s="9" t="s">
         <v>259</v>
@@ -11204,7 +11204,7 @@
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
     </row>
-    <row r="83" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="s">
         <v>73</v>
       </c>
@@ -11246,7 +11246,7 @@
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
     </row>
-    <row r="84" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="s">
         <v>73</v>
       </c>
@@ -11288,7 +11288,7 @@
       <c r="O84" s="7"/>
       <c r="P84" s="7"/>
     </row>
-    <row r="85" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="s">
         <v>73</v>
       </c>
@@ -11317,7 +11317,7 @@
       <c r="J85" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K85" s="70" t="s">
+      <c r="K85" s="75" t="s">
         <v>426</v>
       </c>
       <c r="L85" s="23"/>
@@ -11328,7 +11328,7 @@
       <c r="O85" s="7"/>
       <c r="P85" s="7"/>
     </row>
-    <row r="86" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="s">
         <v>73</v>
       </c>
@@ -11357,7 +11357,7 @@
       <c r="J86" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K86" s="67"/>
+      <c r="K86" s="73"/>
       <c r="L86" s="23"/>
       <c r="M86" s="9" t="s">
         <v>259</v>
@@ -11366,7 +11366,7 @@
       <c r="O86" s="7"/>
       <c r="P86" s="7"/>
     </row>
-    <row r="87" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
         <v>73</v>
       </c>
@@ -11395,7 +11395,7 @@
       <c r="J87" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K87" s="67"/>
+      <c r="K87" s="73"/>
       <c r="L87" s="23"/>
       <c r="M87" s="9" t="s">
         <v>259</v>
@@ -11404,7 +11404,7 @@
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
     </row>
-    <row r="88" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="s">
         <v>73</v>
       </c>
@@ -11431,7 +11431,7 @@
       <c r="J88" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K88" s="67"/>
+      <c r="K88" s="73"/>
       <c r="L88" s="23"/>
       <c r="M88" s="9" t="s">
         <v>259</v>
@@ -11440,7 +11440,7 @@
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
     </row>
-    <row r="89" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
         <v>73</v>
       </c>
@@ -11469,7 +11469,7 @@
       <c r="J89" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K89" s="67"/>
+      <c r="K89" s="73"/>
       <c r="L89" s="23"/>
       <c r="M89" s="9" t="s">
         <v>259</v>
@@ -11478,7 +11478,7 @@
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
     </row>
-    <row r="90" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="s">
         <v>73</v>
       </c>
@@ -11507,7 +11507,7 @@
       <c r="J90" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K90" s="67"/>
+      <c r="K90" s="73"/>
       <c r="L90" s="23"/>
       <c r="M90" s="9" t="s">
         <v>259</v>
@@ -11516,7 +11516,7 @@
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
     </row>
-    <row r="91" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="s">
         <v>73</v>
       </c>
@@ -11545,10 +11545,10 @@
       <c r="J91" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K91" s="79" t="s">
+      <c r="K91" s="66" t="s">
         <v>432</v>
       </c>
-      <c r="L91" s="81" t="s">
+      <c r="L91" s="69" t="s">
         <v>433</v>
       </c>
       <c r="M91" s="25" t="s">
@@ -11558,7 +11558,7 @@
       <c r="O91" s="7"/>
       <c r="P91" s="7"/>
     </row>
-    <row r="92" spans="1:16" ht="72.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" ht="72.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="s">
         <v>73</v>
       </c>
@@ -11587,8 +11587,8 @@
       <c r="J92" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="K92" s="76"/>
-      <c r="L92" s="82"/>
+      <c r="K92" s="67"/>
+      <c r="L92" s="70"/>
       <c r="M92" s="9" t="s">
         <v>259</v>
       </c>
@@ -11596,7 +11596,7 @@
       <c r="O92" s="7"/>
       <c r="P92" s="7"/>
     </row>
-    <row r="93" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
         <v>73</v>
       </c>
@@ -11625,8 +11625,8 @@
       <c r="J93" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="K93" s="76"/>
-      <c r="L93" s="82"/>
+      <c r="K93" s="67"/>
+      <c r="L93" s="70"/>
       <c r="M93" s="9" t="s">
         <v>259</v>
       </c>
@@ -11634,7 +11634,7 @@
       <c r="O93" s="7"/>
       <c r="P93" s="7"/>
     </row>
-    <row r="94" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="s">
         <v>73</v>
       </c>
@@ -11661,8 +11661,8 @@
       <c r="J94" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K94" s="80"/>
-      <c r="L94" s="83"/>
+      <c r="K94" s="68"/>
+      <c r="L94" s="71"/>
       <c r="M94" s="9" t="s">
         <v>259</v>
       </c>
@@ -11670,7 +11670,7 @@
       <c r="O94" s="7"/>
       <c r="P94" s="7"/>
     </row>
-    <row r="95" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="s">
         <v>73</v>
       </c>
@@ -11699,7 +11699,7 @@
       <c r="J95" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K95" s="66"/>
+      <c r="K95" s="72"/>
       <c r="L95" s="23"/>
       <c r="M95" s="25" t="s">
         <v>259</v>
@@ -11708,7 +11708,7 @@
       <c r="O95" s="7"/>
       <c r="P95" s="7"/>
     </row>
-    <row r="96" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
         <v>73</v>
       </c>
@@ -11737,7 +11737,7 @@
       <c r="J96" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K96" s="67"/>
+      <c r="K96" s="73"/>
       <c r="L96" s="23"/>
       <c r="M96" s="25" t="s">
         <v>259</v>
@@ -11746,7 +11746,7 @@
       <c r="O96" s="7"/>
       <c r="P96" s="7"/>
     </row>
-    <row r="97" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="s">
         <v>73</v>
       </c>
@@ -11775,7 +11775,7 @@
       <c r="J97" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K97" s="67"/>
+      <c r="K97" s="73"/>
       <c r="L97" s="23"/>
       <c r="M97" s="25" t="s">
         <v>259</v>
@@ -11784,7 +11784,7 @@
       <c r="O97" s="7"/>
       <c r="P97" s="7"/>
     </row>
-    <row r="98" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="24" t="s">
         <v>73</v>
       </c>
@@ -11813,7 +11813,7 @@
       <c r="J98" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="K98" s="67"/>
+      <c r="K98" s="73"/>
       <c r="L98" s="23"/>
       <c r="M98" s="25" t="s">
         <v>259</v>
@@ -11822,7 +11822,7 @@
       <c r="O98" s="7"/>
       <c r="P98" s="7"/>
     </row>
-    <row r="99" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
         <v>73</v>
       </c>
@@ -11849,7 +11849,7 @@
       <c r="J99" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="K99" s="71"/>
+      <c r="K99" s="74"/>
       <c r="L99" s="38"/>
       <c r="M99" s="40" t="s">
         <v>259</v>
@@ -11858,7 +11858,7 @@
       <c r="O99" s="7"/>
       <c r="P99" s="7"/>
     </row>
-    <row r="100" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24"/>
@@ -11878,6 +11878,28 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="K63:K66"/>
+    <mergeCell ref="K69:K70"/>
     <mergeCell ref="K91:K94"/>
     <mergeCell ref="L91:L94"/>
     <mergeCell ref="K95:K99"/>
@@ -11886,28 +11908,6 @@
     <mergeCell ref="L77:L80"/>
     <mergeCell ref="K81:K82"/>
     <mergeCell ref="K85:K90"/>
-    <mergeCell ref="K50:K54"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="K63:K66"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="K20:K24"/>
-    <mergeCell ref="L20:L24"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11919,13 +11919,13 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>247</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>248</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>249</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
@@ -11976,14 +11976,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>76</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>241</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>241</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>241</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>241</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>241</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>241</v>
       </c>
@@ -12071,29 +12071,29 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:W73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="41.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>76</v>
       </c>
@@ -12140,7 +12140,7 @@
       <c r="V1" s="22"/>
       <c r="W1" s="22"/>
     </row>
-    <row r="2" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>182</v>
       </c>
@@ -12177,7 +12177,7 @@
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
     </row>
-    <row r="3" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>182</v>
       </c>
@@ -12214,7 +12214,7 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
     </row>
-    <row r="4" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>182</v>
       </c>
@@ -12253,7 +12253,7 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
     </row>
-    <row r="5" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>182</v>
       </c>
@@ -12286,7 +12286,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
     </row>
-    <row r="6" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>182</v>
       </c>
@@ -12321,7 +12321,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
     </row>
-    <row r="7" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>182</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="V7" s="22"/>
       <c r="W7" s="22"/>
     </row>
-    <row r="8" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>182</v>
       </c>
@@ -12393,7 +12393,7 @@
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
     </row>
-    <row r="9" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>182</v>
       </c>
@@ -12432,7 +12432,7 @@
       <c r="V9" s="22"/>
       <c r="W9" s="22"/>
     </row>
-    <row r="10" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>182</v>
       </c>
@@ -12467,7 +12467,7 @@
       <c r="V10" s="22"/>
       <c r="W10" s="22"/>
     </row>
-    <row r="11" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>182</v>
       </c>
@@ -12506,7 +12506,7 @@
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
     </row>
-    <row r="12" spans="1:23" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>182</v>
       </c>
@@ -12543,7 +12543,7 @@
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
     </row>
-    <row r="13" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
         <v>209</v>
       </c>
@@ -12582,7 +12582,7 @@
       <c r="V13" s="22"/>
       <c r="W13" s="22"/>
     </row>
-    <row r="14" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>209</v>
       </c>
@@ -12615,7 +12615,7 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
     </row>
-    <row r="15" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>209</v>
       </c>
@@ -12652,7 +12652,7 @@
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
     </row>
-    <row r="16" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>209</v>
       </c>
@@ -12689,7 +12689,7 @@
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
     </row>
-    <row r="17" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>209</v>
       </c>
@@ -12728,7 +12728,7 @@
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
     </row>
-    <row r="18" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>209</v>
       </c>
@@ -12767,7 +12767,7 @@
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
     </row>
-    <row r="19" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>209</v>
       </c>
@@ -12804,7 +12804,7 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
     </row>
-    <row r="20" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>209</v>
       </c>
@@ -12843,7 +12843,7 @@
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
     </row>
-    <row r="21" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>209</v>
       </c>
@@ -12880,7 +12880,7 @@
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
     </row>
-    <row r="22" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>209</v>
       </c>
@@ -12919,7 +12919,7 @@
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
     </row>
-    <row r="23" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
         <v>223</v>
       </c>
@@ -12950,7 +12950,7 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
         <v>147</v>
       </c>
@@ -12993,7 +12993,7 @@
       <c r="V24" s="24"/>
       <c r="W24" s="24"/>
     </row>
-    <row r="25" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>147</v>
       </c>
@@ -13034,7 +13034,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>147</v>
       </c>
@@ -13073,7 +13073,7 @@
       <c r="V26" s="8"/>
       <c r="W26" s="12"/>
     </row>
-    <row r="27" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>147</v>
       </c>
@@ -13110,7 +13110,7 @@
       <c r="V27" s="8"/>
       <c r="W27" s="12"/>
     </row>
-    <row r="28" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>147</v>
       </c>
@@ -13151,7 +13151,7 @@
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
     </row>
-    <row r="29" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>147</v>
       </c>
@@ -13190,7 +13190,7 @@
       <c r="V29" s="8"/>
       <c r="W29" s="12"/>
     </row>
-    <row r="30" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>147</v>
       </c>
@@ -13227,7 +13227,7 @@
       <c r="V30" s="8"/>
       <c r="W30" s="12"/>
     </row>
-    <row r="31" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>147</v>
       </c>
@@ -13266,7 +13266,7 @@
       <c r="V31" s="8"/>
       <c r="W31" s="12"/>
     </row>
-    <row r="32" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>147</v>
       </c>
@@ -13303,7 +13303,7 @@
       <c r="V32" s="8"/>
       <c r="W32" s="12"/>
     </row>
-    <row r="33" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>147</v>
       </c>
@@ -13344,7 +13344,7 @@
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
     </row>
-    <row r="34" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>147</v>
       </c>
@@ -13383,7 +13383,7 @@
       <c r="V34" s="8"/>
       <c r="W34" s="12"/>
     </row>
-    <row r="35" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>147</v>
       </c>
@@ -13420,7 +13420,7 @@
       <c r="V35" s="8"/>
       <c r="W35" s="12"/>
     </row>
-    <row r="36" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>147</v>
       </c>
@@ -13459,7 +13459,7 @@
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
     </row>
-    <row r="37" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>147</v>
       </c>
@@ -13496,7 +13496,7 @@
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
     </row>
-    <row r="38" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
         <v>229</v>
       </c>
@@ -13537,7 +13537,7 @@
       <c r="V38" s="24"/>
       <c r="W38" s="24"/>
     </row>
-    <row r="39" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>229</v>
       </c>
@@ -13576,7 +13576,7 @@
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
     </row>
-    <row r="40" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>229</v>
       </c>
@@ -13613,7 +13613,7 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
     </row>
-    <row r="41" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>229</v>
       </c>
@@ -13648,7 +13648,7 @@
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
     </row>
-    <row r="42" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>229</v>
       </c>
@@ -13687,7 +13687,7 @@
       <c r="V42" s="8"/>
       <c r="W42" s="12"/>
     </row>
-    <row r="43" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>229</v>
       </c>
@@ -13726,7 +13726,7 @@
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
     </row>
-    <row r="44" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>229</v>
       </c>
@@ -13765,7 +13765,7 @@
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
     </row>
-    <row r="45" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>229</v>
       </c>
@@ -13806,7 +13806,7 @@
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
     </row>
-    <row r="46" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>229</v>
       </c>
@@ -13845,7 +13845,7 @@
       <c r="V46" s="8"/>
       <c r="W46" s="12"/>
     </row>
-    <row r="47" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>229</v>
       </c>
@@ -13884,7 +13884,7 @@
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
     </row>
-    <row r="48" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>229</v>
       </c>
@@ -13921,7 +13921,7 @@
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
     </row>
-    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>229</v>
       </c>
@@ -13956,7 +13956,7 @@
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
     </row>
-    <row r="50" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>229</v>
       </c>
@@ -13995,7 +13995,7 @@
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
     </row>
-    <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>229</v>
       </c>
@@ -14032,7 +14032,7 @@
       <c r="V51" s="8"/>
       <c r="W51" s="8"/>
     </row>
-    <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>229</v>
       </c>
@@ -14067,7 +14067,7 @@
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
     </row>
-    <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>229</v>
       </c>
@@ -14106,7 +14106,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
     </row>
-    <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>229</v>
       </c>
@@ -14147,7 +14147,7 @@
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
     </row>
-    <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>229</v>
       </c>
@@ -14182,7 +14182,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
     </row>
-    <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>229</v>
       </c>
@@ -14219,7 +14219,7 @@
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
     </row>
-    <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>229</v>
       </c>
@@ -14258,7 +14258,7 @@
       <c r="V57" s="8"/>
       <c r="W57" s="12"/>
     </row>
-    <row r="58" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>229</v>
       </c>
@@ -14293,7 +14293,7 @@
       <c r="V58" s="13"/>
       <c r="W58" s="13"/>
     </row>
-    <row r="59" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>229</v>
       </c>
@@ -14326,7 +14326,7 @@
       <c r="V59" s="13"/>
       <c r="W59" s="13"/>
     </row>
-    <row r="60" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>238</v>
       </c>
@@ -14359,7 +14359,7 @@
       <c r="V60" s="13"/>
       <c r="W60" s="13"/>
     </row>
-    <row r="61" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>238</v>
       </c>
@@ -14392,7 +14392,7 @@
       <c r="V61" s="13"/>
       <c r="W61" s="13"/>
     </row>
-    <row r="62" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>238</v>
       </c>
@@ -14425,7 +14425,7 @@
       <c r="V62" s="13"/>
       <c r="W62" s="13"/>
     </row>
-    <row r="63" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>238</v>
       </c>
@@ -14458,7 +14458,7 @@
       <c r="V63" s="13"/>
       <c r="W63" s="13"/>
     </row>
-    <row r="64" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>238</v>
       </c>
@@ -14491,7 +14491,7 @@
       <c r="V64" s="13"/>
       <c r="W64" s="13"/>
     </row>
-    <row r="65" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>238</v>
       </c>
@@ -14524,7 +14524,7 @@
       <c r="V65" s="13"/>
       <c r="W65" s="13"/>
     </row>
-    <row r="66" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>238</v>
       </c>
@@ -14557,7 +14557,7 @@
       <c r="V66" s="13"/>
       <c r="W66" s="13"/>
     </row>
-    <row r="67" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>238</v>
       </c>
@@ -14590,7 +14590,7 @@
       <c r="V67" s="13"/>
       <c r="W67" s="13"/>
     </row>
-    <row r="68" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>238</v>
       </c>
@@ -14623,7 +14623,7 @@
       <c r="V68" s="13"/>
       <c r="W68" s="13"/>
     </row>
-    <row r="69" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>238</v>
       </c>
@@ -14656,7 +14656,7 @@
       <c r="V69" s="13"/>
       <c r="W69" s="13"/>
     </row>
-    <row r="70" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>238</v>
       </c>
@@ -14689,7 +14689,7 @@
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
     </row>
-    <row r="71" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>238</v>
       </c>
@@ -14722,7 +14722,7 @@
       <c r="V71" s="13"/>
       <c r="W71" s="13"/>
     </row>
-    <row r="72" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>238</v>
       </c>
@@ -14755,7 +14755,7 @@
       <c r="V72" s="13"/>
       <c r="W72" s="13"/>
     </row>
-    <row r="73" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>238</v>
       </c>
@@ -14799,15 +14799,15 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="100.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="100.5546875" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>150</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>154</v>
       </c>
@@ -14835,7 +14835,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>157</v>
       </c>
@@ -14849,7 +14849,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>157</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>159</v>
       </c>
@@ -14877,7 +14877,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>155</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>84</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>161</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>84</v>
       </c>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>165</v>
       </c>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>165</v>
       </c>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>88</v>
       </c>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>84</v>
       </c>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>88</v>
       </c>
@@ -14991,7 +14991,7 @@
       </c>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>162</v>
       </c>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>84</v>
       </c>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>84</v>
       </c>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>171</v>
       </c>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>162</v>
       </c>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>162</v>
       </c>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>162</v>
       </c>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="D21" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>84</v>
       </c>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="D22" s="7"/>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>177</v>
       </c>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>84</v>
       </c>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="D24" s="7"/>
     </row>
-    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>84</v>
       </c>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>88</v>
       </c>

--- a/Meta/Analytes3.xlsx
+++ b/Meta/Analytes3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/vitense_kelsey_epa_gov/Documents/GL_Data/Meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F46325-E4D9-430E-B5AC-CD143EC772DC}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAF63563-9F10-47A8-8CF6-A13C21A25AE4}"/>
   <bookViews>
-    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="691">
   <si>
     <t>ANALYTE</t>
   </si>
@@ -786,9 +786,6 @@
   </si>
   <si>
     <t>cpar</t>
-  </si>
-  <si>
-    <t>OldName</t>
   </si>
   <si>
     <t>Dissolved Reactive Silica</t>
@@ -2608,11 +2605,41 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2620,10 +2647,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2637,36 +2664,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2978,7 +2975,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2986,12 +2983,12 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2999,7 +2996,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3007,10 +3004,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="64" t="s">
+        <v>633</v>
+      </c>
+      <c r="B8" t="s">
         <v>634</v>
-      </c>
-      <c r="B8" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3018,71 +3015,71 @@
         <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="64" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
+        <v>640</v>
+      </c>
+      <c r="B12" t="s">
         <v>641</v>
-      </c>
-      <c r="B12" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="64" t="s">
+        <v>642</v>
+      </c>
+      <c r="B13" t="s">
         <v>643</v>
-      </c>
-      <c r="B13" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
+        <v>644</v>
+      </c>
+      <c r="B16" t="s">
         <v>645</v>
-      </c>
-      <c r="B16" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
+        <v>646</v>
+      </c>
+      <c r="B17" t="s">
         <v>647</v>
-      </c>
-      <c r="B17" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3090,119 +3087,119 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B19" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
+        <v>650</v>
+      </c>
+      <c r="B20" t="s">
         <v>651</v>
-      </c>
-      <c r="B20" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
+        <v>652</v>
+      </c>
+      <c r="B22" t="s">
         <v>653</v>
-      </c>
-      <c r="B22" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="64" t="s">
+        <v>654</v>
+      </c>
+      <c r="B23" t="s">
         <v>655</v>
-      </c>
-      <c r="B23" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
+        <v>656</v>
+      </c>
+      <c r="B24" t="s">
         <v>657</v>
-      </c>
-      <c r="B24" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
+        <v>658</v>
+      </c>
+      <c r="B25" t="s">
         <v>659</v>
-      </c>
-      <c r="B25" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="64" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B26" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="64" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B27" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="64" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B28" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="B29" t="s">
         <v>663</v>
-      </c>
-      <c r="B29" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="64" t="s">
+        <v>664</v>
+      </c>
+      <c r="B30" t="s">
         <v>665</v>
-      </c>
-      <c r="B30" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="64" t="s">
+        <v>666</v>
+      </c>
+      <c r="B31" t="s">
         <v>667</v>
-      </c>
-      <c r="B31" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="64" t="s">
+        <v>668</v>
+      </c>
+      <c r="B32" t="s">
         <v>669</v>
-      </c>
-      <c r="B32" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3210,7 +3207,7 @@
         <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -3218,7 +3215,7 @@
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3226,23 +3223,23 @@
         <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="64" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B36" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="64" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B37" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -3276,21 +3273,21 @@
         <v>5</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>568</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>239</v>
@@ -3299,7 +3296,7 @@
         <v>159</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>30</v>
@@ -3310,13 +3307,13 @@
         <v>223</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>20</v>
@@ -3324,16 +3321,16 @@
     </row>
     <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
@@ -3341,16 +3338,16 @@
     </row>
     <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>30</v>
@@ -3358,16 +3355,16 @@
     </row>
     <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>30</v>
@@ -3375,16 +3372,16 @@
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>20</v>
@@ -3395,13 +3392,13 @@
         <v>57</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>30</v>
@@ -3412,13 +3409,13 @@
         <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
@@ -3429,13 +3426,13 @@
         <v>61</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>162</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>114</v>
@@ -3443,16 +3440,16 @@
     </row>
     <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>30</v>
@@ -3460,16 +3457,16 @@
     </row>
     <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>30</v>
@@ -3477,16 +3474,16 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>30</v>
@@ -3494,16 +3491,16 @@
     </row>
     <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>20</v>
@@ -3511,16 +3508,16 @@
     </row>
     <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>20</v>
@@ -3528,16 +3525,16 @@
     </row>
     <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>120</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>120</v>
@@ -3545,16 +3542,16 @@
     </row>
     <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>20</v>
@@ -3565,13 +3562,13 @@
         <v>37</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>20</v>
@@ -3582,13 +3579,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>20</v>
@@ -3596,19 +3593,19 @@
     </row>
     <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3616,13 +3613,13 @@
         <v>44</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>20</v>
@@ -3633,13 +3630,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>30</v>
@@ -3647,16 +3644,16 @@
     </row>
     <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>30</v>
@@ -3664,19 +3661,19 @@
     </row>
     <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3684,13 +3681,13 @@
         <v>149</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>20</v>
@@ -3701,13 +3698,13 @@
         <v>111</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>30</v>
@@ -3721,13 +3718,13 @@
         <v>52</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3735,13 +3732,13 @@
         <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>20</v>
@@ -3752,13 +3749,13 @@
         <v>36</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>20</v>
@@ -3766,19 +3763,19 @@
     </row>
     <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3786,13 +3783,13 @@
         <v>47</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>20</v>
@@ -3803,13 +3800,13 @@
         <v>119</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>120</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>120</v>
@@ -3817,16 +3814,16 @@
     </row>
     <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>30</v>
@@ -3834,16 +3831,16 @@
     </row>
     <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>30</v>
@@ -3854,13 +3851,13 @@
         <v>195</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>194</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>194</v>
@@ -3868,16 +3865,16 @@
     </row>
     <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>20</v>
@@ -3888,13 +3885,13 @@
         <v>232</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>30</v>
@@ -3902,16 +3899,16 @@
     </row>
     <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>30</v>
@@ -3919,16 +3916,16 @@
     </row>
     <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>30</v>
@@ -3939,13 +3936,13 @@
         <v>63</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>30</v>
@@ -3956,13 +3953,13 @@
         <v>27</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>20</v>
@@ -3979,7 +3976,7 @@
         <v>202</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>202</v>
@@ -3987,16 +3984,16 @@
     </row>
     <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>154</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>154</v>
@@ -4004,16 +4001,16 @@
     </row>
     <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>155</v>
@@ -4054,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -4094,7 +4091,7 @@
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F2" s="19">
         <v>2015</v>
@@ -4106,13 +4103,13 @@
         <v>148</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J2" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>442</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>443</v>
       </c>
       <c r="L2" s="13"/>
     </row>
@@ -4126,7 +4123,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F3" s="19">
         <v>2015</v>
@@ -4138,13 +4135,13 @@
         <v>148</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J3" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>445</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>446</v>
       </c>
       <c r="L3" s="13"/>
     </row>
@@ -4158,19 +4155,19 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F4" s="19">
         <v>2015</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -4186,7 +4183,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F5" s="19">
         <v>2015</v>
@@ -4198,7 +4195,7 @@
         <v>21</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -4214,7 +4211,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F6" s="19">
         <v>2015</v>
@@ -4226,7 +4223,7 @@
         <v>57</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -4242,7 +4239,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F7" s="19">
         <v>2015</v>
@@ -4254,10 +4251,10 @@
         <v>119</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
@@ -4272,7 +4269,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F8" s="19">
         <v>2015</v>
@@ -4284,10 +4281,10 @@
         <v>148</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
@@ -4302,7 +4299,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F9" s="19">
         <v>2015</v>
@@ -4314,10 +4311,10 @@
         <v>148</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
@@ -4332,7 +4329,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F10" s="19">
         <v>2015</v>
@@ -4344,7 +4341,7 @@
         <v>111</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -4360,7 +4357,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F11" s="19">
         <v>2015</v>
@@ -4370,11 +4367,11 @@
         <v>148</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J11" s="13"/>
       <c r="K11" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L11" s="13"/>
     </row>
@@ -4383,12 +4380,12 @@
         <v>75</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F12" s="19">
         <v>2015</v>
@@ -4398,13 +4395,13 @@
         <v>148</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L12" s="13"/>
     </row>
@@ -4413,12 +4410,12 @@
         <v>75</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F13" s="19">
         <v>2015</v>
@@ -4428,13 +4425,13 @@
         <v>148</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L13" s="13"/>
     </row>
@@ -4443,12 +4440,12 @@
         <v>75</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F14" s="19">
         <v>2015</v>
@@ -4458,13 +4455,13 @@
         <v>148</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L14" s="13"/>
     </row>
@@ -4478,7 +4475,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F15" s="19">
         <v>2015</v>
@@ -4487,10 +4484,10 @@
         <v>159</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -4506,7 +4503,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F16" s="19">
         <v>2015</v>
@@ -4515,10 +4512,10 @@
         <v>159</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
@@ -4534,7 +4531,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F17" s="19">
         <v>2015</v>
@@ -4543,10 +4540,10 @@
         <v>159</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
@@ -4562,7 +4559,7 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F18" s="19">
         <v>2015</v>
@@ -4574,7 +4571,7 @@
         <v>223</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -4590,7 +4587,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F19" s="19">
         <v>2015</v>
@@ -4602,7 +4599,7 @@
         <v>149</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
@@ -4618,7 +4615,7 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F20" s="19">
         <v>2015</v>
@@ -4630,13 +4627,13 @@
         <v>148</v>
       </c>
       <c r="I20" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="J20" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="K20" s="13" t="s">
         <v>476</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>477</v>
       </c>
       <c r="L20" s="13"/>
     </row>
@@ -4650,7 +4647,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F21" s="19">
         <v>2015</v>
@@ -4659,16 +4656,16 @@
         <v>160</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J21" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>479</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>480</v>
       </c>
       <c r="L21" s="13"/>
     </row>
@@ -4682,7 +4679,7 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F22" s="19">
         <v>2015</v>
@@ -4694,7 +4691,7 @@
         <v>52</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
@@ -4710,7 +4707,7 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F23" s="19">
         <v>2015</v>
@@ -4722,13 +4719,13 @@
         <v>148</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J23" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="K23" s="13" t="s">
         <v>483</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>484</v>
       </c>
       <c r="L23" s="13"/>
     </row>
@@ -4742,7 +4739,7 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="13" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F24" s="19">
         <v>2015</v>
@@ -4754,10 +4751,10 @@
         <v>35</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
@@ -4772,7 +4769,7 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F25" s="19">
         <v>2015</v>
@@ -4784,7 +4781,7 @@
         <v>36</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
@@ -4800,7 +4797,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F26" s="19">
         <v>2015</v>
@@ -4812,7 +4809,7 @@
         <v>63</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -4828,7 +4825,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F27" s="19">
         <v>2015</v>
@@ -4840,10 +4837,10 @@
         <v>61</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
@@ -4858,7 +4855,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F28" s="19">
         <v>2015</v>
@@ -4870,7 +4867,7 @@
         <v>27</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
@@ -4886,7 +4883,7 @@
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F29" s="19">
         <v>2015</v>
@@ -4898,7 +4895,7 @@
         <v>203</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
@@ -4914,7 +4911,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F30" s="19">
         <v>2015</v>
@@ -4926,13 +4923,13 @@
         <v>44</v>
       </c>
       <c r="I30" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="J30" s="13" t="s">
         <v>494</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="K30" s="13" t="s">
         <v>495</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>496</v>
       </c>
       <c r="L30" s="13"/>
     </row>
@@ -4946,7 +4943,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F31" s="19">
         <v>2015</v>
@@ -4958,19 +4955,19 @@
         <v>47</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L31" s="13"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>121</v>
@@ -4991,16 +4988,16 @@
         <v>158</v>
       </c>
       <c r="J32" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="K32" s="25" t="s">
         <v>500</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>501</v>
       </c>
       <c r="L32" s="13"/>
     </row>
     <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>123</v>
@@ -5021,16 +5018,16 @@
         <v>158</v>
       </c>
       <c r="J33" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="K33" s="13" t="s">
         <v>502</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>503</v>
       </c>
       <c r="L33" s="13"/>
     </row>
     <row r="34" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>125</v>
@@ -5056,7 +5053,7 @@
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>127</v>
@@ -5077,19 +5074,19 @@
         <v>158</v>
       </c>
       <c r="J35" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="K35" s="13" t="s">
         <v>504</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>505</v>
       </c>
       <c r="L35" s="13"/>
     </row>
     <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -5107,16 +5104,16 @@
         <v>158</v>
       </c>
       <c r="J36" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>506</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>507</v>
       </c>
       <c r="L36" s="13"/>
     </row>
     <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>128</v>
@@ -5137,16 +5134,16 @@
         <v>158</v>
       </c>
       <c r="J37" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>508</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>509</v>
       </c>
       <c r="L37" s="13"/>
     </row>
     <row r="38" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>129</v>
@@ -5167,19 +5164,19 @@
         <v>158</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L38" s="13"/>
     </row>
     <row r="39" spans="1:12" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -5193,16 +5190,16 @@
         <v>158</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L39" s="13"/>
     </row>
     <row r="40" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>130</v>
@@ -5214,7 +5211,7 @@
         <v>2021</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>148</v>
@@ -5223,16 +5220,16 @@
         <v>158</v>
       </c>
       <c r="J40" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="K40" s="13" t="s">
         <v>514</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>515</v>
       </c>
       <c r="L40" s="13"/>
     </row>
     <row r="41" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>131</v>
@@ -5244,7 +5241,7 @@
         <v>2021</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>148</v>
@@ -5253,16 +5250,16 @@
         <v>158</v>
       </c>
       <c r="J41" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>514</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>515</v>
       </c>
       <c r="L41" s="13"/>
     </row>
     <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>245</v>
@@ -5283,17 +5280,17 @@
         <v>158</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
     </row>
     <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -5316,10 +5313,10 @@
     </row>
     <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -5328,7 +5325,7 @@
         <v>2021</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>148</v>
@@ -5337,17 +5334,17 @@
         <v>158</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
     </row>
     <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -5356,7 +5353,7 @@
         <v>2021</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>148</v>
@@ -5365,17 +5362,17 @@
         <v>158</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
     </row>
     <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -5384,7 +5381,7 @@
         <v>2021</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>148</v>
@@ -5393,17 +5390,17 @@
         <v>158</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
     </row>
     <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -5421,17 +5418,17 @@
         <v>158</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13"/>
     </row>
     <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -5440,7 +5437,7 @@
         <v>2021</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>148</v>
@@ -5449,17 +5446,17 @@
         <v>158</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K48" s="13"/>
       <c r="L48" s="13"/>
     </row>
     <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -5468,7 +5465,7 @@
         <v>2021</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>148</v>
@@ -5477,14 +5474,14 @@
         <v>158</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
     </row>
     <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>52</v>
@@ -5510,10 +5507,10 @@
     </row>
     <row r="51" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -5522,7 +5519,7 @@
         <v>2021</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>148</v>
@@ -5532,13 +5529,13 @@
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L51" s="13"/>
     </row>
     <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>132</v>
@@ -5550,7 +5547,7 @@
         <v>2021</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>148</v>
@@ -5564,7 +5561,7 @@
     </row>
     <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>133</v>
@@ -5576,7 +5573,7 @@
         <v>2021</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>148</v>
@@ -5590,7 +5587,7 @@
     </row>
     <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>134</v>
@@ -5602,7 +5599,7 @@
         <v>2021</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>148</v>
@@ -5616,7 +5613,7 @@
     </row>
     <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>135</v>
@@ -5628,7 +5625,7 @@
         <v>2021</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>148</v>
@@ -5642,7 +5639,7 @@
     </row>
     <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>136</v>
@@ -5668,7 +5665,7 @@
     </row>
     <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>138</v>
@@ -5680,7 +5677,7 @@
         <v>2021</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>148</v>
@@ -5694,7 +5691,7 @@
     </row>
     <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>139</v>
@@ -5720,10 +5717,10 @@
     </row>
     <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -5746,10 +5743,10 @@
     </row>
     <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
@@ -5758,7 +5755,7 @@
         <v>2021</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>148</v>
@@ -5772,10 +5769,10 @@
     </row>
     <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -5793,14 +5790,14 @@
         <v>158</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
     </row>
     <row r="62" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>203</v>
@@ -5812,7 +5809,7 @@
         <v>2021</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>148</v>
@@ -5821,14 +5818,14 @@
         <v>158</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>140</v>
@@ -5840,7 +5837,7 @@
         <v>2021</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>148</v>
@@ -5854,7 +5851,7 @@
     </row>
     <row r="64" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>141</v>
@@ -5875,16 +5872,16 @@
         <v>158</v>
       </c>
       <c r="J64" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="K64" s="13" t="s">
         <v>538</v>
-      </c>
-      <c r="K64" s="13" t="s">
-        <v>539</v>
       </c>
       <c r="L64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>143</v>
@@ -5896,7 +5893,7 @@
         <v>2021</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>148</v>
@@ -5910,7 +5907,7 @@
     </row>
     <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>144</v>
@@ -5922,7 +5919,7 @@
         <v>2021</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>148</v>
@@ -5936,7 +5933,7 @@
     </row>
     <row r="67" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>145</v>
@@ -5948,7 +5945,7 @@
         <v>2021</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>148</v>
@@ -5962,7 +5959,7 @@
     </row>
     <row r="68" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>146</v>
@@ -5974,7 +5971,7 @@
         <v>2021</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>148</v>
@@ -5988,10 +5985,10 @@
     </row>
     <row r="69" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -6004,20 +6001,20 @@
         <v>148</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
     </row>
     <row r="70" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -6035,17 +6032,17 @@
         <v>158</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
     </row>
     <row r="71" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -6063,17 +6060,17 @@
         <v>158</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
     </row>
     <row r="72" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
@@ -6092,10 +6089,10 @@
     </row>
     <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
@@ -6107,23 +6104,23 @@
         <v>155</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>158</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
     </row>
     <row r="74" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -6142,10 +6139,10 @@
     </row>
     <row r="75" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -6161,17 +6158,17 @@
         <v>158</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
     </row>
     <row r="76" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
@@ -6187,17 +6184,17 @@
         <v>158</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
     </row>
     <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -6215,14 +6212,14 @@
         <v>158</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
     </row>
     <row r="78" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>92</v>
@@ -6237,20 +6234,20 @@
         <v>30</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I78" s="23" t="s">
         <v>158</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K78" s="25"/>
       <c r="L78" s="13"/>
     </row>
     <row r="79" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>87</v>
@@ -6271,14 +6268,14 @@
         <v>158</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
     </row>
     <row r="80" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>90</v>
@@ -6293,20 +6290,20 @@
         <v>30</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>158</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
     </row>
     <row r="81" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>93</v>
@@ -6321,20 +6318,20 @@
         <v>30</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I81" s="8" t="s">
         <v>158</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
     </row>
     <row r="82" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>83</v>
@@ -6355,14 +6352,14 @@
         <v>158</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
     </row>
     <row r="83" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>34</v>
@@ -6383,14 +6380,14 @@
         <v>158</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
     </row>
     <row r="84" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>91</v>
@@ -6405,20 +6402,20 @@
         <v>30</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>158</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
     </row>
     <row r="85" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>89</v>
@@ -6439,14 +6436,14 @@
         <v>158</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
     </row>
     <row r="86" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>27</v>
@@ -6474,7 +6471,7 @@
     </row>
     <row r="87" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>80</v>
@@ -6486,7 +6483,7 @@
         <v>2021</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>232</v>
@@ -6495,14 +6492,14 @@
         <v>158</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
     </row>
     <row r="88" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>86</v>
@@ -6523,14 +6520,14 @@
         <v>158</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
     </row>
     <row r="89" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>85</v>
@@ -6551,14 +6548,14 @@
         <v>158</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
     </row>
     <row r="90" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>95</v>
@@ -6566,7 +6563,7 @@
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
       <c r="E90" s="13" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F90" s="19">
         <v>2021</v>
@@ -6581,16 +6578,16 @@
         <v>158</v>
       </c>
       <c r="J90" s="13" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L90" s="13"/>
     </row>
     <row r="91" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>96</v>
@@ -6598,7 +6595,7 @@
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="13" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F91" s="19">
         <v>2021</v>
@@ -6613,16 +6610,16 @@
         <v>158</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L91" s="13"/>
     </row>
     <row r="92" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>97</v>
@@ -6654,7 +6651,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D93" s="56"/>
       <c r="E93" s="57"/>
@@ -6665,7 +6662,7 @@
         <v>88</v>
       </c>
       <c r="H93" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I93" s="23" t="s">
         <v>158</v>
@@ -6693,7 +6690,7 @@
         <v>88</v>
       </c>
       <c r="H94" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>158</v>
@@ -6710,7 +6707,7 @@
         <v>87</v>
       </c>
       <c r="C95" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D95" s="59"/>
       <c r="E95" s="60"/>
@@ -6738,7 +6735,7 @@
         <v>94</v>
       </c>
       <c r="C96" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D96" s="59"/>
       <c r="E96" s="60"/>
@@ -6794,7 +6791,7 @@
         <v>90</v>
       </c>
       <c r="C98" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D98" s="59"/>
       <c r="E98" s="60"/>
@@ -6805,7 +6802,7 @@
         <v>88</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>158</v>
@@ -6833,7 +6830,7 @@
         <v>88</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>158</v>
@@ -6850,7 +6847,7 @@
         <v>93</v>
       </c>
       <c r="C100" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D100" s="59"/>
       <c r="E100" s="60"/>
@@ -6861,7 +6858,7 @@
         <v>88</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>158</v>
@@ -6889,7 +6886,7 @@
         <v>88</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I101" s="8" t="s">
         <v>158</v>
@@ -6906,7 +6903,7 @@
         <v>83</v>
       </c>
       <c r="C102" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D102" s="59"/>
       <c r="E102" s="60"/>
@@ -6962,7 +6959,7 @@
         <v>34</v>
       </c>
       <c r="C104" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D104" s="59"/>
       <c r="E104" s="60"/>
@@ -7018,7 +7015,7 @@
         <v>91</v>
       </c>
       <c r="C106" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D106" s="59"/>
       <c r="E106" s="60"/>
@@ -7029,7 +7026,7 @@
         <v>88</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I106" s="8" t="s">
         <v>158</v>
@@ -7057,7 +7054,7 @@
         <v>88</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I107" s="8" t="s">
         <v>158</v>
@@ -7074,7 +7071,7 @@
         <v>99</v>
       </c>
       <c r="C108" s="59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D108" s="59"/>
       <c r="E108" s="60"/>
@@ -7085,19 +7082,19 @@
         <v>84</v>
       </c>
       <c r="H108" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I108" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="J108" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="J108" s="13" t="s">
+      <c r="K108" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="K108" s="13" t="s">
-        <v>557</v>
-      </c>
       <c r="L108" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7119,19 +7116,19 @@
         <v>84</v>
       </c>
       <c r="H109" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I109" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="J109" s="13" t="s">
         <v>555</v>
       </c>
-      <c r="J109" s="13" t="s">
-        <v>556</v>
-      </c>
       <c r="K109" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L109" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7142,7 +7139,7 @@
         <v>98</v>
       </c>
       <c r="C110" s="59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D110" s="59"/>
       <c r="E110" s="60"/>
@@ -7156,16 +7153,16 @@
         <v>35</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L110" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7190,16 +7187,16 @@
         <v>35</v>
       </c>
       <c r="I111" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L111" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7210,7 +7207,7 @@
         <v>100</v>
       </c>
       <c r="C112" s="59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D112" s="59"/>
       <c r="E112" s="60"/>
@@ -7224,16 +7221,16 @@
         <v>36</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J112" s="13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L112" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7258,16 +7255,16 @@
         <v>36</v>
       </c>
       <c r="I113" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L113" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7278,7 +7275,7 @@
         <v>89</v>
       </c>
       <c r="C114" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D114" s="59"/>
       <c r="E114" s="60"/>
@@ -7306,7 +7303,7 @@
         <v>27</v>
       </c>
       <c r="C115" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D115" s="59"/>
       <c r="E115" s="60"/>
@@ -7362,7 +7359,7 @@
         <v>195</v>
       </c>
       <c r="C117" s="59" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D117" s="59"/>
       <c r="E117" s="60"/>
@@ -7370,7 +7367,7 @@
         <v>2010</v>
       </c>
       <c r="G117" s="59" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>195</v>
@@ -7398,7 +7395,7 @@
         <v>2010</v>
       </c>
       <c r="G118" s="59" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H118" s="7" t="s">
         <v>195</v>
@@ -7418,7 +7415,7 @@
         <v>80</v>
       </c>
       <c r="C119" s="59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D119" s="59"/>
       <c r="E119" s="60"/>
@@ -7432,10 +7429,10 @@
         <v>232</v>
       </c>
       <c r="I119" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="J119" s="13" t="s">
         <v>562</v>
-      </c>
-      <c r="J119" s="13" t="s">
-        <v>563</v>
       </c>
       <c r="K119" s="13"/>
       <c r="L119" s="13"/>
@@ -7448,7 +7445,7 @@
         <v>86</v>
       </c>
       <c r="C120" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D120" s="59"/>
       <c r="E120" s="60"/>
@@ -7476,7 +7473,7 @@
         <v>85</v>
       </c>
       <c r="C121" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D121" s="59"/>
       <c r="E121" s="60"/>
@@ -7504,7 +7501,7 @@
         <v>95</v>
       </c>
       <c r="C122" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D122" s="59"/>
       <c r="E122" s="60"/>
@@ -7518,13 +7515,13 @@
         <v>148</v>
       </c>
       <c r="I122" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="J122" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="J122" s="13" t="s">
-        <v>565</v>
-      </c>
       <c r="K122" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L122" s="13"/>
     </row>
@@ -7550,11 +7547,11 @@
         <v>148</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J123" s="13"/>
       <c r="K123" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L123" s="13"/>
     </row>
@@ -7566,7 +7563,7 @@
         <v>96</v>
       </c>
       <c r="C124" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D124" s="59"/>
       <c r="E124" s="60"/>
@@ -7580,11 +7577,11 @@
         <v>148</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J124" s="13"/>
       <c r="K124" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L124" s="13"/>
     </row>
@@ -7610,11 +7607,11 @@
         <v>148</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J125" s="13"/>
       <c r="K125" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L125" s="13"/>
     </row>
@@ -7626,7 +7623,7 @@
         <v>97</v>
       </c>
       <c r="C126" s="59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D126" s="59"/>
       <c r="E126" s="60"/>
@@ -7668,7 +7665,7 @@
         <v>21</v>
       </c>
       <c r="I127" s="14" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J127" s="13"/>
       <c r="K127" s="13"/>
@@ -7729,10 +7726,10 @@
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>202</v>
@@ -7741,12 +7738,12 @@
         <v>148</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>195</v>
@@ -7765,14 +7762,14 @@
     </row>
     <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>21</v>
@@ -7784,14 +7781,14 @@
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>47</v>
@@ -7803,14 +7800,14 @@
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>36</v>
@@ -7822,7 +7819,7 @@
     </row>
     <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>202</v>
@@ -7832,21 +7829,21 @@
         <v>126</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7" t="s">
@@ -7858,26 +7855,26 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -7885,14 +7882,14 @@
     </row>
     <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>232</v>
@@ -7904,7 +7901,7 @@
     </row>
     <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>241</v>
@@ -7923,7 +7920,7 @@
     </row>
     <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>243</v>
@@ -7942,7 +7939,7 @@
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>243</v>
@@ -7961,7 +7958,7 @@
     </row>
     <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>244</v>
@@ -7978,16 +7975,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>148</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -8024,10 +8021,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>250</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>251</v>
       </c>
       <c r="E1" s="29" t="s">
         <v>2</v>
@@ -8065,34 +8062,34 @@
         <v>73</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="D2" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="E2" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="F2" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="G2" s="23" t="s">
         <v>256</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>257</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>126</v>
       </c>
       <c r="I2" s="23"/>
       <c r="J2" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K2" s="65"/>
-      <c r="L2" s="67"/>
+        <v>257</v>
+      </c>
+      <c r="K2" s="73"/>
+      <c r="L2" s="77"/>
       <c r="M2" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -8103,34 +8100,34 @@
         <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>253</v>
-      </c>
       <c r="D3" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>261</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K3" s="66"/>
-      <c r="L3" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K3" s="74"/>
+      <c r="L3" s="78"/>
       <c r="M3" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
@@ -8141,34 +8138,34 @@
         <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>253</v>
-      </c>
       <c r="D4" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K4" s="66"/>
-      <c r="L4" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K4" s="74"/>
+      <c r="L4" s="78"/>
       <c r="M4" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -8179,32 +8176,32 @@
         <v>73</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>253</v>
-      </c>
       <c r="D5" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K5" s="66"/>
-      <c r="L5" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K5" s="74"/>
+      <c r="L5" s="78"/>
       <c r="M5" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -8215,36 +8212,36 @@
         <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>267</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K6" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="L6" s="71"/>
+        <v>257</v>
+      </c>
+      <c r="K6" s="76" t="s">
+        <v>267</v>
+      </c>
+      <c r="L6" s="81"/>
       <c r="M6" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -8255,34 +8252,34 @@
         <v>73</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>270</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K7" s="66"/>
-      <c r="L7" s="72"/>
+        <v>257</v>
+      </c>
+      <c r="K7" s="74"/>
+      <c r="L7" s="82"/>
       <c r="M7" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -8293,32 +8290,32 @@
         <v>73</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>126</v>
       </c>
       <c r="I8" s="27"/>
       <c r="J8" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K8" s="70"/>
-      <c r="L8" s="73"/>
+        <v>257</v>
+      </c>
+      <c r="K8" s="75"/>
+      <c r="L8" s="83"/>
       <c r="M8" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -8329,38 +8326,38 @@
         <v>73</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>274</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>223</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K9" s="74" t="s">
+        <v>257</v>
+      </c>
+      <c r="K9" s="84" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="L9" s="76" t="s">
-        <v>277</v>
-      </c>
       <c r="M9" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -8371,19 +8368,19 @@
         <v>73</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>273</v>
-      </c>
       <c r="E10" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>223</v>
@@ -8393,12 +8390,12 @@
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K10" s="75"/>
-      <c r="L10" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K10" s="68"/>
+      <c r="L10" s="78"/>
       <c r="M10" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -8409,34 +8406,34 @@
         <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>148</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K11" s="75"/>
-      <c r="L11" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K11" s="68"/>
+      <c r="L11" s="78"/>
       <c r="M11" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -8447,17 +8444,17 @@
         <v>73</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>223</v>
@@ -8467,16 +8464,16 @@
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K12" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="L12" s="22" t="s">
-        <v>283</v>
-      </c>
       <c r="M12" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -8487,34 +8484,34 @@
         <v>73</v>
       </c>
       <c r="B13" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="38" t="s">
+      <c r="F13" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="G13" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>286</v>
-      </c>
       <c r="H13" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K13" s="40"/>
       <c r="L13" s="41"/>
       <c r="M13" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -8525,38 +8522,38 @@
         <v>73</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>290</v>
-      </c>
       <c r="H14" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K14" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="L14" s="22" t="s">
-        <v>292</v>
-      </c>
       <c r="M14" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
@@ -8567,34 +8564,34 @@
         <v>73</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>294</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K15" s="35"/>
       <c r="L15" s="22"/>
       <c r="M15" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -8605,38 +8602,38 @@
         <v>73</v>
       </c>
       <c r="B16" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="E16" s="23" t="s">
+      <c r="F16" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="G16" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="H16" s="23" t="s">
         <v>299</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>300</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K16" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="L16" s="43" t="s">
         <v>301</v>
       </c>
-      <c r="L16" s="43" t="s">
-        <v>302</v>
-      </c>
       <c r="M16" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -8647,19 +8644,19 @@
         <v>73</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>94</v>
@@ -8669,16 +8666,16 @@
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K17" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="L17" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="L17" s="22" t="s">
-        <v>305</v>
-      </c>
       <c r="M17" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
@@ -8689,34 +8686,34 @@
         <v>73</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>307</v>
-      </c>
       <c r="H18" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K18" s="69"/>
+        <v>257</v>
+      </c>
+      <c r="K18" s="76"/>
       <c r="L18" s="22"/>
       <c r="M18" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -8727,34 +8724,34 @@
         <v>73</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D19" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>307</v>
       </c>
       <c r="H19" s="26" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K19" s="70"/>
+        <v>257</v>
+      </c>
+      <c r="K19" s="75"/>
       <c r="L19" s="44"/>
       <c r="M19" s="27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -8765,19 +8762,19 @@
         <v>73</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G20" s="23" t="s">
         <v>57</v>
@@ -8787,16 +8784,16 @@
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K20" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="K20" s="76" t="s">
+        <v>310</v>
+      </c>
+      <c r="L20" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="L20" s="76" t="s">
-        <v>312</v>
-      </c>
       <c r="M20" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -8807,19 +8804,19 @@
         <v>73</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E21" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>313</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>314</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>57</v>
@@ -8829,12 +8826,12 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K21" s="66"/>
-      <c r="L21" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K21" s="74"/>
+      <c r="L21" s="78"/>
       <c r="M21" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
@@ -8845,17 +8842,17 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>57</v>
@@ -8865,12 +8862,12 @@
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K22" s="66"/>
-      <c r="L22" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K22" s="74"/>
+      <c r="L22" s="78"/>
       <c r="M22" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -8881,19 +8878,19 @@
         <v>73</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>57</v>
@@ -8903,12 +8900,12 @@
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K23" s="66"/>
-      <c r="L23" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K23" s="74"/>
+      <c r="L23" s="78"/>
       <c r="M23" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -8919,19 +8916,19 @@
         <v>73</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>57</v>
@@ -8941,12 +8938,12 @@
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K24" s="66"/>
-      <c r="L24" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K24" s="74"/>
+      <c r="L24" s="78"/>
       <c r="M24" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -8957,38 +8954,38 @@
         <v>73</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E25" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>260</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>261</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I25" s="23"/>
       <c r="J25" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K25" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="K25" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="L25" s="77" t="s">
         <v>318</v>
       </c>
-      <c r="L25" s="67" t="s">
-        <v>319</v>
-      </c>
       <c r="M25" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
@@ -8999,34 +8996,34 @@
         <v>73</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E26" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>320</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>321</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K26" s="66"/>
-      <c r="L26" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K26" s="74"/>
+      <c r="L26" s="78"/>
       <c r="M26" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
@@ -9037,34 +9034,34 @@
         <v>73</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K27" s="66"/>
-      <c r="L27" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K27" s="74"/>
+      <c r="L27" s="78"/>
       <c r="M27" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -9075,32 +9072,32 @@
         <v>73</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K28" s="70"/>
-      <c r="L28" s="77"/>
+        <v>257</v>
+      </c>
+      <c r="K28" s="75"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
@@ -9114,16 +9111,16 @@
         <v>127</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="F29" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>256</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>61</v>
@@ -9133,14 +9130,14 @@
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K29" s="69" t="s">
-        <v>324</v>
+        <v>257</v>
+      </c>
+      <c r="K29" s="76" t="s">
+        <v>323</v>
       </c>
       <c r="L29" s="22"/>
       <c r="M29" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
@@ -9154,16 +9151,16 @@
         <v>127</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>61</v>
@@ -9173,12 +9170,12 @@
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K30" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K30" s="74"/>
       <c r="L30" s="22"/>
       <c r="M30" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
@@ -9192,31 +9189,31 @@
         <v>127</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>61</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K31" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K31" s="74"/>
       <c r="L31" s="22"/>
       <c r="M31" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
@@ -9230,14 +9227,14 @@
         <v>127</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>61</v>
@@ -9247,12 +9244,12 @@
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K32" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K32" s="74"/>
       <c r="L32" s="22"/>
       <c r="M32" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
@@ -9263,38 +9260,38 @@
         <v>73</v>
       </c>
       <c r="B33" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="C33" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>327</v>
-      </c>
       <c r="H33" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I33" s="23"/>
       <c r="J33" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K33" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="K33" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="L33" s="43" t="s">
         <v>291</v>
       </c>
-      <c r="L33" s="43" t="s">
-        <v>292</v>
-      </c>
       <c r="M33" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -9305,34 +9302,34 @@
         <v>73</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H34" s="26" t="s">
         <v>126</v>
       </c>
       <c r="I34" s="26"/>
       <c r="J34" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K34" s="70"/>
+        <v>257</v>
+      </c>
+      <c r="K34" s="75"/>
       <c r="L34" s="44"/>
       <c r="M34" s="27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
@@ -9343,38 +9340,38 @@
         <v>73</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="H35" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K35" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="K35" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="L35" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="L35" s="22" t="s">
-        <v>292</v>
-      </c>
       <c r="M35" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N35" s="7"/>
       <c r="O35" s="7"/>
@@ -9385,34 +9382,34 @@
         <v>73</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K36" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K36" s="74"/>
       <c r="L36" s="22"/>
       <c r="M36" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N36" s="7"/>
       <c r="O36" s="7"/>
@@ -9423,34 +9420,34 @@
         <v>73</v>
       </c>
       <c r="B37" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="E37" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="C37" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="E37" s="38" t="s">
+      <c r="F37" s="38" t="s">
         <v>334</v>
       </c>
-      <c r="F37" s="38" t="s">
+      <c r="G37" s="38" t="s">
         <v>335</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>336</v>
       </c>
       <c r="H37" s="38" t="s">
         <v>118</v>
       </c>
       <c r="I37" s="38"/>
       <c r="J37" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K37" s="40"/>
       <c r="L37" s="41"/>
       <c r="M37" s="45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N37" s="7"/>
       <c r="O37" s="7"/>
@@ -9461,34 +9458,34 @@
         <v>73</v>
       </c>
       <c r="B38" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>338</v>
-      </c>
       <c r="H38" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K38" s="35"/>
       <c r="L38" s="22"/>
       <c r="M38" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
@@ -9499,19 +9496,19 @@
         <v>73</v>
       </c>
       <c r="B39" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E39" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>340</v>
-      </c>
       <c r="F39" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G39" s="23" t="s">
         <v>37</v>
@@ -9521,14 +9518,14 @@
       </c>
       <c r="I39" s="23"/>
       <c r="J39" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K39" s="46" t="s">
-        <v>341</v>
-      </c>
-      <c r="L39" s="67"/>
+        <v>340</v>
+      </c>
+      <c r="L39" s="77"/>
       <c r="M39" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
@@ -9539,19 +9536,19 @@
         <v>73</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>343</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>44</v>
@@ -9561,12 +9558,12 @@
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K40" s="35"/>
-      <c r="L40" s="68"/>
+      <c r="L40" s="78"/>
       <c r="M40" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
@@ -9577,19 +9574,19 @@
         <v>73</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>35</v>
@@ -9599,16 +9596,16 @@
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K41" s="35" t="s">
+        <v>344</v>
+      </c>
+      <c r="L41" s="44" t="s">
         <v>345</v>
       </c>
-      <c r="L41" s="44" t="s">
-        <v>346</v>
-      </c>
       <c r="M41" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
@@ -9619,19 +9616,19 @@
         <v>73</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E42" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>149</v>
@@ -9641,16 +9638,16 @@
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K42" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="K42" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="L42" s="79" t="s">
         <v>348</v>
       </c>
-      <c r="L42" s="76" t="s">
-        <v>349</v>
-      </c>
       <c r="M42" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
@@ -9661,19 +9658,19 @@
         <v>73</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>149</v>
@@ -9683,12 +9680,12 @@
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K43" s="66"/>
-      <c r="L43" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K43" s="74"/>
+      <c r="L43" s="78"/>
       <c r="M43" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
@@ -9699,19 +9696,19 @@
         <v>73</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>149</v>
@@ -9721,12 +9718,12 @@
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K44" s="66"/>
-      <c r="L44" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K44" s="74"/>
+      <c r="L44" s="78"/>
       <c r="M44" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
@@ -9737,17 +9734,17 @@
         <v>73</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>149</v>
@@ -9757,12 +9754,12 @@
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K45" s="66"/>
-      <c r="L45" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K45" s="74"/>
+      <c r="L45" s="78"/>
       <c r="M45" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
@@ -9773,19 +9770,19 @@
         <v>73</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>149</v>
@@ -9795,12 +9792,12 @@
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K46" s="66"/>
-      <c r="L46" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K46" s="74"/>
+      <c r="L46" s="78"/>
       <c r="M46" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -9811,19 +9808,19 @@
         <v>73</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>149</v>
@@ -9833,12 +9830,12 @@
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K47" s="66"/>
-      <c r="L47" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K47" s="74"/>
+      <c r="L47" s="78"/>
       <c r="M47" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
@@ -9849,19 +9846,19 @@
         <v>73</v>
       </c>
       <c r="B48" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="E48" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="C48" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>354</v>
-      </c>
       <c r="F48" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G48" s="45" t="s">
         <v>35</v>
@@ -9871,16 +9868,16 @@
       </c>
       <c r="I48" s="45"/>
       <c r="J48" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K48" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="L48" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="L48" s="41" t="s">
-        <v>356</v>
-      </c>
       <c r="M48" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
@@ -9891,34 +9888,34 @@
         <v>73</v>
       </c>
       <c r="B49" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="F49" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G49" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="G49" s="8" t="s">
+      <c r="H49" s="8" t="s">
         <v>359</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>360</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K49" s="35"/>
       <c r="L49" s="22"/>
       <c r="M49" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N49" s="7"/>
       <c r="O49" s="7"/>
@@ -9929,19 +9926,19 @@
         <v>73</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E50" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F50" s="23" t="s">
         <v>260</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>261</v>
       </c>
       <c r="G50" s="23" t="s">
         <v>111</v>
@@ -9951,14 +9948,14 @@
       </c>
       <c r="I50" s="23"/>
       <c r="J50" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K50" s="78" t="s">
-        <v>362</v>
+        <v>257</v>
+      </c>
+      <c r="K50" s="67" t="s">
+        <v>361</v>
       </c>
       <c r="L50" s="43"/>
       <c r="M50" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N50" s="7"/>
       <c r="O50" s="7"/>
@@ -9969,19 +9966,19 @@
         <v>73</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E51" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>364</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>111</v>
@@ -9991,12 +9988,12 @@
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K51" s="75"/>
+        <v>257</v>
+      </c>
+      <c r="K51" s="68"/>
       <c r="L51" s="22"/>
       <c r="M51" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N51" s="7"/>
       <c r="O51" s="7"/>
@@ -10007,19 +10004,19 @@
         <v>73</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E52" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>365</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>366</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>111</v>
@@ -10029,12 +10026,12 @@
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K52" s="75"/>
+        <v>257</v>
+      </c>
+      <c r="K52" s="68"/>
       <c r="L52" s="22"/>
       <c r="M52" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
@@ -10045,19 +10042,19 @@
         <v>73</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>111</v>
@@ -10067,12 +10064,12 @@
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K53" s="75"/>
+        <v>257</v>
+      </c>
+      <c r="K53" s="68"/>
       <c r="L53" s="22"/>
       <c r="M53" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
@@ -10083,17 +10080,17 @@
         <v>73</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>111</v>
@@ -10103,12 +10100,12 @@
       </c>
       <c r="I54" s="26"/>
       <c r="J54" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K54" s="79"/>
+        <v>257</v>
+      </c>
+      <c r="K54" s="69"/>
       <c r="L54" s="44"/>
       <c r="M54" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
@@ -10119,38 +10116,38 @@
         <v>73</v>
       </c>
       <c r="B55" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E55" s="8" t="s">
+      <c r="F55" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>371</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>148</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I55" s="7"/>
       <c r="J55" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K55" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="L55" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="L55" s="10" t="s">
-        <v>373</v>
-      </c>
       <c r="M55" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
@@ -10161,36 +10158,36 @@
         <v>73</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G56" s="45" t="s">
         <v>39</v>
       </c>
       <c r="H56" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I56" s="45"/>
       <c r="J56" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K56" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="L56" s="41" t="s">
         <v>375</v>
       </c>
-      <c r="L56" s="41" t="s">
-        <v>376</v>
-      </c>
       <c r="M56" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N56" s="7"/>
       <c r="O56" s="7"/>
@@ -10201,36 +10198,36 @@
         <v>73</v>
       </c>
       <c r="B57" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>377</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>378</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K57" s="69" t="s">
-        <v>379</v>
+        <v>257</v>
+      </c>
+      <c r="K57" s="76" t="s">
+        <v>378</v>
       </c>
       <c r="L57" s="22"/>
       <c r="M57" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N57" s="7"/>
       <c r="O57" s="7"/>
@@ -10241,34 +10238,34 @@
         <v>73</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F58" s="8" t="s">
         <v>380</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>381</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K58" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K58" s="74"/>
       <c r="L58" s="22"/>
       <c r="M58" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
@@ -10279,32 +10276,32 @@
         <v>73</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>27</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K59" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K59" s="74"/>
       <c r="L59" s="22"/>
       <c r="M59" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N59" s="7"/>
       <c r="O59" s="7"/>
@@ -10315,36 +10312,36 @@
         <v>73</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E60" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F60" s="23" t="s">
         <v>260</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>261</v>
       </c>
       <c r="G60" s="24" t="s">
         <v>39</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I60" s="24"/>
       <c r="J60" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="K60" s="67" t="s">
-        <v>384</v>
+        <v>257</v>
+      </c>
+      <c r="K60" s="77" t="s">
+        <v>383</v>
       </c>
       <c r="L60" s="43"/>
       <c r="M60" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N60" s="7"/>
       <c r="O60" s="7"/>
@@ -10355,36 +10352,36 @@
         <v>73</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>39</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K61" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K61" s="78"/>
       <c r="L61" s="22" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
@@ -10395,36 +10392,36 @@
         <v>73</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>39</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K62" s="68"/>
+        <v>257</v>
+      </c>
+      <c r="K62" s="78"/>
       <c r="L62" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
@@ -10435,34 +10432,34 @@
         <v>73</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D63" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="F63" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="K63" s="69"/>
+        <v>257</v>
+      </c>
+      <c r="K63" s="76"/>
       <c r="L63" s="22"/>
       <c r="M63" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -10473,34 +10470,34 @@
         <v>73</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="K64" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K64" s="74"/>
       <c r="L64" s="22"/>
       <c r="M64" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
@@ -10511,36 +10508,36 @@
         <v>73</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="K65" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K65" s="74"/>
       <c r="L65" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
@@ -10551,32 +10548,32 @@
         <v>73</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="K66" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K66" s="74"/>
       <c r="L66" s="13"/>
       <c r="M66" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -10587,34 +10584,34 @@
         <v>73</v>
       </c>
       <c r="B67" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="E67" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="C67" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="D67" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="E67" s="26" t="s">
-        <v>390</v>
-      </c>
       <c r="F67" s="26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>36</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I67" s="26"/>
       <c r="J67" s="26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K67" s="48"/>
       <c r="L67" s="37"/>
       <c r="M67" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N67" s="7"/>
       <c r="O67" s="7"/>
@@ -10625,34 +10622,34 @@
         <v>73</v>
       </c>
       <c r="B68" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E68" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="C68" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="D68" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="E68" s="26" t="s">
+      <c r="F68" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="G68" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="F68" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>393</v>
-      </c>
       <c r="H68" s="26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I68" s="26"/>
       <c r="J68" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K68" s="40"/>
       <c r="L68" s="44"/>
       <c r="M68" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
@@ -10663,38 +10660,38 @@
         <v>73</v>
       </c>
       <c r="B69" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G69" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>395</v>
-      </c>
       <c r="H69" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K69" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="K69" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="L69" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="L69" s="22" t="s">
-        <v>292</v>
-      </c>
       <c r="M69" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
@@ -10705,34 +10702,34 @@
         <v>73</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H70" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K70" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K70" s="74"/>
       <c r="L70" s="22"/>
       <c r="M70" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
@@ -10743,17 +10740,17 @@
         <v>73</v>
       </c>
       <c r="B71" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="C71" s="23" t="s">
         <v>397</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>398</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>399</v>
-      </c>
-      <c r="F71" s="23" t="s">
-        <v>400</v>
       </c>
       <c r="G71" s="23" t="s">
         <v>195</v>
@@ -10763,16 +10760,16 @@
       </c>
       <c r="I71" s="23"/>
       <c r="J71" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K71" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="L71" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="L71" s="43" t="s">
-        <v>402</v>
-      </c>
       <c r="M71" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
@@ -10783,34 +10780,34 @@
         <v>73</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E72" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>195</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K72" s="69"/>
+        <v>257</v>
+      </c>
+      <c r="K72" s="76"/>
       <c r="L72" s="22"/>
       <c r="M72" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N72" s="7"/>
       <c r="O72" s="7"/>
@@ -10821,32 +10818,32 @@
         <v>73</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C73" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>253</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>254</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>195</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K73" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K73" s="74"/>
       <c r="L73" s="22"/>
       <c r="M73" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N73" s="7"/>
       <c r="O73" s="7"/>
@@ -10857,17 +10854,17 @@
         <v>73</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>195</v>
@@ -10877,12 +10874,12 @@
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K74" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K74" s="74"/>
       <c r="L74" s="22"/>
       <c r="M74" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
@@ -10893,15 +10890,15 @@
         <v>73</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="26" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>195</v>
@@ -10911,12 +10908,12 @@
       </c>
       <c r="I75" s="26"/>
       <c r="J75" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K75" s="70"/>
+        <v>257</v>
+      </c>
+      <c r="K75" s="75"/>
       <c r="L75" s="44"/>
       <c r="M75" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
@@ -10927,34 +10924,34 @@
         <v>73</v>
       </c>
       <c r="B76" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="G76" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>409</v>
-      </c>
       <c r="H76" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K76" s="35"/>
       <c r="L76" s="22"/>
       <c r="M76" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
@@ -10968,16 +10965,16 @@
         <v>79</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E77" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="F77" s="23" t="s">
         <v>313</v>
-      </c>
-      <c r="F77" s="23" t="s">
-        <v>314</v>
       </c>
       <c r="G77" s="23" t="s">
         <v>232</v>
@@ -10986,19 +10983,19 @@
         <v>126</v>
       </c>
       <c r="I77" s="49" t="s">
+        <v>409</v>
+      </c>
+      <c r="J77" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="K77" s="67" t="s">
         <v>410</v>
       </c>
-      <c r="J77" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="K77" s="78" t="s">
+      <c r="L77" s="73" t="s">
         <v>411</v>
       </c>
-      <c r="L77" s="65" t="s">
-        <v>412</v>
-      </c>
       <c r="M77" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
@@ -11012,16 +11009,16 @@
         <v>79</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G78" s="23" t="s">
         <v>232</v>
@@ -11030,15 +11027,15 @@
         <v>126</v>
       </c>
       <c r="I78" s="49" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J78" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K78" s="79"/>
-      <c r="L78" s="81"/>
+        <v>257</v>
+      </c>
+      <c r="K78" s="69"/>
+      <c r="L78" s="71"/>
       <c r="M78" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
@@ -11052,16 +11049,16 @@
         <v>81</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E79" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G79" s="23" t="s">
         <v>232</v>
@@ -11071,14 +11068,14 @@
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K79" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="L79" s="81"/>
+        <v>412</v>
+      </c>
+      <c r="L79" s="71"/>
       <c r="M79" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N79" s="7"/>
       <c r="O79" s="7"/>
@@ -11092,14 +11089,14 @@
         <v>82</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E80" s="26"/>
       <c r="F80" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G80" s="23" t="s">
         <v>232</v>
@@ -11108,17 +11105,17 @@
         <v>126</v>
       </c>
       <c r="I80" s="49" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J80" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="L80" s="70"/>
+        <v>412</v>
+      </c>
+      <c r="L80" s="75"/>
       <c r="M80" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N80" s="7"/>
       <c r="O80" s="7"/>
@@ -11129,38 +11126,38 @@
         <v>73</v>
       </c>
       <c r="B81" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G81" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>415</v>
-      </c>
       <c r="H81" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K81" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="K81" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="L81" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="L81" s="22" t="s">
-        <v>292</v>
-      </c>
       <c r="M81" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N81" s="7"/>
       <c r="O81" s="7"/>
@@ -11171,34 +11168,34 @@
         <v>73</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K82" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K82" s="74"/>
       <c r="L82" s="22"/>
       <c r="M82" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N82" s="7"/>
       <c r="O82" s="7"/>
@@ -11209,19 +11206,19 @@
         <v>73</v>
       </c>
       <c r="B83" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="C83" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="D83" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83" s="38" t="s">
         <v>417</v>
       </c>
-      <c r="C83" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="D83" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="E83" s="38" t="s">
-        <v>418</v>
-      </c>
       <c r="F83" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G83" s="38" t="s">
         <v>148</v>
@@ -11231,16 +11228,16 @@
       </c>
       <c r="I83" s="38"/>
       <c r="J83" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K83" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="L83" s="41" t="s">
         <v>419</v>
       </c>
-      <c r="L83" s="41" t="s">
-        <v>420</v>
-      </c>
       <c r="M83" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N83" s="7"/>
       <c r="O83" s="7"/>
@@ -11254,16 +11251,16 @@
         <v>121</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E84" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="F84" s="8" t="s">
         <v>421</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>422</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>148</v>
@@ -11273,16 +11270,16 @@
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K84" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="L84" s="22" t="s">
         <v>423</v>
       </c>
-      <c r="L84" s="22" t="s">
-        <v>424</v>
-      </c>
       <c r="M84" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N84" s="7"/>
       <c r="O84" s="7"/>
@@ -11296,16 +11293,16 @@
         <v>121</v>
       </c>
       <c r="C85" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E85" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>203</v>
@@ -11315,14 +11312,14 @@
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K85" s="69" t="s">
-        <v>425</v>
+        <v>257</v>
+      </c>
+      <c r="K85" s="76" t="s">
+        <v>424</v>
       </c>
       <c r="L85" s="22"/>
       <c r="M85" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N85" s="7"/>
       <c r="O85" s="7"/>
@@ -11336,16 +11333,16 @@
         <v>121</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D86" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E86" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>203</v>
@@ -11355,12 +11352,12 @@
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K86" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K86" s="74"/>
       <c r="L86" s="22"/>
       <c r="M86" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N86" s="7"/>
       <c r="O86" s="7"/>
@@ -11374,16 +11371,16 @@
         <v>121</v>
       </c>
       <c r="C87" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D87" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D87" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E87" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>421</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>422</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>203</v>
@@ -11393,12 +11390,12 @@
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K87" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K87" s="74"/>
       <c r="L87" s="22"/>
       <c r="M87" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N87" s="7"/>
       <c r="O87" s="7"/>
@@ -11412,14 +11409,14 @@
         <v>121</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>253</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>254</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>203</v>
@@ -11429,12 +11426,12 @@
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K88" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K88" s="74"/>
       <c r="L88" s="22"/>
       <c r="M88" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
@@ -11448,16 +11445,16 @@
         <v>121</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D89" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E89" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E89" s="8" t="s">
-        <v>260</v>
-      </c>
       <c r="F89" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>203</v>
@@ -11467,12 +11464,12 @@
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K89" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K89" s="74"/>
       <c r="L89" s="22"/>
       <c r="M89" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N89" s="7"/>
       <c r="O89" s="7"/>
@@ -11486,16 +11483,16 @@
         <v>121</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>203</v>
@@ -11505,12 +11502,12 @@
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K90" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K90" s="74"/>
       <c r="L90" s="22"/>
       <c r="M90" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N90" s="7"/>
       <c r="O90" s="7"/>
@@ -11524,35 +11521,35 @@
         <v>204</v>
       </c>
       <c r="C91" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D91" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="D91" s="23" t="s">
+      <c r="E91" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="E91" s="23" t="s">
+      <c r="F91" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="F91" s="23" t="s">
-        <v>256</v>
-      </c>
       <c r="G91" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H91" s="23" t="s">
         <v>155</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K91" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="K91" s="67" t="s">
+        <v>430</v>
+      </c>
+      <c r="L91" s="70" t="s">
         <v>431</v>
       </c>
-      <c r="L91" s="80" t="s">
-        <v>432</v>
-      </c>
       <c r="M91" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N91" s="7"/>
       <c r="O91" s="7"/>
@@ -11566,31 +11563,31 @@
         <v>204</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D92" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E92" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="F92" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="F92" s="8" t="s">
-        <v>261</v>
-      </c>
       <c r="G92" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H92" s="8" t="s">
         <v>154</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K92" s="75"/>
-      <c r="L92" s="81"/>
+        <v>257</v>
+      </c>
+      <c r="K92" s="68"/>
+      <c r="L92" s="71"/>
       <c r="M92" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N92" s="7"/>
       <c r="O92" s="7"/>
@@ -11604,31 +11601,31 @@
         <v>204</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K93" s="75"/>
-      <c r="L93" s="81"/>
+        <v>257</v>
+      </c>
+      <c r="K93" s="68"/>
+      <c r="L93" s="71"/>
       <c r="M93" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N93" s="7"/>
       <c r="O93" s="7"/>
@@ -11642,29 +11639,29 @@
         <v>204</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G94" s="27" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H94" s="26" t="s">
         <v>155</v>
       </c>
       <c r="I94" s="27"/>
       <c r="J94" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K94" s="79"/>
-      <c r="L94" s="82"/>
+        <v>257</v>
+      </c>
+      <c r="K94" s="69"/>
+      <c r="L94" s="72"/>
       <c r="M94" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N94" s="7"/>
       <c r="O94" s="7"/>
@@ -11678,16 +11675,16 @@
         <v>52</v>
       </c>
       <c r="C95" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E95" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>52</v>
@@ -11697,12 +11694,12 @@
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K95" s="65"/>
+        <v>257</v>
+      </c>
+      <c r="K95" s="73"/>
       <c r="L95" s="22"/>
       <c r="M95" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N95" s="7"/>
       <c r="O95" s="7"/>
@@ -11716,16 +11713,16 @@
         <v>52</v>
       </c>
       <c r="C96" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D96" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="E96" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="F96" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>256</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>52</v>
@@ -11735,12 +11732,12 @@
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K96" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K96" s="74"/>
       <c r="L96" s="22"/>
       <c r="M96" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N96" s="7"/>
       <c r="O96" s="7"/>
@@ -11754,16 +11751,16 @@
         <v>52</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D97" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E97" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="F97" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>52</v>
@@ -11773,12 +11770,12 @@
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K97" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K97" s="74"/>
       <c r="L97" s="22"/>
       <c r="M97" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
@@ -11792,16 +11789,16 @@
         <v>52</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>52</v>
@@ -11811,12 +11808,12 @@
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="K98" s="66"/>
+        <v>257</v>
+      </c>
+      <c r="K98" s="74"/>
       <c r="L98" s="22"/>
       <c r="M98" s="24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
@@ -11830,14 +11827,14 @@
         <v>52</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>52</v>
@@ -11847,12 +11844,12 @@
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="K99" s="70"/>
+        <v>257</v>
+      </c>
+      <c r="K99" s="75"/>
       <c r="L99" s="37"/>
       <c r="M99" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N99" s="7"/>
       <c r="O99" s="7"/>
@@ -11878,6 +11875,28 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="K63:K66"/>
+    <mergeCell ref="K69:K70"/>
     <mergeCell ref="K91:K94"/>
     <mergeCell ref="L91:L94"/>
     <mergeCell ref="K95:K99"/>
@@ -11886,28 +11905,6 @@
     <mergeCell ref="L77:L80"/>
     <mergeCell ref="K81:K82"/>
     <mergeCell ref="K85:K90"/>
-    <mergeCell ref="K50:K54"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="K63:K66"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="K20:K24"/>
-    <mergeCell ref="L20:L24"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11927,15 +11924,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="7" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>232</v>
@@ -11943,7 +11940,7 @@
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>149</v>
@@ -14803,7 +14800,7 @@
   <cols>
     <col min="1" max="1" width="11.140625" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="84" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="66" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="100.5703125" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14814,7 +14811,7 @@
       <c r="B1" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="65" t="s">
         <v>152</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -14828,7 +14825,7 @@
       <c r="B2" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="65" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -14842,7 +14839,7 @@
       <c r="B3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="83">
+      <c r="C3" s="65">
         <v>1000</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -14856,7 +14853,7 @@
       <c r="B4" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="65">
         <v>1000</v>
       </c>
       <c r="D4" s="18" t="s">
@@ -14870,7 +14867,7 @@
       <c r="B5" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5" s="65">
         <v>1E-3</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -14884,7 +14881,7 @@
       <c r="B6" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="65" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -14898,7 +14895,7 @@
       <c r="B7" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="83">
+      <c r="C7" s="65">
         <v>1000</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -14912,7 +14909,7 @@
       <c r="B8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="65">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -14926,7 +14923,7 @@
       <c r="B9" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="65">
         <v>1</v>
       </c>
       <c r="D9" s="7"/>
@@ -14938,7 +14935,7 @@
       <c r="B10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="83">
+      <c r="C10" s="65">
         <v>1</v>
       </c>
       <c r="D10" s="7"/>
@@ -14950,7 +14947,7 @@
       <c r="B11" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="65">
         <v>1</v>
       </c>
       <c r="D11" s="7"/>
@@ -14962,7 +14959,7 @@
       <c r="B12" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12" s="65">
         <v>1</v>
       </c>
       <c r="D12" s="7"/>
@@ -14974,7 +14971,7 @@
       <c r="B13" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="83">
+      <c r="C13" s="65">
         <v>1</v>
       </c>
       <c r="D13" s="7"/>
@@ -14986,7 +14983,7 @@
       <c r="B14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="83">
+      <c r="C14" s="65">
         <v>1E-3</v>
       </c>
       <c r="D14" s="7"/>
@@ -14998,7 +14995,7 @@
       <c r="B15" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="83">
+      <c r="C15" s="65">
         <v>1</v>
       </c>
       <c r="D15" s="7"/>
@@ -15010,7 +15007,7 @@
       <c r="B16" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="83">
+      <c r="C16" s="65">
         <v>1000</v>
       </c>
       <c r="D16" s="7"/>
@@ -15022,7 +15019,7 @@
       <c r="B17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17" s="65">
         <v>1000</v>
       </c>
       <c r="D17" s="7"/>
@@ -15034,7 +15031,7 @@
       <c r="B18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="83">
+      <c r="C18" s="65">
         <v>1</v>
       </c>
       <c r="D18" s="7"/>
@@ -15046,7 +15043,7 @@
       <c r="B19" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="83">
+      <c r="C19" s="65">
         <v>1</v>
       </c>
       <c r="D19" s="7"/>
@@ -15058,7 +15055,7 @@
       <c r="B20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="83">
+      <c r="C20" s="65">
         <v>1000</v>
       </c>
       <c r="D20" s="7"/>
@@ -15070,7 +15067,7 @@
       <c r="B21" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="83">
+      <c r="C21" s="65">
         <v>1000</v>
       </c>
       <c r="D21" s="7"/>
@@ -15082,7 +15079,7 @@
       <c r="B22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="83">
+      <c r="C22" s="65">
         <v>1000</v>
       </c>
       <c r="D22" s="7"/>
@@ -15094,7 +15091,7 @@
       <c r="B23" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="83">
+      <c r="C23" s="65">
         <v>1</v>
       </c>
       <c r="D23" s="7"/>
@@ -15106,7 +15103,7 @@
       <c r="B24" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="83">
+      <c r="C24" s="65">
         <v>1</v>
       </c>
       <c r="D24" s="7"/>
@@ -15118,7 +15115,7 @@
       <c r="B25" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="83">
+      <c r="C25" s="65">
         <v>1</v>
       </c>
       <c r="D25" s="7"/>
@@ -15130,7 +15127,7 @@
       <c r="B26" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="83">
+      <c r="C26" s="65">
         <v>1.33</v>
       </c>
       <c r="D26" s="7"/>

--- a/Meta/Analytes3.xlsx
+++ b/Meta/Analytes3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/vitense_kelsey_epa_gov/Documents/GL_Data/Meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAF63563-9F10-47A8-8CF6-A13C21A25AE4}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E5D6A43-EF34-47DA-8DD4-B826B6962B6A}"/>
   <bookViews>
-    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="693">
   <si>
     <t>ANALYTE</t>
   </si>
@@ -2131,6 +2131,12 @@
   </si>
   <si>
     <t>PAR</t>
+  </si>
+  <si>
+    <t>ftu</t>
+  </si>
+  <si>
+    <t>ntu</t>
   </si>
 </sst>
 </file>
@@ -2611,35 +2617,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2647,10 +2629,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2664,6 +2646,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8086,8 +8092,8 @@
       <c r="J2" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="77"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="69"/>
       <c r="M2" s="24" t="s">
         <v>257</v>
       </c>
@@ -8124,8 +8130,8 @@
       <c r="J3" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K3" s="74"/>
-      <c r="L3" s="78"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="70"/>
       <c r="M3" s="9" t="s">
         <v>257</v>
       </c>
@@ -8162,8 +8168,8 @@
       <c r="J4" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K4" s="74"/>
-      <c r="L4" s="78"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="9" t="s">
         <v>257</v>
       </c>
@@ -8198,8 +8204,8 @@
       <c r="J5" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="74"/>
-      <c r="L5" s="78"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="70"/>
       <c r="M5" s="9" t="s">
         <v>257</v>
       </c>
@@ -8236,10 +8242,10 @@
       <c r="J6" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K6" s="76" t="s">
+      <c r="K6" s="71" t="s">
         <v>267</v>
       </c>
-      <c r="L6" s="81"/>
+      <c r="L6" s="73"/>
       <c r="M6" s="9" t="s">
         <v>257</v>
       </c>
@@ -8276,8 +8282,8 @@
       <c r="J7" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K7" s="74"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="74"/>
       <c r="M7" s="9" t="s">
         <v>257</v>
       </c>
@@ -8312,8 +8318,8 @@
       <c r="J8" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="83"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="75"/>
       <c r="M8" s="9" t="s">
         <v>257</v>
       </c>
@@ -8350,10 +8356,10 @@
       <c r="J9" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K9" s="84" t="s">
+      <c r="K9" s="76" t="s">
         <v>275</v>
       </c>
-      <c r="L9" s="79" t="s">
+      <c r="L9" s="78" t="s">
         <v>276</v>
       </c>
       <c r="M9" s="24" t="s">
@@ -8392,8 +8398,8 @@
       <c r="J10" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="78"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="70"/>
       <c r="M10" s="9" t="s">
         <v>257</v>
       </c>
@@ -8430,8 +8436,8 @@
       <c r="J11" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K11" s="68"/>
-      <c r="L11" s="78"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="70"/>
       <c r="M11" s="9" t="s">
         <v>257</v>
       </c>
@@ -8710,7 +8716,7 @@
       <c r="J18" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K18" s="76"/>
+      <c r="K18" s="71"/>
       <c r="L18" s="22"/>
       <c r="M18" s="9" t="s">
         <v>257</v>
@@ -8748,7 +8754,7 @@
       <c r="J19" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K19" s="75"/>
+      <c r="K19" s="72"/>
       <c r="L19" s="44"/>
       <c r="M19" s="27" t="s">
         <v>257</v>
@@ -8786,10 +8792,10 @@
       <c r="J20" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K20" s="76" t="s">
+      <c r="K20" s="71" t="s">
         <v>310</v>
       </c>
-      <c r="L20" s="79" t="s">
+      <c r="L20" s="78" t="s">
         <v>311</v>
       </c>
       <c r="M20" s="9" t="s">
@@ -8828,8 +8834,8 @@
       <c r="J21" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K21" s="74"/>
-      <c r="L21" s="78"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="70"/>
       <c r="M21" s="9" t="s">
         <v>257</v>
       </c>
@@ -8864,8 +8870,8 @@
       <c r="J22" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K22" s="74"/>
-      <c r="L22" s="78"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="70"/>
       <c r="M22" s="9" t="s">
         <v>257</v>
       </c>
@@ -8902,8 +8908,8 @@
       <c r="J23" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K23" s="74"/>
-      <c r="L23" s="78"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="70"/>
       <c r="M23" s="9" t="s">
         <v>257</v>
       </c>
@@ -8940,8 +8946,8 @@
       <c r="J24" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K24" s="74"/>
-      <c r="L24" s="78"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="70"/>
       <c r="M24" s="9" t="s">
         <v>257</v>
       </c>
@@ -8978,10 +8984,10 @@
       <c r="J25" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="67" t="s">
         <v>317</v>
       </c>
-      <c r="L25" s="77" t="s">
+      <c r="L25" s="69" t="s">
         <v>318</v>
       </c>
       <c r="M25" s="24" t="s">
@@ -9020,8 +9026,8 @@
       <c r="J26" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K26" s="74"/>
-      <c r="L26" s="78"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="70"/>
       <c r="M26" s="9" t="s">
         <v>257</v>
       </c>
@@ -9058,8 +9064,8 @@
       <c r="J27" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K27" s="74"/>
-      <c r="L27" s="78"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="70"/>
       <c r="M27" s="9" t="s">
         <v>257</v>
       </c>
@@ -9094,8 +9100,8 @@
       <c r="J28" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K28" s="75"/>
-      <c r="L28" s="80"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="79"/>
       <c r="M28" s="27" t="s">
         <v>257</v>
       </c>
@@ -9132,7 +9138,7 @@
       <c r="J29" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K29" s="76" t="s">
+      <c r="K29" s="71" t="s">
         <v>323</v>
       </c>
       <c r="L29" s="22"/>
@@ -9172,7 +9178,7 @@
       <c r="J30" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K30" s="74"/>
+      <c r="K30" s="68"/>
       <c r="L30" s="22"/>
       <c r="M30" s="9" t="s">
         <v>257</v>
@@ -9210,7 +9216,7 @@
       <c r="J31" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K31" s="74"/>
+      <c r="K31" s="68"/>
       <c r="L31" s="22"/>
       <c r="M31" s="9" t="s">
         <v>257</v>
@@ -9246,7 +9252,7 @@
       <c r="J32" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K32" s="74"/>
+      <c r="K32" s="68"/>
       <c r="L32" s="22"/>
       <c r="M32" s="9" t="s">
         <v>257</v>
@@ -9284,7 +9290,7 @@
       <c r="J33" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K33" s="73" t="s">
+      <c r="K33" s="67" t="s">
         <v>290</v>
       </c>
       <c r="L33" s="43" t="s">
@@ -9326,7 +9332,7 @@
       <c r="J34" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K34" s="75"/>
+      <c r="K34" s="72"/>
       <c r="L34" s="44"/>
       <c r="M34" s="27" t="s">
         <v>257</v>
@@ -9364,7 +9370,7 @@
       <c r="J35" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K35" s="76" t="s">
+      <c r="K35" s="71" t="s">
         <v>290</v>
       </c>
       <c r="L35" s="22" t="s">
@@ -9406,7 +9412,7 @@
       <c r="J36" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K36" s="74"/>
+      <c r="K36" s="68"/>
       <c r="L36" s="22"/>
       <c r="M36" s="9" t="s">
         <v>257</v>
@@ -9523,7 +9529,7 @@
       <c r="K39" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="L39" s="77"/>
+      <c r="L39" s="69"/>
       <c r="M39" s="24" t="s">
         <v>257</v>
       </c>
@@ -9561,7 +9567,7 @@
         <v>257</v>
       </c>
       <c r="K40" s="35"/>
-      <c r="L40" s="78"/>
+      <c r="L40" s="70"/>
       <c r="M40" s="9" t="s">
         <v>257</v>
       </c>
@@ -9640,10 +9646,10 @@
       <c r="J42" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K42" s="76" t="s">
+      <c r="K42" s="71" t="s">
         <v>347</v>
       </c>
-      <c r="L42" s="79" t="s">
+      <c r="L42" s="78" t="s">
         <v>348</v>
       </c>
       <c r="M42" s="24" t="s">
@@ -9682,8 +9688,8 @@
       <c r="J43" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K43" s="74"/>
-      <c r="L43" s="78"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="70"/>
       <c r="M43" s="9" t="s">
         <v>257</v>
       </c>
@@ -9720,8 +9726,8 @@
       <c r="J44" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K44" s="74"/>
-      <c r="L44" s="78"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="70"/>
       <c r="M44" s="9" t="s">
         <v>257</v>
       </c>
@@ -9756,8 +9762,8 @@
       <c r="J45" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K45" s="74"/>
-      <c r="L45" s="78"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="70"/>
       <c r="M45" s="9" t="s">
         <v>257</v>
       </c>
@@ -9794,8 +9800,8 @@
       <c r="J46" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K46" s="74"/>
-      <c r="L46" s="78"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="70"/>
       <c r="M46" s="9" t="s">
         <v>257</v>
       </c>
@@ -9832,8 +9838,8 @@
       <c r="J47" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K47" s="74"/>
-      <c r="L47" s="78"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="70"/>
       <c r="M47" s="9" t="s">
         <v>257</v>
       </c>
@@ -9950,7 +9956,7 @@
       <c r="J50" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="67" t="s">
+      <c r="K50" s="80" t="s">
         <v>361</v>
       </c>
       <c r="L50" s="43"/>
@@ -9990,7 +9996,7 @@
       <c r="J51" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K51" s="68"/>
+      <c r="K51" s="77"/>
       <c r="L51" s="22"/>
       <c r="M51" s="24" t="s">
         <v>257</v>
@@ -10028,7 +10034,7 @@
       <c r="J52" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K52" s="68"/>
+      <c r="K52" s="77"/>
       <c r="L52" s="22"/>
       <c r="M52" s="24" t="s">
         <v>257</v>
@@ -10066,7 +10072,7 @@
       <c r="J53" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K53" s="68"/>
+      <c r="K53" s="77"/>
       <c r="L53" s="22"/>
       <c r="M53" s="24" t="s">
         <v>257</v>
@@ -10102,7 +10108,7 @@
       <c r="J54" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K54" s="69"/>
+      <c r="K54" s="81"/>
       <c r="L54" s="44"/>
       <c r="M54" s="24" t="s">
         <v>257</v>
@@ -10222,7 +10228,7 @@
       <c r="J57" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K57" s="76" t="s">
+      <c r="K57" s="71" t="s">
         <v>378</v>
       </c>
       <c r="L57" s="22"/>
@@ -10262,7 +10268,7 @@
       <c r="J58" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K58" s="74"/>
+      <c r="K58" s="68"/>
       <c r="L58" s="22"/>
       <c r="M58" s="9" t="s">
         <v>257</v>
@@ -10298,7 +10304,7 @@
       <c r="J59" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K59" s="74"/>
+      <c r="K59" s="68"/>
       <c r="L59" s="22"/>
       <c r="M59" s="9" t="s">
         <v>257</v>
@@ -10336,7 +10342,7 @@
       <c r="J60" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="K60" s="77" t="s">
+      <c r="K60" s="69" t="s">
         <v>383</v>
       </c>
       <c r="L60" s="43"/>
@@ -10376,7 +10382,7 @@
       <c r="J61" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K61" s="78"/>
+      <c r="K61" s="70"/>
       <c r="L61" s="22" t="s">
         <v>385</v>
       </c>
@@ -10416,7 +10422,7 @@
       <c r="J62" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K62" s="78"/>
+      <c r="K62" s="70"/>
       <c r="L62" s="22" t="s">
         <v>387</v>
       </c>
@@ -10456,7 +10462,7 @@
       <c r="J63" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K63" s="76"/>
+      <c r="K63" s="71"/>
       <c r="L63" s="22"/>
       <c r="M63" s="9" t="s">
         <v>257</v>
@@ -10494,7 +10500,7 @@
       <c r="J64" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K64" s="74"/>
+      <c r="K64" s="68"/>
       <c r="L64" s="22"/>
       <c r="M64" s="9" t="s">
         <v>257</v>
@@ -10532,7 +10538,7 @@
       <c r="J65" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K65" s="74"/>
+      <c r="K65" s="68"/>
       <c r="L65" s="22" t="s">
         <v>387</v>
       </c>
@@ -10570,7 +10576,7 @@
       <c r="J66" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K66" s="74"/>
+      <c r="K66" s="68"/>
       <c r="L66" s="13"/>
       <c r="M66" s="34" t="s">
         <v>257</v>
@@ -10684,7 +10690,7 @@
       <c r="J69" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K69" s="76" t="s">
+      <c r="K69" s="71" t="s">
         <v>290</v>
       </c>
       <c r="L69" s="22" t="s">
@@ -10726,7 +10732,7 @@
       <c r="J70" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K70" s="74"/>
+      <c r="K70" s="68"/>
       <c r="L70" s="22"/>
       <c r="M70" s="9" t="s">
         <v>257</v>
@@ -10804,7 +10810,7 @@
       <c r="J72" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K72" s="76"/>
+      <c r="K72" s="71"/>
       <c r="L72" s="22"/>
       <c r="M72" s="9" t="s">
         <v>257</v>
@@ -10840,7 +10846,7 @@
       <c r="J73" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K73" s="74"/>
+      <c r="K73" s="68"/>
       <c r="L73" s="22"/>
       <c r="M73" s="9" t="s">
         <v>257</v>
@@ -10876,7 +10882,7 @@
       <c r="J74" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K74" s="74"/>
+      <c r="K74" s="68"/>
       <c r="L74" s="22"/>
       <c r="M74" s="9" t="s">
         <v>257</v>
@@ -10910,7 +10916,7 @@
       <c r="J75" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K75" s="75"/>
+      <c r="K75" s="72"/>
       <c r="L75" s="44"/>
       <c r="M75" s="9" t="s">
         <v>257</v>
@@ -10988,10 +10994,10 @@
       <c r="J77" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K77" s="67" t="s">
+      <c r="K77" s="80" t="s">
         <v>410</v>
       </c>
-      <c r="L77" s="73" t="s">
+      <c r="L77" s="67" t="s">
         <v>411</v>
       </c>
       <c r="M77" s="24" t="s">
@@ -11032,8 +11038,8 @@
       <c r="J78" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K78" s="69"/>
-      <c r="L78" s="71"/>
+      <c r="K78" s="81"/>
+      <c r="L78" s="83"/>
       <c r="M78" s="34" t="s">
         <v>257</v>
       </c>
@@ -11073,7 +11079,7 @@
       <c r="K79" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L79" s="71"/>
+      <c r="L79" s="83"/>
       <c r="M79" s="34" t="s">
         <v>257</v>
       </c>
@@ -11113,7 +11119,7 @@
       <c r="K80" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L80" s="75"/>
+      <c r="L80" s="72"/>
       <c r="M80" s="9" t="s">
         <v>257</v>
       </c>
@@ -11150,7 +11156,7 @@
       <c r="J81" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K81" s="76" t="s">
+      <c r="K81" s="71" t="s">
         <v>290</v>
       </c>
       <c r="L81" s="22" t="s">
@@ -11192,7 +11198,7 @@
       <c r="J82" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K82" s="74"/>
+      <c r="K82" s="68"/>
       <c r="L82" s="22"/>
       <c r="M82" s="9" t="s">
         <v>257</v>
@@ -11314,7 +11320,7 @@
       <c r="J85" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K85" s="76" t="s">
+      <c r="K85" s="71" t="s">
         <v>424</v>
       </c>
       <c r="L85" s="22"/>
@@ -11354,7 +11360,7 @@
       <c r="J86" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K86" s="74"/>
+      <c r="K86" s="68"/>
       <c r="L86" s="22"/>
       <c r="M86" s="9" t="s">
         <v>257</v>
@@ -11392,7 +11398,7 @@
       <c r="J87" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K87" s="74"/>
+      <c r="K87" s="68"/>
       <c r="L87" s="22"/>
       <c r="M87" s="9" t="s">
         <v>257</v>
@@ -11428,7 +11434,7 @@
       <c r="J88" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K88" s="74"/>
+      <c r="K88" s="68"/>
       <c r="L88" s="22"/>
       <c r="M88" s="9" t="s">
         <v>257</v>
@@ -11466,7 +11472,7 @@
       <c r="J89" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K89" s="74"/>
+      <c r="K89" s="68"/>
       <c r="L89" s="22"/>
       <c r="M89" s="9" t="s">
         <v>257</v>
@@ -11504,7 +11510,7 @@
       <c r="J90" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K90" s="74"/>
+      <c r="K90" s="68"/>
       <c r="L90" s="22"/>
       <c r="M90" s="9" t="s">
         <v>257</v>
@@ -11542,10 +11548,10 @@
       <c r="J91" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K91" s="67" t="s">
+      <c r="K91" s="80" t="s">
         <v>430</v>
       </c>
-      <c r="L91" s="70" t="s">
+      <c r="L91" s="82" t="s">
         <v>431</v>
       </c>
       <c r="M91" s="24" t="s">
@@ -11584,8 +11590,8 @@
       <c r="J92" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K92" s="68"/>
-      <c r="L92" s="71"/>
+      <c r="K92" s="77"/>
+      <c r="L92" s="83"/>
       <c r="M92" s="9" t="s">
         <v>257</v>
       </c>
@@ -11622,8 +11628,8 @@
       <c r="J93" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K93" s="68"/>
-      <c r="L93" s="71"/>
+      <c r="K93" s="77"/>
+      <c r="L93" s="83"/>
       <c r="M93" s="9" t="s">
         <v>257</v>
       </c>
@@ -11658,8 +11664,8 @@
       <c r="J94" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K94" s="69"/>
-      <c r="L94" s="72"/>
+      <c r="K94" s="81"/>
+      <c r="L94" s="84"/>
       <c r="M94" s="9" t="s">
         <v>257</v>
       </c>
@@ -11696,7 +11702,7 @@
       <c r="J95" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K95" s="73"/>
+      <c r="K95" s="67"/>
       <c r="L95" s="22"/>
       <c r="M95" s="24" t="s">
         <v>257</v>
@@ -11734,7 +11740,7 @@
       <c r="J96" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K96" s="74"/>
+      <c r="K96" s="68"/>
       <c r="L96" s="22"/>
       <c r="M96" s="24" t="s">
         <v>257</v>
@@ -11772,7 +11778,7 @@
       <c r="J97" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K97" s="74"/>
+      <c r="K97" s="68"/>
       <c r="L97" s="22"/>
       <c r="M97" s="24" t="s">
         <v>257</v>
@@ -11810,7 +11816,7 @@
       <c r="J98" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K98" s="74"/>
+      <c r="K98" s="68"/>
       <c r="L98" s="22"/>
       <c r="M98" s="24" t="s">
         <v>257</v>
@@ -11846,7 +11852,7 @@
       <c r="J99" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K99" s="75"/>
+      <c r="K99" s="72"/>
       <c r="L99" s="37"/>
       <c r="M99" s="39" t="s">
         <v>257</v>
@@ -11875,28 +11881,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="K20:K24"/>
-    <mergeCell ref="L20:L24"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="K50:K54"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="K63:K66"/>
-    <mergeCell ref="K69:K70"/>
     <mergeCell ref="K91:K94"/>
     <mergeCell ref="L91:L94"/>
     <mergeCell ref="K95:K99"/>
@@ -11905,6 +11889,28 @@
     <mergeCell ref="L77:L80"/>
     <mergeCell ref="K81:K82"/>
     <mergeCell ref="K85:K90"/>
+    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="K63:K66"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14820,10 +14826,10 @@
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>154</v>
+        <v>691</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>155</v>
+        <v>692</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>12</v>
@@ -14876,10 +14882,10 @@
     </row>
     <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>155</v>
+        <v>692</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>154</v>
+        <v>691</v>
       </c>
       <c r="C6" s="65" t="s">
         <v>12</v>

--- a/Meta/Analytes3.xlsx
+++ b/Meta/Analytes3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/vitense_kelsey_epa_gov/Documents/GL_Data/Meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E5D6A43-EF34-47DA-8DD4-B826B6962B6A}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C1EC90-6557-4C8E-BDFB-3B17394C2A46}"/>
   <bookViews>
-    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="695">
   <si>
     <t>ANALYTE</t>
   </si>
@@ -2137,6 +2137,12 @@
   </si>
   <si>
     <t>ntu</t>
+  </si>
+  <si>
+    <t>Note that all rows with Methods in this spreadsheet came from non-GL lakes. GL lake Methods are NA for all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These are derived variables in code (from nitrate and nitrite). </t>
   </si>
 </sst>
 </file>
@@ -2617,11 +2623,35 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2629,10 +2659,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2646,30 +2676,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8092,8 +8098,8 @@
       <c r="J2" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="67"/>
-      <c r="L2" s="69"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="77"/>
       <c r="M2" s="24" t="s">
         <v>257</v>
       </c>
@@ -8130,8 +8136,8 @@
       <c r="J3" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K3" s="68"/>
-      <c r="L3" s="70"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="78"/>
       <c r="M3" s="9" t="s">
         <v>257</v>
       </c>
@@ -8168,8 +8174,8 @@
       <c r="J4" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K4" s="68"/>
-      <c r="L4" s="70"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="78"/>
       <c r="M4" s="9" t="s">
         <v>257</v>
       </c>
@@ -8204,8 +8210,8 @@
       <c r="J5" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="68"/>
-      <c r="L5" s="70"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="78"/>
       <c r="M5" s="9" t="s">
         <v>257</v>
       </c>
@@ -8242,10 +8248,10 @@
       <c r="J6" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K6" s="71" t="s">
+      <c r="K6" s="76" t="s">
         <v>267</v>
       </c>
-      <c r="L6" s="73"/>
+      <c r="L6" s="81"/>
       <c r="M6" s="9" t="s">
         <v>257</v>
       </c>
@@ -8282,8 +8288,8 @@
       <c r="J7" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K7" s="68"/>
-      <c r="L7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="82"/>
       <c r="M7" s="9" t="s">
         <v>257</v>
       </c>
@@ -8318,8 +8324,8 @@
       <c r="J8" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K8" s="72"/>
-      <c r="L8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="83"/>
       <c r="M8" s="9" t="s">
         <v>257</v>
       </c>
@@ -8356,10 +8362,10 @@
       <c r="J9" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K9" s="76" t="s">
+      <c r="K9" s="84" t="s">
         <v>275</v>
       </c>
-      <c r="L9" s="78" t="s">
+      <c r="L9" s="79" t="s">
         <v>276</v>
       </c>
       <c r="M9" s="24" t="s">
@@ -8398,8 +8404,8 @@
       <c r="J10" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K10" s="77"/>
-      <c r="L10" s="70"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="78"/>
       <c r="M10" s="9" t="s">
         <v>257</v>
       </c>
@@ -8436,8 +8442,8 @@
       <c r="J11" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K11" s="77"/>
-      <c r="L11" s="70"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="78"/>
       <c r="M11" s="9" t="s">
         <v>257</v>
       </c>
@@ -8716,7 +8722,7 @@
       <c r="J18" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K18" s="71"/>
+      <c r="K18" s="76"/>
       <c r="L18" s="22"/>
       <c r="M18" s="9" t="s">
         <v>257</v>
@@ -8754,7 +8760,7 @@
       <c r="J19" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K19" s="72"/>
+      <c r="K19" s="75"/>
       <c r="L19" s="44"/>
       <c r="M19" s="27" t="s">
         <v>257</v>
@@ -8792,10 +8798,10 @@
       <c r="J20" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K20" s="71" t="s">
+      <c r="K20" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="L20" s="78" t="s">
+      <c r="L20" s="79" t="s">
         <v>311</v>
       </c>
       <c r="M20" s="9" t="s">
@@ -8834,8 +8840,8 @@
       <c r="J21" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K21" s="68"/>
-      <c r="L21" s="70"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="78"/>
       <c r="M21" s="9" t="s">
         <v>257</v>
       </c>
@@ -8870,8 +8876,8 @@
       <c r="J22" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K22" s="68"/>
-      <c r="L22" s="70"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="78"/>
       <c r="M22" s="9" t="s">
         <v>257</v>
       </c>
@@ -8908,8 +8914,8 @@
       <c r="J23" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K23" s="68"/>
-      <c r="L23" s="70"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="78"/>
       <c r="M23" s="9" t="s">
         <v>257</v>
       </c>
@@ -8946,8 +8952,8 @@
       <c r="J24" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K24" s="68"/>
-      <c r="L24" s="70"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="78"/>
       <c r="M24" s="9" t="s">
         <v>257</v>
       </c>
@@ -8984,10 +8990,10 @@
       <c r="J25" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="L25" s="69" t="s">
+      <c r="L25" s="77" t="s">
         <v>318</v>
       </c>
       <c r="M25" s="24" t="s">
@@ -9026,8 +9032,8 @@
       <c r="J26" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K26" s="68"/>
-      <c r="L26" s="70"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="78"/>
       <c r="M26" s="9" t="s">
         <v>257</v>
       </c>
@@ -9064,8 +9070,8 @@
       <c r="J27" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K27" s="68"/>
-      <c r="L27" s="70"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="78"/>
       <c r="M27" s="9" t="s">
         <v>257</v>
       </c>
@@ -9100,8 +9106,8 @@
       <c r="J28" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K28" s="72"/>
-      <c r="L28" s="79"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="27" t="s">
         <v>257</v>
       </c>
@@ -9138,7 +9144,7 @@
       <c r="J29" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K29" s="71" t="s">
+      <c r="K29" s="76" t="s">
         <v>323</v>
       </c>
       <c r="L29" s="22"/>
@@ -9178,7 +9184,7 @@
       <c r="J30" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K30" s="68"/>
+      <c r="K30" s="74"/>
       <c r="L30" s="22"/>
       <c r="M30" s="9" t="s">
         <v>257</v>
@@ -9216,7 +9222,7 @@
       <c r="J31" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K31" s="68"/>
+      <c r="K31" s="74"/>
       <c r="L31" s="22"/>
       <c r="M31" s="9" t="s">
         <v>257</v>
@@ -9252,7 +9258,7 @@
       <c r="J32" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K32" s="68"/>
+      <c r="K32" s="74"/>
       <c r="L32" s="22"/>
       <c r="M32" s="9" t="s">
         <v>257</v>
@@ -9290,7 +9296,7 @@
       <c r="J33" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K33" s="67" t="s">
+      <c r="K33" s="73" t="s">
         <v>290</v>
       </c>
       <c r="L33" s="43" t="s">
@@ -9332,7 +9338,7 @@
       <c r="J34" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K34" s="72"/>
+      <c r="K34" s="75"/>
       <c r="L34" s="44"/>
       <c r="M34" s="27" t="s">
         <v>257</v>
@@ -9370,7 +9376,7 @@
       <c r="J35" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K35" s="71" t="s">
+      <c r="K35" s="76" t="s">
         <v>290</v>
       </c>
       <c r="L35" s="22" t="s">
@@ -9412,7 +9418,7 @@
       <c r="J36" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K36" s="68"/>
+      <c r="K36" s="74"/>
       <c r="L36" s="22"/>
       <c r="M36" s="9" t="s">
         <v>257</v>
@@ -9529,7 +9535,7 @@
       <c r="K39" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="L39" s="69"/>
+      <c r="L39" s="77"/>
       <c r="M39" s="24" t="s">
         <v>257</v>
       </c>
@@ -9567,7 +9573,7 @@
         <v>257</v>
       </c>
       <c r="K40" s="35"/>
-      <c r="L40" s="70"/>
+      <c r="L40" s="78"/>
       <c r="M40" s="9" t="s">
         <v>257</v>
       </c>
@@ -9646,10 +9652,10 @@
       <c r="J42" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K42" s="71" t="s">
+      <c r="K42" s="76" t="s">
         <v>347</v>
       </c>
-      <c r="L42" s="78" t="s">
+      <c r="L42" s="79" t="s">
         <v>348</v>
       </c>
       <c r="M42" s="24" t="s">
@@ -9688,8 +9694,8 @@
       <c r="J43" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K43" s="68"/>
-      <c r="L43" s="70"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="78"/>
       <c r="M43" s="9" t="s">
         <v>257</v>
       </c>
@@ -9726,8 +9732,8 @@
       <c r="J44" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K44" s="68"/>
-      <c r="L44" s="70"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="78"/>
       <c r="M44" s="9" t="s">
         <v>257</v>
       </c>
@@ -9762,8 +9768,8 @@
       <c r="J45" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K45" s="68"/>
-      <c r="L45" s="70"/>
+      <c r="K45" s="74"/>
+      <c r="L45" s="78"/>
       <c r="M45" s="9" t="s">
         <v>257</v>
       </c>
@@ -9800,8 +9806,8 @@
       <c r="J46" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K46" s="68"/>
-      <c r="L46" s="70"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="78"/>
       <c r="M46" s="9" t="s">
         <v>257</v>
       </c>
@@ -9838,8 +9844,8 @@
       <c r="J47" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K47" s="68"/>
-      <c r="L47" s="70"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="78"/>
       <c r="M47" s="9" t="s">
         <v>257</v>
       </c>
@@ -9956,7 +9962,7 @@
       <c r="J50" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="80" t="s">
+      <c r="K50" s="67" t="s">
         <v>361</v>
       </c>
       <c r="L50" s="43"/>
@@ -9996,7 +10002,7 @@
       <c r="J51" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K51" s="77"/>
+      <c r="K51" s="68"/>
       <c r="L51" s="22"/>
       <c r="M51" s="24" t="s">
         <v>257</v>
@@ -10034,7 +10040,7 @@
       <c r="J52" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K52" s="77"/>
+      <c r="K52" s="68"/>
       <c r="L52" s="22"/>
       <c r="M52" s="24" t="s">
         <v>257</v>
@@ -10072,7 +10078,7 @@
       <c r="J53" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K53" s="77"/>
+      <c r="K53" s="68"/>
       <c r="L53" s="22"/>
       <c r="M53" s="24" t="s">
         <v>257</v>
@@ -10108,7 +10114,7 @@
       <c r="J54" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K54" s="81"/>
+      <c r="K54" s="69"/>
       <c r="L54" s="44"/>
       <c r="M54" s="24" t="s">
         <v>257</v>
@@ -10228,7 +10234,7 @@
       <c r="J57" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K57" s="71" t="s">
+      <c r="K57" s="76" t="s">
         <v>378</v>
       </c>
       <c r="L57" s="22"/>
@@ -10268,7 +10274,7 @@
       <c r="J58" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K58" s="68"/>
+      <c r="K58" s="74"/>
       <c r="L58" s="22"/>
       <c r="M58" s="9" t="s">
         <v>257</v>
@@ -10304,7 +10310,7 @@
       <c r="J59" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K59" s="68"/>
+      <c r="K59" s="74"/>
       <c r="L59" s="22"/>
       <c r="M59" s="9" t="s">
         <v>257</v>
@@ -10342,7 +10348,7 @@
       <c r="J60" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="K60" s="69" t="s">
+      <c r="K60" s="77" t="s">
         <v>383</v>
       </c>
       <c r="L60" s="43"/>
@@ -10382,7 +10388,7 @@
       <c r="J61" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K61" s="70"/>
+      <c r="K61" s="78"/>
       <c r="L61" s="22" t="s">
         <v>385</v>
       </c>
@@ -10422,7 +10428,7 @@
       <c r="J62" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K62" s="70"/>
+      <c r="K62" s="78"/>
       <c r="L62" s="22" t="s">
         <v>387</v>
       </c>
@@ -10462,7 +10468,7 @@
       <c r="J63" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K63" s="71"/>
+      <c r="K63" s="76"/>
       <c r="L63" s="22"/>
       <c r="M63" s="9" t="s">
         <v>257</v>
@@ -10500,7 +10506,7 @@
       <c r="J64" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K64" s="68"/>
+      <c r="K64" s="74"/>
       <c r="L64" s="22"/>
       <c r="M64" s="9" t="s">
         <v>257</v>
@@ -10538,7 +10544,7 @@
       <c r="J65" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K65" s="68"/>
+      <c r="K65" s="74"/>
       <c r="L65" s="22" t="s">
         <v>387</v>
       </c>
@@ -10576,7 +10582,7 @@
       <c r="J66" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K66" s="68"/>
+      <c r="K66" s="74"/>
       <c r="L66" s="13"/>
       <c r="M66" s="34" t="s">
         <v>257</v>
@@ -10690,7 +10696,7 @@
       <c r="J69" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K69" s="71" t="s">
+      <c r="K69" s="76" t="s">
         <v>290</v>
       </c>
       <c r="L69" s="22" t="s">
@@ -10732,7 +10738,7 @@
       <c r="J70" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K70" s="68"/>
+      <c r="K70" s="74"/>
       <c r="L70" s="22"/>
       <c r="M70" s="9" t="s">
         <v>257</v>
@@ -10810,7 +10816,7 @@
       <c r="J72" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K72" s="71"/>
+      <c r="K72" s="76"/>
       <c r="L72" s="22"/>
       <c r="M72" s="9" t="s">
         <v>257</v>
@@ -10846,7 +10852,7 @@
       <c r="J73" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K73" s="68"/>
+      <c r="K73" s="74"/>
       <c r="L73" s="22"/>
       <c r="M73" s="9" t="s">
         <v>257</v>
@@ -10882,7 +10888,7 @@
       <c r="J74" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K74" s="68"/>
+      <c r="K74" s="74"/>
       <c r="L74" s="22"/>
       <c r="M74" s="9" t="s">
         <v>257</v>
@@ -10916,7 +10922,7 @@
       <c r="J75" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K75" s="72"/>
+      <c r="K75" s="75"/>
       <c r="L75" s="44"/>
       <c r="M75" s="9" t="s">
         <v>257</v>
@@ -10994,10 +11000,10 @@
       <c r="J77" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K77" s="80" t="s">
+      <c r="K77" s="67" t="s">
         <v>410</v>
       </c>
-      <c r="L77" s="67" t="s">
+      <c r="L77" s="73" t="s">
         <v>411</v>
       </c>
       <c r="M77" s="24" t="s">
@@ -11038,8 +11044,8 @@
       <c r="J78" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K78" s="81"/>
-      <c r="L78" s="83"/>
+      <c r="K78" s="69"/>
+      <c r="L78" s="71"/>
       <c r="M78" s="34" t="s">
         <v>257</v>
       </c>
@@ -11079,7 +11085,7 @@
       <c r="K79" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L79" s="83"/>
+      <c r="L79" s="71"/>
       <c r="M79" s="34" t="s">
         <v>257</v>
       </c>
@@ -11119,7 +11125,7 @@
       <c r="K80" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L80" s="72"/>
+      <c r="L80" s="75"/>
       <c r="M80" s="9" t="s">
         <v>257</v>
       </c>
@@ -11156,7 +11162,7 @@
       <c r="J81" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K81" s="71" t="s">
+      <c r="K81" s="76" t="s">
         <v>290</v>
       </c>
       <c r="L81" s="22" t="s">
@@ -11198,7 +11204,7 @@
       <c r="J82" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K82" s="68"/>
+      <c r="K82" s="74"/>
       <c r="L82" s="22"/>
       <c r="M82" s="9" t="s">
         <v>257</v>
@@ -11320,7 +11326,7 @@
       <c r="J85" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K85" s="71" t="s">
+      <c r="K85" s="76" t="s">
         <v>424</v>
       </c>
       <c r="L85" s="22"/>
@@ -11360,7 +11366,7 @@
       <c r="J86" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K86" s="68"/>
+      <c r="K86" s="74"/>
       <c r="L86" s="22"/>
       <c r="M86" s="9" t="s">
         <v>257</v>
@@ -11398,7 +11404,7 @@
       <c r="J87" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K87" s="68"/>
+      <c r="K87" s="74"/>
       <c r="L87" s="22"/>
       <c r="M87" s="9" t="s">
         <v>257</v>
@@ -11434,7 +11440,7 @@
       <c r="J88" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K88" s="68"/>
+      <c r="K88" s="74"/>
       <c r="L88" s="22"/>
       <c r="M88" s="9" t="s">
         <v>257</v>
@@ -11472,7 +11478,7 @@
       <c r="J89" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K89" s="68"/>
+      <c r="K89" s="74"/>
       <c r="L89" s="22"/>
       <c r="M89" s="9" t="s">
         <v>257</v>
@@ -11510,7 +11516,7 @@
       <c r="J90" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K90" s="68"/>
+      <c r="K90" s="74"/>
       <c r="L90" s="22"/>
       <c r="M90" s="9" t="s">
         <v>257</v>
@@ -11548,10 +11554,10 @@
       <c r="J91" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K91" s="80" t="s">
+      <c r="K91" s="67" t="s">
         <v>430</v>
       </c>
-      <c r="L91" s="82" t="s">
+      <c r="L91" s="70" t="s">
         <v>431</v>
       </c>
       <c r="M91" s="24" t="s">
@@ -11590,8 +11596,8 @@
       <c r="J92" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K92" s="77"/>
-      <c r="L92" s="83"/>
+      <c r="K92" s="68"/>
+      <c r="L92" s="71"/>
       <c r="M92" s="9" t="s">
         <v>257</v>
       </c>
@@ -11628,8 +11634,8 @@
       <c r="J93" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K93" s="77"/>
-      <c r="L93" s="83"/>
+      <c r="K93" s="68"/>
+      <c r="L93" s="71"/>
       <c r="M93" s="9" t="s">
         <v>257</v>
       </c>
@@ -11664,8 +11670,8 @@
       <c r="J94" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K94" s="81"/>
-      <c r="L94" s="84"/>
+      <c r="K94" s="69"/>
+      <c r="L94" s="72"/>
       <c r="M94" s="9" t="s">
         <v>257</v>
       </c>
@@ -11702,7 +11708,7 @@
       <c r="J95" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K95" s="67"/>
+      <c r="K95" s="73"/>
       <c r="L95" s="22"/>
       <c r="M95" s="24" t="s">
         <v>257</v>
@@ -11740,7 +11746,7 @@
       <c r="J96" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K96" s="68"/>
+      <c r="K96" s="74"/>
       <c r="L96" s="22"/>
       <c r="M96" s="24" t="s">
         <v>257</v>
@@ -11778,7 +11784,7 @@
       <c r="J97" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K97" s="68"/>
+      <c r="K97" s="74"/>
       <c r="L97" s="22"/>
       <c r="M97" s="24" t="s">
         <v>257</v>
@@ -11816,7 +11822,7 @@
       <c r="J98" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K98" s="68"/>
+      <c r="K98" s="74"/>
       <c r="L98" s="22"/>
       <c r="M98" s="24" t="s">
         <v>257</v>
@@ -11852,7 +11858,7 @@
       <c r="J99" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K99" s="72"/>
+      <c r="K99" s="75"/>
       <c r="L99" s="37"/>
       <c r="M99" s="39" t="s">
         <v>257</v>
@@ -11881,6 +11887,28 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="K63:K66"/>
+    <mergeCell ref="K69:K70"/>
     <mergeCell ref="K91:K94"/>
     <mergeCell ref="L91:L94"/>
     <mergeCell ref="K95:K99"/>
@@ -11889,28 +11917,6 @@
     <mergeCell ref="L77:L80"/>
     <mergeCell ref="K81:K82"/>
     <mergeCell ref="K85:K90"/>
-    <mergeCell ref="K50:K54"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="K63:K66"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="K20:K24"/>
-    <mergeCell ref="L20:L24"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13060,7 +13066,9 @@
         <v>21</v>
       </c>
       <c r="H26" s="21"/>
-      <c r="I26" s="13"/>
+      <c r="I26" s="13" t="s">
+        <v>693</v>
+      </c>
       <c r="J26" s="13"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
@@ -14279,7 +14287,7 @@
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13" t="s">
-        <v>191</v>
+        <v>694</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -14312,7 +14320,7 @@
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13" t="s">
-        <v>191</v>
+        <v>694</v>
       </c>
       <c r="J59" s="13"/>
       <c r="K59" s="13"/>

--- a/Meta/Analytes3.xlsx
+++ b/Meta/Analytes3.xlsx
@@ -1,34 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/vitense_kelsey_epa_gov/Documents/GL_Data/Meta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C1EC90-6557-4C8E-BDFB-3B17394C2A46}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="11_CFA7FA0AC8BEC675FF6906A82B7A2EC91D13FE60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE1B4470-4E3A-4B0C-BEE3-D1DC7161497A}"/>
   <bookViews>
-    <workbookView xWindow="-61548" yWindow="-1872" windowWidth="30936" windowHeight="16776" tabRatio="802" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata" sheetId="11" r:id="rId1"/>
-    <sheet name="Key" sheetId="1" r:id="rId2"/>
-    <sheet name="CSMI_Map" sheetId="2" r:id="rId3"/>
-    <sheet name="NOAA_Map" sheetId="3" r:id="rId4"/>
-    <sheet name="GLENDA_Map" sheetId="4" r:id="rId5"/>
-    <sheet name="GLENDA_mdl_Map" sheetId="6" r:id="rId6"/>
-    <sheet name="SeaBird_Map" sheetId="7" r:id="rId7"/>
-    <sheet name="NCCA_Map" sheetId="8" r:id="rId8"/>
-    <sheet name="UnitConversions" sheetId="9" r:id="rId9"/>
+    <sheet name="Key" sheetId="1" r:id="rId1"/>
+    <sheet name="CSMI_Map" sheetId="2" r:id="rId2"/>
+    <sheet name="NOAA_Map" sheetId="3" r:id="rId3"/>
+    <sheet name="GLENDA_Map" sheetId="4" r:id="rId4"/>
+    <sheet name="GLENDA_mdl_Map" sheetId="6" r:id="rId5"/>
+    <sheet name="SeaBird_Map" sheetId="7" r:id="rId6"/>
+    <sheet name="NCCA_Map" sheetId="8" r:id="rId7"/>
+    <sheet name="UnitConversions" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">CSMI_Map!$H$1:$H$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">GLENDA_Map!$B$1:$M$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Key!$A$1:$A$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7">NCCA_Map!$A$1:$A$57</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="1">Key!$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">CSMI_Map!$H$1:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">GLENDA_Map!$B$1:$M$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Key!$A$1:$A$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">NCCA_Map!$A$1:$A$57</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="0">Key!$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="639">
   <si>
     <t>ANALYTE</t>
   </si>
@@ -1950,159 +1949,6 @@
     <t>Remove because no surface PAR to compute CPAR</t>
   </si>
   <si>
-    <t>Lake Michigan Water quality data compiled across multiple studies.</t>
-  </si>
-  <si>
-    <t> and NOAA data sources. The variables are as follows:</t>
-  </si>
-  <si>
-    <t>format: A data frame with 309210 rows and 28 variables:</t>
-  </si>
-  <si>
-    <t>UID</t>
-  </si>
-  <si>
-    <t>Unique ID across all sources</t>
-  </si>
-  <si>
-    <t>Name of study</t>
-  </si>
-  <si>
-    <t>Name of site</t>
-  </si>
-  <si>
-    <t>SITE_ID</t>
-  </si>
-  <si>
-    <t>Latitude in degreees decimals (41.66336--55.30979)</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Longitude in degreees decimals (41.66336--55.30979)</t>
-  </si>
-  <si>
-    <t>stationDepth</t>
-  </si>
-  <si>
-    <t>Depth in meters of the station / site (0.2--273.4056)</t>
-  </si>
-  <si>
-    <t>sampleDateTime</t>
-  </si>
-  <si>
-    <t>Date time of sampling event (1983/04/19 12:00:00 UTC--2023/08/05 04:14:54 UTC)</t>
-  </si>
-  <si>
-    <t>sampleDepth</t>
-  </si>
-  <si>
-    <t>Depth at which sample was taken (0.1--258.5)</t>
-  </si>
-  <si>
-    <t>Unified, unique names for all of the measured quantities along with units separated by underscore. (Examples: Diss_Cl, Tot_P, DOC)</t>
-  </si>
-  <si>
-    <t>Unified, unique full names for all of the measured quantities.</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>Value of the measurement.</t>
-  </si>
-  <si>
-    <t>MDL</t>
-  </si>
-  <si>
-    <t>Method detection limit. Matched per analyte, method, study, and year when available.</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>Reporting limit. Matched per analyte, method, study, and year when available.</t>
-  </si>
-  <si>
-    <t>Unified_Flag</t>
-  </si>
-  <si>
-    <t>Unified qc flag to relate quality of the corresponding measurement.</t>
-  </si>
-  <si>
-    <t>Unified_Comment</t>
-  </si>
-  <si>
-    <t>Unified qc comment to relate quality of the corresponding measurement.</t>
-  </si>
-  <si>
-    <t>METHOD</t>
-  </si>
-  <si>
-    <t>LAB</t>
-  </si>
-  <si>
-    <t>Orig_QAcode</t>
-  </si>
-  <si>
-    <t>QA code in the original data source</t>
-  </si>
-  <si>
-    <t>Orig_QAcomment</t>
-  </si>
-  <si>
-    <t>QA comment in the original data source</t>
-  </si>
-  <si>
-    <t>Orig_QAdefinition</t>
-  </si>
-  <si>
-    <t>QA definition in the original data source</t>
-  </si>
-  <si>
-    <t>ANALYTE_Orig_Name</t>
-  </si>
-  <si>
-    <t>ANALYTE name in the original data source</t>
-  </si>
-  <si>
-    <t>Measurement units in the original data source</t>
-  </si>
-  <si>
-    <t>Desired measurement units for the output data</t>
-  </si>
-  <si>
-    <t>Multiplicative conversion factor if conversion is necessary to convert from ReportedUnits to TargetUnits</t>
-  </si>
-  <si>
-    <t>Retain_InternalUse</t>
-  </si>
-  <si>
-    <t>Action_InternalUse</t>
-  </si>
-  <si>
-    <t>A dataset containing water quality measurements from NCCA, CSMI, GLNPO,</t>
-  </si>
-  <si>
-    <t>Analyte category inspired by LAGOS</t>
-  </si>
-  <si>
-    <t>Associated measurement method, where available.</t>
-  </si>
-  <si>
-    <t>Associated lab taking measurement, where available.</t>
-  </si>
-  <si>
-    <t>Internal decision on what data to retain based on QC flags - PROBABLY DELETE THIS IN FINAL VERSION</t>
-  </si>
-  <si>
-    <t>Verbose description of decision made off of qa flags - PROBABLY DELETE THIS IN FINAL VESION</t>
-  </si>
-  <si>
     <t>This is at the very surface with a hand held thermometer.  It's pretty sensitive to air temp/solar heating, but is a back up for when the CTD does not work or is not dropped.</t>
   </si>
   <si>
@@ -2113,21 +1959,6 @@
   </si>
   <si>
     <t>SiO2</t>
-  </si>
-  <si>
-    <t>sampleDate</t>
-  </si>
-  <si>
-    <t>sampleTime</t>
-  </si>
-  <si>
-    <t>Date of sampling event (1983/04/19--2023/08/05)</t>
-  </si>
-  <si>
-    <t>Hour of sampling event. Missing if time was not recorded</t>
-  </si>
-  <si>
-    <t>Units of associated measurement.</t>
   </si>
   <si>
     <t>PAR</t>
@@ -2149,7 +1980,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2181,24 +2012,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF6A9955"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2429,7 +2242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2608,38 +2421,11 @@
     <xf numFmtId="3" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2647,22 +2433,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2676,6 +2456,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2978,287 +2782,767 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944E5B29-DA5B-4213-9FBD-6DB720F31476}">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="64"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="64"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="64"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
-        <v>633</v>
-      </c>
-      <c r="B8" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
-        <v>637</v>
-      </c>
-      <c r="B10" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
-        <v>639</v>
-      </c>
-      <c r="B11" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
-        <v>640</v>
-      </c>
-      <c r="B12" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
-        <v>642</v>
-      </c>
-      <c r="B13" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>685</v>
-      </c>
-      <c r="B14" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
-        <v>686</v>
-      </c>
-      <c r="B15" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="64" t="s">
-        <v>644</v>
-      </c>
-      <c r="B16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
-        <v>646</v>
-      </c>
-      <c r="B17" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B18" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="B1" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="B19" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
-        <v>650</v>
-      </c>
-      <c r="B20" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="64" t="s">
+      <c r="C1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="B21" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
-        <v>652</v>
-      </c>
-      <c r="B22" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
-        <v>654</v>
-      </c>
-      <c r="B23" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>656</v>
-      </c>
-      <c r="B24" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
-        <v>658</v>
-      </c>
-      <c r="B25" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="64" t="s">
-        <v>567</v>
-      </c>
-      <c r="B26" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
-        <v>660</v>
-      </c>
-      <c r="B27" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="64" t="s">
-        <v>661</v>
-      </c>
-      <c r="B28" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
-        <v>662</v>
-      </c>
-      <c r="B29" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
-        <v>664</v>
-      </c>
-      <c r="B30" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
-        <v>666</v>
-      </c>
-      <c r="B31" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
-        <v>668</v>
-      </c>
-      <c r="B32" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="B34" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="64" t="s">
-        <v>152</v>
-      </c>
-      <c r="B35" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="64" t="s">
-        <v>673</v>
-      </c>
-      <c r="B36" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="64" t="s">
-        <v>674</v>
-      </c>
-      <c r="B37" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="62"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="63"/>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>584</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B20" s="59" t="s">
+        <v>588</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>592</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B30" s="59" t="s">
+        <v>598</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>155</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3266,796 +3550,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>581</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>584</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B20" s="59" t="s">
-        <v>588</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B24" s="59" t="s">
-        <v>592</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="B30" s="59" t="s">
-        <v>598</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L127"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="75.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="64.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
         <v>76</v>
       </c>
@@ -4093,7 +3609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="165" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>75</v>
       </c>
@@ -4125,7 +3641,7 @@
       </c>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>75</v>
       </c>
@@ -4157,7 +3673,7 @@
       </c>
       <c r="L3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>75</v>
       </c>
@@ -4185,7 +3701,7 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
     </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>75</v>
       </c>
@@ -4213,7 +3729,7 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
     </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>75</v>
       </c>
@@ -4241,7 +3757,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>75</v>
       </c>
@@ -4271,7 +3787,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>75</v>
       </c>
@@ -4301,7 +3817,7 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>75</v>
       </c>
@@ -4331,7 +3847,7 @@
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>75</v>
       </c>
@@ -4359,7 +3875,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>75</v>
       </c>
@@ -4387,7 +3903,7 @@
       </c>
       <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>75</v>
       </c>
@@ -4417,7 +3933,7 @@
       </c>
       <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>75</v>
       </c>
@@ -4447,7 +3963,7 @@
       </c>
       <c r="L13" s="13"/>
     </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -4477,7 +3993,7 @@
       </c>
       <c r="L14" s="13"/>
     </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -4505,7 +4021,7 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>75</v>
       </c>
@@ -4533,7 +4049,7 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>75</v>
       </c>
@@ -4561,7 +4077,7 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
     </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>75</v>
       </c>
@@ -4589,7 +4105,7 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
     </row>
-    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>75</v>
       </c>
@@ -4617,7 +4133,7 @@
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
     </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>75</v>
       </c>
@@ -4649,7 +4165,7 @@
       </c>
       <c r="L20" s="13"/>
     </row>
-    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>75</v>
       </c>
@@ -4681,7 +4197,7 @@
       </c>
       <c r="L21" s="13"/>
     </row>
-    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>75</v>
       </c>
@@ -4709,7 +4225,7 @@
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
     </row>
-    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>75</v>
       </c>
@@ -4741,7 +4257,7 @@
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>75</v>
       </c>
@@ -4771,7 +4287,7 @@
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
     </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>75</v>
       </c>
@@ -4799,7 +4315,7 @@
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
     </row>
-    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>75</v>
       </c>
@@ -4827,7 +4343,7 @@
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
     </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>75</v>
       </c>
@@ -4857,7 +4373,7 @@
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
     </row>
-    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>75</v>
       </c>
@@ -4885,7 +4401,7 @@
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
     </row>
-    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>75</v>
       </c>
@@ -4913,7 +4429,7 @@
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>75</v>
       </c>
@@ -4945,7 +4461,7 @@
       </c>
       <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>75</v>
       </c>
@@ -4977,7 +4493,7 @@
       </c>
       <c r="L31" s="13"/>
     </row>
-    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>498</v>
       </c>
@@ -5007,7 +4523,7 @@
       </c>
       <c r="L32" s="13"/>
     </row>
-    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>498</v>
       </c>
@@ -5037,7 +4553,7 @@
       </c>
       <c r="L33" s="13"/>
     </row>
-    <row r="34" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>498</v>
       </c>
@@ -5063,7 +4579,7 @@
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
     </row>
-    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>498</v>
       </c>
@@ -5093,7 +4609,7 @@
       </c>
       <c r="L35" s="13"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>498</v>
       </c>
@@ -5123,7 +4639,7 @@
       </c>
       <c r="L36" s="13"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>498</v>
       </c>
@@ -5153,7 +4669,7 @@
       </c>
       <c r="L37" s="13"/>
     </row>
-    <row r="38" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>498</v>
       </c>
@@ -5183,7 +4699,7 @@
       </c>
       <c r="L38" s="13"/>
     </row>
-    <row r="39" spans="1:12" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>498</v>
       </c>
@@ -5209,7 +4725,7 @@
       </c>
       <c r="L39" s="13"/>
     </row>
-    <row r="40" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>498</v>
       </c>
@@ -5239,7 +4755,7 @@
       </c>
       <c r="L40" s="13"/>
     </row>
-    <row r="41" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>498</v>
       </c>
@@ -5269,7 +4785,7 @@
       </c>
       <c r="L41" s="13"/>
     </row>
-    <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>498</v>
       </c>
@@ -5297,7 +4813,7 @@
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
     </row>
-    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>498</v>
       </c>
@@ -5323,7 +4839,7 @@
       <c r="K43" s="13"/>
       <c r="L43" s="13"/>
     </row>
-    <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>498</v>
       </c>
@@ -5351,7 +4867,7 @@
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
     </row>
-    <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>498</v>
       </c>
@@ -5379,7 +4895,7 @@
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
     </row>
-    <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>498</v>
       </c>
@@ -5407,7 +4923,7 @@
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
     </row>
-    <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>498</v>
       </c>
@@ -5435,7 +4951,7 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13"/>
     </row>
-    <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>498</v>
       </c>
@@ -5463,7 +4979,7 @@
       <c r="K48" s="13"/>
       <c r="L48" s="13"/>
     </row>
-    <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>498</v>
       </c>
@@ -5491,7 +5007,7 @@
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
     </row>
-    <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>498</v>
       </c>
@@ -5517,7 +5033,7 @@
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
     </row>
-    <row r="51" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>498</v>
       </c>
@@ -5545,7 +5061,7 @@
       </c>
       <c r="L51" s="13"/>
     </row>
-    <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>498</v>
       </c>
@@ -5571,7 +5087,7 @@
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
     </row>
-    <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>498</v>
       </c>
@@ -5597,7 +5113,7 @@
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
     </row>
-    <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>498</v>
       </c>
@@ -5623,7 +5139,7 @@
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
     </row>
-    <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>498</v>
       </c>
@@ -5649,7 +5165,7 @@
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
     </row>
-    <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>498</v>
       </c>
@@ -5675,7 +5191,7 @@
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
     </row>
-    <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>498</v>
       </c>
@@ -5701,7 +5217,7 @@
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
     </row>
-    <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>498</v>
       </c>
@@ -5727,7 +5243,7 @@
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
     </row>
-    <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>498</v>
       </c>
@@ -5753,7 +5269,7 @@
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
     </row>
-    <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>498</v>
       </c>
@@ -5779,7 +5295,7 @@
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
     </row>
-    <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>498</v>
       </c>
@@ -5807,7 +5323,7 @@
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
     </row>
-    <row r="62" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>498</v>
       </c>
@@ -5835,7 +5351,7 @@
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
     </row>
-    <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>498</v>
       </c>
@@ -5861,7 +5377,7 @@
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
     </row>
-    <row r="64" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>498</v>
       </c>
@@ -5891,7 +5407,7 @@
       </c>
       <c r="L64" s="13"/>
     </row>
-    <row r="65" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>498</v>
       </c>
@@ -5917,7 +5433,7 @@
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
     </row>
-    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>498</v>
       </c>
@@ -5943,7 +5459,7 @@
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
     </row>
-    <row r="67" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>498</v>
       </c>
@@ -5969,7 +5485,7 @@
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
     </row>
-    <row r="68" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>498</v>
       </c>
@@ -5995,7 +5511,7 @@
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
     </row>
-    <row r="69" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>498</v>
       </c>
@@ -6021,7 +5537,7 @@
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
     </row>
-    <row r="70" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>498</v>
       </c>
@@ -6049,7 +5565,7 @@
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
     </row>
-    <row r="71" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>498</v>
       </c>
@@ -6077,7 +5593,7 @@
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
     </row>
-    <row r="72" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>498</v>
       </c>
@@ -6099,7 +5615,7 @@
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
     </row>
-    <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>498</v>
       </c>
@@ -6127,7 +5643,7 @@
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
     </row>
-    <row r="74" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
         <v>498</v>
       </c>
@@ -6149,7 +5665,7 @@
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
     </row>
-    <row r="75" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>498</v>
       </c>
@@ -6175,7 +5691,7 @@
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
     </row>
-    <row r="76" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>498</v>
       </c>
@@ -6201,7 +5717,7 @@
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
     </row>
-    <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>498</v>
       </c>
@@ -6229,7 +5745,7 @@
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
     </row>
-    <row r="78" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>540</v>
       </c>
@@ -6257,7 +5773,7 @@
       <c r="K78" s="25"/>
       <c r="L78" s="13"/>
     </row>
-    <row r="79" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>540</v>
       </c>
@@ -6285,7 +5801,7 @@
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
     </row>
-    <row r="80" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
         <v>540</v>
       </c>
@@ -6313,7 +5829,7 @@
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
     </row>
-    <row r="81" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>540</v>
       </c>
@@ -6341,7 +5857,7 @@
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
     </row>
-    <row r="82" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>540</v>
       </c>
@@ -6369,7 +5885,7 @@
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
     </row>
-    <row r="83" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>540</v>
       </c>
@@ -6397,7 +5913,7 @@
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
     </row>
-    <row r="84" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
         <v>540</v>
       </c>
@@ -6425,7 +5941,7 @@
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
     </row>
-    <row r="85" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>540</v>
       </c>
@@ -6453,7 +5969,7 @@
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
     </row>
-    <row r="86" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
         <v>540</v>
       </c>
@@ -6481,7 +5997,7 @@
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
     </row>
-    <row r="87" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>540</v>
       </c>
@@ -6509,7 +6025,7 @@
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
     </row>
-    <row r="88" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
         <v>540</v>
       </c>
@@ -6537,7 +6053,7 @@
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
     </row>
-    <row r="89" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>540</v>
       </c>
@@ -6565,7 +6081,7 @@
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
     </row>
-    <row r="90" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>540</v>
       </c>
@@ -6597,7 +6113,7 @@
       </c>
       <c r="L90" s="13"/>
     </row>
-    <row r="91" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>540</v>
       </c>
@@ -6629,7 +6145,7 @@
       </c>
       <c r="L91" s="13"/>
     </row>
-    <row r="92" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>540</v>
       </c>
@@ -6655,7 +6171,7 @@
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
     </row>
-    <row r="93" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>74</v>
       </c>
@@ -6683,7 +6199,7 @@
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
     </row>
-    <row r="94" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>74</v>
       </c>
@@ -6711,7 +6227,7 @@
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
     </row>
-    <row r="95" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>74</v>
       </c>
@@ -6739,7 +6255,7 @@
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
     </row>
-    <row r="96" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>74</v>
       </c>
@@ -6767,7 +6283,7 @@
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
     </row>
-    <row r="97" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>74</v>
       </c>
@@ -6795,7 +6311,7 @@
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
     </row>
-    <row r="98" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>74</v>
       </c>
@@ -6823,7 +6339,7 @@
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
     </row>
-    <row r="99" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>74</v>
       </c>
@@ -6851,7 +6367,7 @@
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
     </row>
-    <row r="100" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>74</v>
       </c>
@@ -6879,7 +6395,7 @@
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
     </row>
-    <row r="101" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>74</v>
       </c>
@@ -6907,7 +6423,7 @@
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
     </row>
-    <row r="102" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>74</v>
       </c>
@@ -6935,7 +6451,7 @@
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
     </row>
-    <row r="103" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>74</v>
       </c>
@@ -6963,7 +6479,7 @@
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
     </row>
-    <row r="104" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>74</v>
       </c>
@@ -6991,7 +6507,7 @@
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
     </row>
-    <row r="105" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>74</v>
       </c>
@@ -7019,7 +6535,7 @@
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
     </row>
-    <row r="106" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>74</v>
       </c>
@@ -7047,7 +6563,7 @@
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
     </row>
-    <row r="107" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>74</v>
       </c>
@@ -7075,7 +6591,7 @@
       <c r="K107" s="13"/>
       <c r="L107" s="13"/>
     </row>
-    <row r="108" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>74</v>
       </c>
@@ -7109,7 +6625,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>74</v>
       </c>
@@ -7143,7 +6659,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>74</v>
       </c>
@@ -7177,7 +6693,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>74</v>
       </c>
@@ -7211,7 +6727,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>74</v>
       </c>
@@ -7245,7 +6761,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>74</v>
       </c>
@@ -7279,7 +6795,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>74</v>
       </c>
@@ -7307,7 +6823,7 @@
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
     </row>
-    <row r="115" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>74</v>
       </c>
@@ -7335,7 +6851,7 @@
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
     </row>
-    <row r="116" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>74</v>
       </c>
@@ -7363,7 +6879,7 @@
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
     </row>
-    <row r="117" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>74</v>
       </c>
@@ -7391,7 +6907,7 @@
       <c r="K117" s="13"/>
       <c r="L117" s="13"/>
     </row>
-    <row r="118" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>74</v>
       </c>
@@ -7419,7 +6935,7 @@
       <c r="K118" s="13"/>
       <c r="L118" s="13"/>
     </row>
-    <row r="119" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>74</v>
       </c>
@@ -7449,7 +6965,7 @@
       <c r="K119" s="13"/>
       <c r="L119" s="13"/>
     </row>
-    <row r="120" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
         <v>74</v>
       </c>
@@ -7477,7 +6993,7 @@
       <c r="K120" s="13"/>
       <c r="L120" s="13"/>
     </row>
-    <row r="121" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>74</v>
       </c>
@@ -7505,7 +7021,7 @@
       <c r="K121" s="13"/>
       <c r="L121" s="13"/>
     </row>
-    <row r="122" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
         <v>74</v>
       </c>
@@ -7537,7 +7053,7 @@
       </c>
       <c r="L122" s="13"/>
     </row>
-    <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>74</v>
       </c>
@@ -7567,7 +7083,7 @@
       </c>
       <c r="L123" s="13"/>
     </row>
-    <row r="124" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>74</v>
       </c>
@@ -7597,7 +7113,7 @@
       </c>
       <c r="L124" s="13"/>
     </row>
-    <row r="125" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>74</v>
       </c>
@@ -7627,7 +7143,7 @@
       </c>
       <c r="L125" s="13"/>
     </row>
-    <row r="126" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
         <v>74</v>
       </c>
@@ -7655,7 +7171,7 @@
       <c r="K126" s="13"/>
       <c r="L126" s="13"/>
     </row>
-    <row r="127" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>74</v>
       </c>
@@ -7682,6 +7198,322 @@
       <c r="J127" s="13"/>
       <c r="K127" s="13"/>
       <c r="L127" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>438</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>629</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7689,343 +7521,27 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>682</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>438</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>690</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>629</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="51.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="8.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="51.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="8.6640625" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>76</v>
       </c>
@@ -8069,7 +7585,7 @@
       <c r="O1" s="29"/>
       <c r="P1" s="29"/>
     </row>
-    <row r="2" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>73</v>
       </c>
@@ -8098,8 +7614,8 @@
       <c r="J2" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="77"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="66"/>
       <c r="M2" s="24" t="s">
         <v>257</v>
       </c>
@@ -8107,7 +7623,7 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>73</v>
       </c>
@@ -8136,8 +7652,8 @@
       <c r="J3" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K3" s="74"/>
-      <c r="L3" s="78"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="67"/>
       <c r="M3" s="9" t="s">
         <v>257</v>
       </c>
@@ -8145,7 +7661,7 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
         <v>73</v>
       </c>
@@ -8174,8 +7690,8 @@
       <c r="J4" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K4" s="74"/>
-      <c r="L4" s="78"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="67"/>
       <c r="M4" s="9" t="s">
         <v>257</v>
       </c>
@@ -8183,7 +7699,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>73</v>
       </c>
@@ -8210,8 +7726,8 @@
       <c r="J5" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="74"/>
-      <c r="L5" s="78"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="67"/>
       <c r="M5" s="9" t="s">
         <v>257</v>
       </c>
@@ -8219,7 +7735,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>73</v>
       </c>
@@ -8248,10 +7764,10 @@
       <c r="J6" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K6" s="76" t="s">
+      <c r="K6" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="L6" s="81"/>
+      <c r="L6" s="70"/>
       <c r="M6" s="9" t="s">
         <v>257</v>
       </c>
@@ -8259,7 +7775,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>73</v>
       </c>
@@ -8288,8 +7804,8 @@
       <c r="J7" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K7" s="74"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="71"/>
       <c r="M7" s="9" t="s">
         <v>257</v>
       </c>
@@ -8297,7 +7813,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
         <v>73</v>
       </c>
@@ -8324,8 +7840,8 @@
       <c r="J8" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="83"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="72"/>
       <c r="M8" s="9" t="s">
         <v>257</v>
       </c>
@@ -8333,7 +7849,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>73</v>
       </c>
@@ -8362,10 +7878,10 @@
       <c r="J9" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K9" s="84" t="s">
+      <c r="K9" s="73" t="s">
         <v>275</v>
       </c>
-      <c r="L9" s="79" t="s">
+      <c r="L9" s="75" t="s">
         <v>276</v>
       </c>
       <c r="M9" s="24" t="s">
@@ -8375,7 +7891,7 @@
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>73</v>
       </c>
@@ -8404,8 +7920,8 @@
       <c r="J10" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="78"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="67"/>
       <c r="M10" s="9" t="s">
         <v>257</v>
       </c>
@@ -8413,7 +7929,7 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>73</v>
       </c>
@@ -8442,8 +7958,8 @@
       <c r="J11" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K11" s="68"/>
-      <c r="L11" s="78"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="67"/>
       <c r="M11" s="9" t="s">
         <v>257</v>
       </c>
@@ -8451,7 +7967,7 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>73</v>
       </c>
@@ -8491,7 +8007,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>73</v>
       </c>
@@ -8529,7 +8045,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
         <v>73</v>
       </c>
@@ -8571,7 +8087,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>73</v>
       </c>
@@ -8609,7 +8125,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>73</v>
       </c>
@@ -8651,7 +8167,7 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>73</v>
       </c>
@@ -8693,7 +8209,7 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
         <v>73</v>
       </c>
@@ -8722,7 +8238,7 @@
       <c r="J18" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K18" s="76"/>
+      <c r="K18" s="68"/>
       <c r="L18" s="22"/>
       <c r="M18" s="9" t="s">
         <v>257</v>
@@ -8731,7 +8247,7 @@
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
     </row>
-    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
         <v>73</v>
       </c>
@@ -8760,7 +8276,7 @@
       <c r="J19" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K19" s="75"/>
+      <c r="K19" s="69"/>
       <c r="L19" s="44"/>
       <c r="M19" s="27" t="s">
         <v>257</v>
@@ -8769,7 +8285,7 @@
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
     </row>
-    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>73</v>
       </c>
@@ -8798,10 +8314,10 @@
       <c r="J20" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K20" s="76" t="s">
+      <c r="K20" s="68" t="s">
         <v>310</v>
       </c>
-      <c r="L20" s="79" t="s">
+      <c r="L20" s="75" t="s">
         <v>311</v>
       </c>
       <c r="M20" s="9" t="s">
@@ -8811,7 +8327,7 @@
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
     </row>
-    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>73</v>
       </c>
@@ -8840,8 +8356,8 @@
       <c r="J21" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K21" s="74"/>
-      <c r="L21" s="78"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="67"/>
       <c r="M21" s="9" t="s">
         <v>257</v>
       </c>
@@ -8849,7 +8365,7 @@
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
     </row>
-    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>73</v>
       </c>
@@ -8876,8 +8392,8 @@
       <c r="J22" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K22" s="74"/>
-      <c r="L22" s="78"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="67"/>
       <c r="M22" s="9" t="s">
         <v>257</v>
       </c>
@@ -8885,7 +8401,7 @@
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
     </row>
-    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>73</v>
       </c>
@@ -8914,8 +8430,8 @@
       <c r="J23" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K23" s="74"/>
-      <c r="L23" s="78"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="67"/>
       <c r="M23" s="9" t="s">
         <v>257</v>
       </c>
@@ -8923,7 +8439,7 @@
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
     </row>
-    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>73</v>
       </c>
@@ -8952,8 +8468,8 @@
       <c r="J24" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K24" s="74"/>
-      <c r="L24" s="78"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="67"/>
       <c r="M24" s="9" t="s">
         <v>257</v>
       </c>
@@ -8961,7 +8477,7 @@
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
     </row>
-    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>73</v>
       </c>
@@ -8990,10 +8506,10 @@
       <c r="J25" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="64" t="s">
         <v>317</v>
       </c>
-      <c r="L25" s="77" t="s">
+      <c r="L25" s="66" t="s">
         <v>318</v>
       </c>
       <c r="M25" s="24" t="s">
@@ -9003,7 +8519,7 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
     </row>
-    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +8548,8 @@
       <c r="J26" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K26" s="74"/>
-      <c r="L26" s="78"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="67"/>
       <c r="M26" s="9" t="s">
         <v>257</v>
       </c>
@@ -9041,7 +8557,7 @@
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
     </row>
-    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>73</v>
       </c>
@@ -9070,8 +8586,8 @@
       <c r="J27" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K27" s="74"/>
-      <c r="L27" s="78"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="67"/>
       <c r="M27" s="9" t="s">
         <v>257</v>
       </c>
@@ -9079,7 +8595,7 @@
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
     </row>
-    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>73</v>
       </c>
@@ -9106,8 +8622,8 @@
       <c r="J28" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K28" s="75"/>
-      <c r="L28" s="80"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="76"/>
       <c r="M28" s="27" t="s">
         <v>257</v>
       </c>
@@ -9115,7 +8631,7 @@
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
     </row>
-    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>73</v>
       </c>
@@ -9144,7 +8660,7 @@
       <c r="J29" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K29" s="76" t="s">
+      <c r="K29" s="68" t="s">
         <v>323</v>
       </c>
       <c r="L29" s="22"/>
@@ -9155,7 +8671,7 @@
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
     </row>
-    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>73</v>
       </c>
@@ -9184,7 +8700,7 @@
       <c r="J30" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K30" s="74"/>
+      <c r="K30" s="65"/>
       <c r="L30" s="22"/>
       <c r="M30" s="9" t="s">
         <v>257</v>
@@ -9193,7 +8709,7 @@
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>73</v>
       </c>
@@ -9222,7 +8738,7 @@
       <c r="J31" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K31" s="74"/>
+      <c r="K31" s="65"/>
       <c r="L31" s="22"/>
       <c r="M31" s="9" t="s">
         <v>257</v>
@@ -9231,7 +8747,7 @@
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>73</v>
       </c>
@@ -9258,7 +8774,7 @@
       <c r="J32" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K32" s="74"/>
+      <c r="K32" s="65"/>
       <c r="L32" s="22"/>
       <c r="M32" s="9" t="s">
         <v>257</v>
@@ -9267,7 +8783,7 @@
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
     </row>
-    <row r="33" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>73</v>
       </c>
@@ -9296,7 +8812,7 @@
       <c r="J33" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K33" s="73" t="s">
+      <c r="K33" s="64" t="s">
         <v>290</v>
       </c>
       <c r="L33" s="43" t="s">
@@ -9309,7 +8825,7 @@
       <c r="O33" s="7"/>
       <c r="P33" s="7"/>
     </row>
-    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>73</v>
       </c>
@@ -9338,7 +8854,7 @@
       <c r="J34" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K34" s="75"/>
+      <c r="K34" s="69"/>
       <c r="L34" s="44"/>
       <c r="M34" s="27" t="s">
         <v>257</v>
@@ -9347,7 +8863,7 @@
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
     </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>73</v>
       </c>
@@ -9376,7 +8892,7 @@
       <c r="J35" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K35" s="76" t="s">
+      <c r="K35" s="68" t="s">
         <v>290</v>
       </c>
       <c r="L35" s="22" t="s">
@@ -9389,7 +8905,7 @@
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
     </row>
-    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>73</v>
       </c>
@@ -9418,7 +8934,7 @@
       <c r="J36" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K36" s="74"/>
+      <c r="K36" s="65"/>
       <c r="L36" s="22"/>
       <c r="M36" s="9" t="s">
         <v>257</v>
@@ -9427,7 +8943,7 @@
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
     </row>
-    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23" t="s">
         <v>73</v>
       </c>
@@ -9465,7 +8981,7 @@
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
     </row>
-    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
         <v>73</v>
       </c>
@@ -9503,7 +9019,7 @@
       <c r="O38" s="7"/>
       <c r="P38" s="7"/>
     </row>
-    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>73</v>
       </c>
@@ -9535,7 +9051,7 @@
       <c r="K39" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="L39" s="77"/>
+      <c r="L39" s="66"/>
       <c r="M39" s="24" t="s">
         <v>257</v>
       </c>
@@ -9543,7 +9059,7 @@
       <c r="O39" s="7"/>
       <c r="P39" s="7"/>
     </row>
-    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="23" t="s">
         <v>73</v>
       </c>
@@ -9573,7 +9089,7 @@
         <v>257</v>
       </c>
       <c r="K40" s="35"/>
-      <c r="L40" s="78"/>
+      <c r="L40" s="67"/>
       <c r="M40" s="9" t="s">
         <v>257</v>
       </c>
@@ -9581,7 +9097,7 @@
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
     </row>
-    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
         <v>73</v>
       </c>
@@ -9623,7 +9139,7 @@
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
     </row>
-    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>73</v>
       </c>
@@ -9652,10 +9168,10 @@
       <c r="J42" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K42" s="76" t="s">
+      <c r="K42" s="68" t="s">
         <v>347</v>
       </c>
-      <c r="L42" s="79" t="s">
+      <c r="L42" s="75" t="s">
         <v>348</v>
       </c>
       <c r="M42" s="24" t="s">
@@ -9665,7 +9181,7 @@
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
     </row>
-    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>73</v>
       </c>
@@ -9694,8 +9210,8 @@
       <c r="J43" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K43" s="74"/>
-      <c r="L43" s="78"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="67"/>
       <c r="M43" s="9" t="s">
         <v>257</v>
       </c>
@@ -9703,7 +9219,7 @@
       <c r="O43" s="7"/>
       <c r="P43" s="7"/>
     </row>
-    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23" t="s">
         <v>73</v>
       </c>
@@ -9732,8 +9248,8 @@
       <c r="J44" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K44" s="74"/>
-      <c r="L44" s="78"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="67"/>
       <c r="M44" s="9" t="s">
         <v>257</v>
       </c>
@@ -9741,7 +9257,7 @@
       <c r="O44" s="7"/>
       <c r="P44" s="7"/>
     </row>
-    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
         <v>73</v>
       </c>
@@ -9768,8 +9284,8 @@
       <c r="J45" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K45" s="74"/>
-      <c r="L45" s="78"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="67"/>
       <c r="M45" s="9" t="s">
         <v>257</v>
       </c>
@@ -9777,7 +9293,7 @@
       <c r="O45" s="7"/>
       <c r="P45" s="7"/>
     </row>
-    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>73</v>
       </c>
@@ -9806,8 +9322,8 @@
       <c r="J46" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K46" s="74"/>
-      <c r="L46" s="78"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="67"/>
       <c r="M46" s="9" t="s">
         <v>257</v>
       </c>
@@ -9815,7 +9331,7 @@
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
     </row>
-    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23" t="s">
         <v>73</v>
       </c>
@@ -9844,8 +9360,8 @@
       <c r="J47" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K47" s="74"/>
-      <c r="L47" s="78"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="67"/>
       <c r="M47" s="9" t="s">
         <v>257</v>
       </c>
@@ -9853,7 +9369,7 @@
       <c r="O47" s="7"/>
       <c r="P47" s="7"/>
     </row>
-    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
         <v>73</v>
       </c>
@@ -9895,7 +9411,7 @@
       <c r="O48" s="7"/>
       <c r="P48" s="7"/>
     </row>
-    <row r="49" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="23" t="s">
         <v>73</v>
       </c>
@@ -9933,7 +9449,7 @@
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
     </row>
-    <row r="50" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
         <v>73</v>
       </c>
@@ -9962,7 +9478,7 @@
       <c r="J50" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="67" t="s">
+      <c r="K50" s="77" t="s">
         <v>361</v>
       </c>
       <c r="L50" s="43"/>
@@ -9973,7 +9489,7 @@
       <c r="O50" s="7"/>
       <c r="P50" s="7"/>
     </row>
-    <row r="51" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23" t="s">
         <v>73</v>
       </c>
@@ -10002,7 +9518,7 @@
       <c r="J51" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K51" s="68"/>
+      <c r="K51" s="74"/>
       <c r="L51" s="22"/>
       <c r="M51" s="24" t="s">
         <v>257</v>
@@ -10011,7 +9527,7 @@
       <c r="O51" s="7"/>
       <c r="P51" s="7"/>
     </row>
-    <row r="52" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>73</v>
       </c>
@@ -10040,7 +9556,7 @@
       <c r="J52" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K52" s="68"/>
+      <c r="K52" s="74"/>
       <c r="L52" s="22"/>
       <c r="M52" s="24" t="s">
         <v>257</v>
@@ -10049,7 +9565,7 @@
       <c r="O52" s="7"/>
       <c r="P52" s="7"/>
     </row>
-    <row r="53" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="23" t="s">
         <v>73</v>
       </c>
@@ -10078,7 +9594,7 @@
       <c r="J53" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K53" s="68"/>
+      <c r="K53" s="74"/>
       <c r="L53" s="22"/>
       <c r="M53" s="24" t="s">
         <v>257</v>
@@ -10087,7 +9603,7 @@
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
     </row>
-    <row r="54" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>73</v>
       </c>
@@ -10114,7 +9630,7 @@
       <c r="J54" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K54" s="69"/>
+      <c r="K54" s="78"/>
       <c r="L54" s="44"/>
       <c r="M54" s="24" t="s">
         <v>257</v>
@@ -10123,7 +9639,7 @@
       <c r="O54" s="7"/>
       <c r="P54" s="7"/>
     </row>
-    <row r="55" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>73</v>
       </c>
@@ -10165,7 +9681,7 @@
       <c r="O55" s="7"/>
       <c r="P55" s="7"/>
     </row>
-    <row r="56" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
         <v>73</v>
       </c>
@@ -10205,7 +9721,7 @@
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
     </row>
-    <row r="57" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>73</v>
       </c>
@@ -10234,7 +9750,7 @@
       <c r="J57" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K57" s="76" t="s">
+      <c r="K57" s="68" t="s">
         <v>378</v>
       </c>
       <c r="L57" s="22"/>
@@ -10245,7 +9761,7 @@
       <c r="O57" s="7"/>
       <c r="P57" s="7"/>
     </row>
-    <row r="58" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>73</v>
       </c>
@@ -10274,7 +9790,7 @@
       <c r="J58" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K58" s="74"/>
+      <c r="K58" s="65"/>
       <c r="L58" s="22"/>
       <c r="M58" s="9" t="s">
         <v>257</v>
@@ -10283,7 +9799,7 @@
       <c r="O58" s="7"/>
       <c r="P58" s="7"/>
     </row>
-    <row r="59" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>73</v>
       </c>
@@ -10310,7 +9826,7 @@
       <c r="J59" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K59" s="74"/>
+      <c r="K59" s="65"/>
       <c r="L59" s="22"/>
       <c r="M59" s="9" t="s">
         <v>257</v>
@@ -10319,7 +9835,7 @@
       <c r="O59" s="7"/>
       <c r="P59" s="7"/>
     </row>
-    <row r="60" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>73</v>
       </c>
@@ -10348,7 +9864,7 @@
       <c r="J60" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="K60" s="77" t="s">
+      <c r="K60" s="66" t="s">
         <v>383</v>
       </c>
       <c r="L60" s="43"/>
@@ -10359,7 +9875,7 @@
       <c r="O60" s="7"/>
       <c r="P60" s="7"/>
     </row>
-    <row r="61" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>73</v>
       </c>
@@ -10388,7 +9904,7 @@
       <c r="J61" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K61" s="78"/>
+      <c r="K61" s="67"/>
       <c r="L61" s="22" t="s">
         <v>385</v>
       </c>
@@ -10399,7 +9915,7 @@
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
     </row>
-    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>73</v>
       </c>
@@ -10428,7 +9944,7 @@
       <c r="J62" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K62" s="78"/>
+      <c r="K62" s="67"/>
       <c r="L62" s="22" t="s">
         <v>387</v>
       </c>
@@ -10439,7 +9955,7 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
     </row>
-    <row r="63" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23" t="s">
         <v>73</v>
       </c>
@@ -10468,7 +9984,7 @@
       <c r="J63" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K63" s="76"/>
+      <c r="K63" s="68"/>
       <c r="L63" s="22"/>
       <c r="M63" s="9" t="s">
         <v>257</v>
@@ -10477,7 +9993,7 @@
       <c r="O63" s="7"/>
       <c r="P63" s="7"/>
     </row>
-    <row r="64" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>73</v>
       </c>
@@ -10506,7 +10022,7 @@
       <c r="J64" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K64" s="74"/>
+      <c r="K64" s="65"/>
       <c r="L64" s="22"/>
       <c r="M64" s="9" t="s">
         <v>257</v>
@@ -10515,7 +10031,7 @@
       <c r="O64" s="7"/>
       <c r="P64" s="7"/>
     </row>
-    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>73</v>
       </c>
@@ -10544,7 +10060,7 @@
       <c r="J65" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K65" s="74"/>
+      <c r="K65" s="65"/>
       <c r="L65" s="22" t="s">
         <v>387</v>
       </c>
@@ -10555,7 +10071,7 @@
       <c r="O65" s="7"/>
       <c r="P65" s="7"/>
     </row>
-    <row r="66" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>73</v>
       </c>
@@ -10582,7 +10098,7 @@
       <c r="J66" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="K66" s="74"/>
+      <c r="K66" s="65"/>
       <c r="L66" s="13"/>
       <c r="M66" s="34" t="s">
         <v>257</v>
@@ -10591,7 +10107,7 @@
       <c r="O66" s="7"/>
       <c r="P66" s="7"/>
     </row>
-    <row r="67" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>73</v>
       </c>
@@ -10629,7 +10145,7 @@
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
     </row>
-    <row r="68" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>73</v>
       </c>
@@ -10667,7 +10183,7 @@
       <c r="O68" s="7"/>
       <c r="P68" s="7"/>
     </row>
-    <row r="69" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="23" t="s">
         <v>73</v>
       </c>
@@ -10696,7 +10212,7 @@
       <c r="J69" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K69" s="76" t="s">
+      <c r="K69" s="68" t="s">
         <v>290</v>
       </c>
       <c r="L69" s="22" t="s">
@@ -10709,7 +10225,7 @@
       <c r="O69" s="7"/>
       <c r="P69" s="7"/>
     </row>
-    <row r="70" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>73</v>
       </c>
@@ -10738,7 +10254,7 @@
       <c r="J70" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K70" s="74"/>
+      <c r="K70" s="65"/>
       <c r="L70" s="22"/>
       <c r="M70" s="9" t="s">
         <v>257</v>
@@ -10747,7 +10263,7 @@
       <c r="O70" s="7"/>
       <c r="P70" s="7"/>
     </row>
-    <row r="71" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>73</v>
       </c>
@@ -10787,7 +10303,7 @@
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
     </row>
-    <row r="72" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>73</v>
       </c>
@@ -10816,7 +10332,7 @@
       <c r="J72" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K72" s="76"/>
+      <c r="K72" s="68"/>
       <c r="L72" s="22"/>
       <c r="M72" s="9" t="s">
         <v>257</v>
@@ -10825,7 +10341,7 @@
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
     </row>
-    <row r="73" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
         <v>73</v>
       </c>
@@ -10852,7 +10368,7 @@
       <c r="J73" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K73" s="74"/>
+      <c r="K73" s="65"/>
       <c r="L73" s="22"/>
       <c r="M73" s="9" t="s">
         <v>257</v>
@@ -10861,7 +10377,7 @@
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
     </row>
-    <row r="74" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>73</v>
       </c>
@@ -10888,7 +10404,7 @@
       <c r="J74" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K74" s="74"/>
+      <c r="K74" s="65"/>
       <c r="L74" s="22"/>
       <c r="M74" s="9" t="s">
         <v>257</v>
@@ -10897,7 +10413,7 @@
       <c r="O74" s="7"/>
       <c r="P74" s="7"/>
     </row>
-    <row r="75" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
         <v>73</v>
       </c>
@@ -10922,7 +10438,7 @@
       <c r="J75" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K75" s="75"/>
+      <c r="K75" s="69"/>
       <c r="L75" s="44"/>
       <c r="M75" s="9" t="s">
         <v>257</v>
@@ -10931,7 +10447,7 @@
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
     </row>
-    <row r="76" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>73</v>
       </c>
@@ -10969,7 +10485,7 @@
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
     </row>
-    <row r="77" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
         <v>73</v>
       </c>
@@ -11000,10 +10516,10 @@
       <c r="J77" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="K77" s="67" t="s">
+      <c r="K77" s="77" t="s">
         <v>410</v>
       </c>
-      <c r="L77" s="73" t="s">
+      <c r="L77" s="64" t="s">
         <v>411</v>
       </c>
       <c r="M77" s="24" t="s">
@@ -11013,7 +10529,7 @@
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
     </row>
-    <row r="78" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="23" t="s">
         <v>73</v>
       </c>
@@ -11044,8 +10560,8 @@
       <c r="J78" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K78" s="69"/>
-      <c r="L78" s="71"/>
+      <c r="K78" s="78"/>
+      <c r="L78" s="80"/>
       <c r="M78" s="34" t="s">
         <v>257</v>
       </c>
@@ -11053,7 +10569,7 @@
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
     </row>
-    <row r="79" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="23" t="s">
         <v>73</v>
       </c>
@@ -11085,7 +10601,7 @@
       <c r="K79" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L79" s="71"/>
+      <c r="L79" s="80"/>
       <c r="M79" s="34" t="s">
         <v>257</v>
       </c>
@@ -11093,7 +10609,7 @@
       <c r="O79" s="7"/>
       <c r="P79" s="7"/>
     </row>
-    <row r="80" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>73</v>
       </c>
@@ -11125,7 +10641,7 @@
       <c r="K80" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="L80" s="75"/>
+      <c r="L80" s="69"/>
       <c r="M80" s="9" t="s">
         <v>257</v>
       </c>
@@ -11133,7 +10649,7 @@
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
     </row>
-    <row r="81" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="s">
         <v>73</v>
       </c>
@@ -11162,7 +10678,7 @@
       <c r="J81" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K81" s="76" t="s">
+      <c r="K81" s="68" t="s">
         <v>290</v>
       </c>
       <c r="L81" s="22" t="s">
@@ -11175,7 +10691,7 @@
       <c r="O81" s="7"/>
       <c r="P81" s="7"/>
     </row>
-    <row r="82" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>73</v>
       </c>
@@ -11204,7 +10720,7 @@
       <c r="J82" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K82" s="74"/>
+      <c r="K82" s="65"/>
       <c r="L82" s="22"/>
       <c r="M82" s="9" t="s">
         <v>257</v>
@@ -11213,7 +10729,7 @@
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
     </row>
-    <row r="83" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>73</v>
       </c>
@@ -11255,7 +10771,7 @@
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
     </row>
-    <row r="84" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>73</v>
       </c>
@@ -11297,7 +10813,7 @@
       <c r="O84" s="7"/>
       <c r="P84" s="7"/>
     </row>
-    <row r="85" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="23" t="s">
         <v>73</v>
       </c>
@@ -11326,7 +10842,7 @@
       <c r="J85" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K85" s="76" t="s">
+      <c r="K85" s="68" t="s">
         <v>424</v>
       </c>
       <c r="L85" s="22"/>
@@ -11337,7 +10853,7 @@
       <c r="O85" s="7"/>
       <c r="P85" s="7"/>
     </row>
-    <row r="86" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>73</v>
       </c>
@@ -11366,7 +10882,7 @@
       <c r="J86" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K86" s="74"/>
+      <c r="K86" s="65"/>
       <c r="L86" s="22"/>
       <c r="M86" s="9" t="s">
         <v>257</v>
@@ -11375,7 +10891,7 @@
       <c r="O86" s="7"/>
       <c r="P86" s="7"/>
     </row>
-    <row r="87" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>73</v>
       </c>
@@ -11404,7 +10920,7 @@
       <c r="J87" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K87" s="74"/>
+      <c r="K87" s="65"/>
       <c r="L87" s="22"/>
       <c r="M87" s="9" t="s">
         <v>257</v>
@@ -11413,7 +10929,7 @@
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
     </row>
-    <row r="88" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>73</v>
       </c>
@@ -11440,7 +10956,7 @@
       <c r="J88" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K88" s="74"/>
+      <c r="K88" s="65"/>
       <c r="L88" s="22"/>
       <c r="M88" s="9" t="s">
         <v>257</v>
@@ -11449,7 +10965,7 @@
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
     </row>
-    <row r="89" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="23" t="s">
         <v>73</v>
       </c>
@@ -11478,7 +10994,7 @@
       <c r="J89" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K89" s="74"/>
+      <c r="K89" s="65"/>
       <c r="L89" s="22"/>
       <c r="M89" s="9" t="s">
         <v>257</v>
@@ -11487,7 +11003,7 @@
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
     </row>
-    <row r="90" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="23" t="s">
         <v>73</v>
       </c>
@@ -11516,7 +11032,7 @@
       <c r="J90" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K90" s="74"/>
+      <c r="K90" s="65"/>
       <c r="L90" s="22"/>
       <c r="M90" s="9" t="s">
         <v>257</v>
@@ -11525,7 +11041,7 @@
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
     </row>
-    <row r="91" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="23" t="s">
         <v>73</v>
       </c>
@@ -11554,10 +11070,10 @@
       <c r="J91" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K91" s="67" t="s">
+      <c r="K91" s="77" t="s">
         <v>430</v>
       </c>
-      <c r="L91" s="70" t="s">
+      <c r="L91" s="79" t="s">
         <v>431</v>
       </c>
       <c r="M91" s="24" t="s">
@@ -11567,7 +11083,7 @@
       <c r="O91" s="7"/>
       <c r="P91" s="7"/>
     </row>
-    <row r="92" spans="1:16" ht="72.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" ht="72.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>73</v>
       </c>
@@ -11596,8 +11112,8 @@
       <c r="J92" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K92" s="68"/>
-      <c r="L92" s="71"/>
+      <c r="K92" s="74"/>
+      <c r="L92" s="80"/>
       <c r="M92" s="9" t="s">
         <v>257</v>
       </c>
@@ -11605,7 +11121,7 @@
       <c r="O92" s="7"/>
       <c r="P92" s="7"/>
     </row>
-    <row r="93" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="23" t="s">
         <v>73</v>
       </c>
@@ -11634,8 +11150,8 @@
       <c r="J93" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="K93" s="68"/>
-      <c r="L93" s="71"/>
+      <c r="K93" s="74"/>
+      <c r="L93" s="80"/>
       <c r="M93" s="9" t="s">
         <v>257</v>
       </c>
@@ -11643,7 +11159,7 @@
       <c r="O93" s="7"/>
       <c r="P93" s="7"/>
     </row>
-    <row r="94" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>73</v>
       </c>
@@ -11670,8 +11186,8 @@
       <c r="J94" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K94" s="69"/>
-      <c r="L94" s="72"/>
+      <c r="K94" s="78"/>
+      <c r="L94" s="81"/>
       <c r="M94" s="9" t="s">
         <v>257</v>
       </c>
@@ -11679,7 +11195,7 @@
       <c r="O94" s="7"/>
       <c r="P94" s="7"/>
     </row>
-    <row r="95" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
         <v>73</v>
       </c>
@@ -11708,7 +11224,7 @@
       <c r="J95" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K95" s="73"/>
+      <c r="K95" s="64"/>
       <c r="L95" s="22"/>
       <c r="M95" s="24" t="s">
         <v>257</v>
@@ -11717,7 +11233,7 @@
       <c r="O95" s="7"/>
       <c r="P95" s="7"/>
     </row>
-    <row r="96" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>73</v>
       </c>
@@ -11746,7 +11262,7 @@
       <c r="J96" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K96" s="74"/>
+      <c r="K96" s="65"/>
       <c r="L96" s="22"/>
       <c r="M96" s="24" t="s">
         <v>257</v>
@@ -11755,7 +11271,7 @@
       <c r="O96" s="7"/>
       <c r="P96" s="7"/>
     </row>
-    <row r="97" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>73</v>
       </c>
@@ -11784,7 +11300,7 @@
       <c r="J97" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K97" s="74"/>
+      <c r="K97" s="65"/>
       <c r="L97" s="22"/>
       <c r="M97" s="24" t="s">
         <v>257</v>
@@ -11793,7 +11309,7 @@
       <c r="O97" s="7"/>
       <c r="P97" s="7"/>
     </row>
-    <row r="98" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>73</v>
       </c>
@@ -11822,7 +11338,7 @@
       <c r="J98" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="K98" s="74"/>
+      <c r="K98" s="65"/>
       <c r="L98" s="22"/>
       <c r="M98" s="24" t="s">
         <v>257</v>
@@ -11831,7 +11347,7 @@
       <c r="O98" s="7"/>
       <c r="P98" s="7"/>
     </row>
-    <row r="99" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>73</v>
       </c>
@@ -11858,7 +11374,7 @@
       <c r="J99" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="K99" s="75"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="37"/>
       <c r="M99" s="39" t="s">
         <v>257</v>
@@ -11867,7 +11383,7 @@
       <c r="O99" s="7"/>
       <c r="P99" s="7"/>
     </row>
-    <row r="100" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23"/>
@@ -11887,28 +11403,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="K20:K24"/>
-    <mergeCell ref="L20:L24"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K42:K47"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="K50:K54"/>
-    <mergeCell ref="K57:K59"/>
-    <mergeCell ref="K60:K62"/>
-    <mergeCell ref="K63:K66"/>
-    <mergeCell ref="K69:K70"/>
     <mergeCell ref="K91:K94"/>
     <mergeCell ref="L91:L94"/>
     <mergeCell ref="K95:K99"/>
@@ -11917,24 +11411,46 @@
     <mergeCell ref="L77:L80"/>
     <mergeCell ref="K81:K82"/>
     <mergeCell ref="K85:K90"/>
+    <mergeCell ref="K50:K54"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="K63:K66"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K42:K47"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -11942,7 +11458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>246</v>
       </c>
@@ -11950,7 +11466,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>247</v>
       </c>
@@ -11958,7 +11474,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
@@ -11966,12 +11482,107 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -11980,129 +11591,34 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:W73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="41.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="13.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>76</v>
       </c>
@@ -12149,7 +11665,7 @@
       <c r="V1" s="21"/>
       <c r="W1" s="21"/>
     </row>
-    <row r="2" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>181</v>
       </c>
@@ -12186,7 +11702,7 @@
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
     </row>
-    <row r="3" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>181</v>
       </c>
@@ -12223,7 +11739,7 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
     </row>
-    <row r="4" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>181</v>
       </c>
@@ -12262,7 +11778,7 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
     </row>
-    <row r="5" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>181</v>
       </c>
@@ -12295,7 +11811,7 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
     </row>
-    <row r="6" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>181</v>
       </c>
@@ -12330,7 +11846,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
     </row>
-    <row r="7" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
         <v>181</v>
       </c>
@@ -12369,7 +11885,7 @@
       <c r="V7" s="21"/>
       <c r="W7" s="21"/>
     </row>
-    <row r="8" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>181</v>
       </c>
@@ -12402,7 +11918,7 @@
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
     </row>
-    <row r="9" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>181</v>
       </c>
@@ -12441,7 +11957,7 @@
       <c r="V9" s="21"/>
       <c r="W9" s="21"/>
     </row>
-    <row r="10" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
         <v>181</v>
       </c>
@@ -12476,7 +11992,7 @@
       <c r="V10" s="21"/>
       <c r="W10" s="21"/>
     </row>
-    <row r="11" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" s="15" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>181</v>
       </c>
@@ -12515,7 +12031,7 @@
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
     </row>
-    <row r="12" spans="1:23" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>181</v>
       </c>
@@ -12552,7 +12068,7 @@
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
     </row>
-    <row r="13" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>208</v>
       </c>
@@ -12591,7 +12107,7 @@
       <c r="V13" s="21"/>
       <c r="W13" s="21"/>
     </row>
-    <row r="14" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" s="15" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>208</v>
       </c>
@@ -12624,7 +12140,7 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
     </row>
-    <row r="15" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" s="15" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>208</v>
       </c>
@@ -12661,7 +12177,7 @@
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
     </row>
-    <row r="16" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>208</v>
       </c>
@@ -12698,7 +12214,7 @@
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
     </row>
-    <row r="17" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>208</v>
       </c>
@@ -12737,7 +12253,7 @@
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
     </row>
-    <row r="18" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>208</v>
       </c>
@@ -12776,7 +12292,7 @@
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
     </row>
-    <row r="19" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>208</v>
       </c>
@@ -12813,7 +12329,7 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
     </row>
-    <row r="20" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>208</v>
       </c>
@@ -12852,7 +12368,7 @@
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
     </row>
-    <row r="21" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>208</v>
       </c>
@@ -12889,7 +12405,7 @@
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
     </row>
-    <row r="22" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>208</v>
       </c>
@@ -12928,7 +12444,7 @@
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
     </row>
-    <row r="23" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>222</v>
       </c>
@@ -12959,7 +12475,7 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>147</v>
       </c>
@@ -13002,7 +12518,7 @@
       <c r="V24" s="23"/>
       <c r="W24" s="23"/>
     </row>
-    <row r="25" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>147</v>
       </c>
@@ -13043,7 +12559,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
     </row>
-    <row r="26" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>147</v>
       </c>
@@ -13067,7 +12583,7 @@
       </c>
       <c r="H26" s="21"/>
       <c r="I26" s="13" t="s">
-        <v>693</v>
+        <v>637</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="6"/>
@@ -13084,7 +12600,7 @@
       <c r="V26" s="8"/>
       <c r="W26" s="12"/>
     </row>
-    <row r="27" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>147</v>
       </c>
@@ -13121,7 +12637,7 @@
       <c r="V27" s="8"/>
       <c r="W27" s="12"/>
     </row>
-    <row r="28" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>147</v>
       </c>
@@ -13162,7 +12678,7 @@
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
     </row>
-    <row r="29" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
         <v>147</v>
       </c>
@@ -13201,7 +12717,7 @@
       <c r="V29" s="8"/>
       <c r="W29" s="12"/>
     </row>
-    <row r="30" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
         <v>147</v>
       </c>
@@ -13238,7 +12754,7 @@
       <c r="V30" s="8"/>
       <c r="W30" s="12"/>
     </row>
-    <row r="31" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>147</v>
       </c>
@@ -13277,7 +12793,7 @@
       <c r="V31" s="8"/>
       <c r="W31" s="12"/>
     </row>
-    <row r="32" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>147</v>
       </c>
@@ -13314,7 +12830,7 @@
       <c r="V32" s="8"/>
       <c r="W32" s="12"/>
     </row>
-    <row r="33" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>147</v>
       </c>
@@ -13355,7 +12871,7 @@
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
     </row>
-    <row r="34" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>147</v>
       </c>
@@ -13394,7 +12910,7 @@
       <c r="V34" s="8"/>
       <c r="W34" s="12"/>
     </row>
-    <row r="35" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>147</v>
       </c>
@@ -13431,7 +12947,7 @@
       <c r="V35" s="8"/>
       <c r="W35" s="12"/>
     </row>
-    <row r="36" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>147</v>
       </c>
@@ -13470,7 +12986,7 @@
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
     </row>
-    <row r="37" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>147</v>
       </c>
@@ -13507,7 +13023,7 @@
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
     </row>
-    <row r="38" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23" t="s">
         <v>228</v>
       </c>
@@ -13548,7 +13064,7 @@
       <c r="V38" s="23"/>
       <c r="W38" s="23"/>
     </row>
-    <row r="39" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>228</v>
       </c>
@@ -13587,7 +13103,7 @@
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
     </row>
-    <row r="40" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>228</v>
       </c>
@@ -13624,7 +13140,7 @@
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
     </row>
-    <row r="41" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>228</v>
       </c>
@@ -13659,7 +13175,7 @@
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
     </row>
-    <row r="42" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
         <v>228</v>
       </c>
@@ -13698,7 +13214,7 @@
       <c r="V42" s="8"/>
       <c r="W42" s="12"/>
     </row>
-    <row r="43" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
         <v>228</v>
       </c>
@@ -13737,7 +13253,7 @@
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
     </row>
-    <row r="44" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
         <v>228</v>
       </c>
@@ -13776,7 +13292,7 @@
       <c r="V44" s="8"/>
       <c r="W44" s="8"/>
     </row>
-    <row r="45" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
         <v>228</v>
       </c>
@@ -13817,7 +13333,7 @@
       <c r="V45" s="8"/>
       <c r="W45" s="8"/>
     </row>
-    <row r="46" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
         <v>228</v>
       </c>
@@ -13856,7 +13372,7 @@
       <c r="V46" s="8"/>
       <c r="W46" s="12"/>
     </row>
-    <row r="47" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
         <v>228</v>
       </c>
@@ -13895,7 +13411,7 @@
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
     </row>
-    <row r="48" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
         <v>228</v>
       </c>
@@ -13932,7 +13448,7 @@
       <c r="V48" s="8"/>
       <c r="W48" s="8"/>
     </row>
-    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
         <v>228</v>
       </c>
@@ -13967,7 +13483,7 @@
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
     </row>
-    <row r="50" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
         <v>228</v>
       </c>
@@ -14006,7 +13522,7 @@
       <c r="V50" s="8"/>
       <c r="W50" s="8"/>
     </row>
-    <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="21" t="s">
         <v>228</v>
       </c>
@@ -14043,7 +13559,7 @@
       <c r="V51" s="8"/>
       <c r="W51" s="8"/>
     </row>
-    <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="21" t="s">
         <v>228</v>
       </c>
@@ -14078,7 +13594,7 @@
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
     </row>
-    <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>228</v>
       </c>
@@ -14117,7 +13633,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
     </row>
-    <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="21" t="s">
         <v>228</v>
       </c>
@@ -14158,7 +13674,7 @@
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
     </row>
-    <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="21" t="s">
         <v>228</v>
       </c>
@@ -14193,7 +13709,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
     </row>
-    <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="21" t="s">
         <v>228</v>
       </c>
@@ -14230,7 +13746,7 @@
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
     </row>
-    <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="21" t="s">
         <v>228</v>
       </c>
@@ -14269,7 +13785,7 @@
       <c r="V57" s="8"/>
       <c r="W57" s="12"/>
     </row>
-    <row r="58" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>228</v>
       </c>
@@ -14287,7 +13803,7 @@
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13" t="s">
-        <v>694</v>
+        <v>638</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
@@ -14304,7 +13820,7 @@
       <c r="V58" s="13"/>
       <c r="W58" s="13"/>
     </row>
-    <row r="59" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>228</v>
       </c>
@@ -14320,7 +13836,7 @@
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13" t="s">
-        <v>694</v>
+        <v>638</v>
       </c>
       <c r="J59" s="13"/>
       <c r="K59" s="13"/>
@@ -14337,7 +13853,7 @@
       <c r="V59" s="13"/>
       <c r="W59" s="13"/>
     </row>
-    <row r="60" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>237</v>
       </c>
@@ -14370,7 +13886,7 @@
       <c r="V60" s="13"/>
       <c r="W60" s="13"/>
     </row>
-    <row r="61" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>237</v>
       </c>
@@ -14403,7 +13919,7 @@
       <c r="V61" s="13"/>
       <c r="W61" s="13"/>
     </row>
-    <row r="62" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>237</v>
       </c>
@@ -14436,7 +13952,7 @@
       <c r="V62" s="13"/>
       <c r="W62" s="13"/>
     </row>
-    <row r="63" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>237</v>
       </c>
@@ -14469,7 +13985,7 @@
       <c r="V63" s="13"/>
       <c r="W63" s="13"/>
     </row>
-    <row r="64" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>237</v>
       </c>
@@ -14502,7 +14018,7 @@
       <c r="V64" s="13"/>
       <c r="W64" s="13"/>
     </row>
-    <row r="65" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>237</v>
       </c>
@@ -14535,7 +14051,7 @@
       <c r="V65" s="13"/>
       <c r="W65" s="13"/>
     </row>
-    <row r="66" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>237</v>
       </c>
@@ -14568,7 +14084,7 @@
       <c r="V66" s="13"/>
       <c r="W66" s="13"/>
     </row>
-    <row r="67" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>237</v>
       </c>
@@ -14601,7 +14117,7 @@
       <c r="V67" s="13"/>
       <c r="W67" s="13"/>
     </row>
-    <row r="68" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>237</v>
       </c>
@@ -14634,7 +14150,7 @@
       <c r="V68" s="13"/>
       <c r="W68" s="13"/>
     </row>
-    <row r="69" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>237</v>
       </c>
@@ -14667,7 +14183,7 @@
       <c r="V69" s="13"/>
       <c r="W69" s="13"/>
     </row>
-    <row r="70" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>237</v>
       </c>
@@ -14700,7 +14216,7 @@
       <c r="V70" s="13"/>
       <c r="W70" s="13"/>
     </row>
-    <row r="71" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>237</v>
       </c>
@@ -14733,7 +14249,7 @@
       <c r="V71" s="13"/>
       <c r="W71" s="13"/>
     </row>
-    <row r="72" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>237</v>
       </c>
@@ -14766,7 +14282,7 @@
       <c r="V72" s="13"/>
       <c r="W72" s="13"/>
     </row>
-    <row r="73" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" s="15" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>237</v>
       </c>
@@ -14804,344 +14320,344 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="66" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="100.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="100.5546875" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="62" t="s">
         <v>152</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>691</v>
+        <v>635</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="C2" s="65" t="s">
+        <v>636</v>
+      </c>
+      <c r="C2" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>157</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="65">
+      <c r="C3" s="62">
         <v>1000</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>157</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="62">
         <v>1000</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="62">
         <v>1E-3</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>692</v>
+        <v>636</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="C6" s="65" t="s">
+        <v>635</v>
+      </c>
+      <c r="C6" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="65">
+      <c r="C7" s="62">
         <v>1000</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>161</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="65">
+      <c r="C8" s="62">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="65">
+      <c r="C9" s="62">
         <v>1</v>
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>165</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="65">
+      <c r="C10" s="62">
         <v>1</v>
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>165</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="62">
         <v>1</v>
       </c>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>88</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="62">
         <v>1</v>
       </c>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="62">
         <v>1</v>
       </c>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>88</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="62">
         <v>1E-3</v>
       </c>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>162</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="62">
         <v>1</v>
       </c>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="62">
         <v>1000</v>
       </c>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="62">
         <v>1000</v>
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>171</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="62">
         <v>1</v>
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>162</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="62">
         <v>1</v>
       </c>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>162</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="62">
         <v>1000</v>
       </c>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>162</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="62">
         <v>1000</v>
       </c>
       <c r="D21" s="7"/>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="62">
         <v>1000</v>
       </c>
       <c r="D22" s="7"/>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="62">
         <v>1</v>
       </c>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="62">
         <v>1</v>
       </c>
       <c r="D24" s="7"/>
     </row>
-    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>84</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="62">
         <v>1</v>
       </c>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>88</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="62">
         <v>1.33</v>
       </c>
       <c r="D26" s="7"/>
